--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5299,31 +5302,111 @@
       <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25498.74</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25548.78</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25325.52</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>223.26</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24652.31</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24786.22</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25214.14</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25642.07</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25922.98</v>
+      </c>
+      <c r="N58" t="n">
+        <v>26203.9</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26778.83</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>24652.31</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>24786.22</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>25214.14</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>25642.07</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>25922.98</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>26203.9</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>26778.83</v>
+      <c r="I59" s="14" t="n">
+        <v>25102.26</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>25772.04</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5317,13 +5314,13 @@
         <v>25325.52</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>25440.81</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-127.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.005</v>
       </c>
       <c r="H58" t="n">
         <v>223.26</v>
@@ -5349,10 +5346,8 @@
       <c r="O58" t="n">
         <v>26778.83</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5360,9 +5355,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5382,30 +5377,30 @@
       <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
+      <c r="I59" s="13" t="n">
         <v>25102.26</v>
       </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
+      <c r="J59" s="13" t="n">
+        <v>25219.38</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>25329.18</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>25438.98</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>25552.44</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>25665.9</v>
+      </c>
+      <c r="O59" s="13" t="n">
         <v>25772.04</v>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5311,19 +5311,19 @@
         <v>25548.78</v>
       </c>
       <c r="D58" t="n">
-        <v>25325.52</v>
+        <v>25172.89</v>
       </c>
       <c r="E58" t="n">
-        <v>25440.81</v>
+        <v>25402.28</v>
       </c>
       <c r="F58" t="n">
-        <v>-127.75</v>
+        <v>-166.28</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0065</v>
       </c>
       <c r="H58" t="n">
-        <v>223.26</v>
+        <v>375.89</v>
       </c>
       <c r="I58" t="n">
         <v>24652.31</v>
@@ -5352,12 +5352,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5383,25 +5385,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>25102.26</v>
+        <v>24797</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>25219.38</v>
+        <v>25047.11</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>25329.18</v>
+        <v>25214.33</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>25438.98</v>
+        <v>25381.56</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>25552.44</v>
+        <v>25590.22</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>25665.9</v>
+        <v>25798.89</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25772.04</v>
+        <v>25924.67</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>264.5</v>
       </c>
       <c r="I2" t="n">
-        <v>23344.37</v>
+        <v>23741.47</v>
       </c>
       <c r="J2" t="n">
-        <v>23823.99</v>
+        <v>23972.91</v>
       </c>
       <c r="K2" t="n">
-        <v>24061.37</v>
+        <v>24160.64</v>
       </c>
       <c r="L2" t="n">
-        <v>24298.74</v>
+        <v>24348.38</v>
       </c>
       <c r="M2" t="n">
-        <v>24657.24</v>
+        <v>24557.96</v>
       </c>
       <c r="N2" t="n">
-        <v>25015.73</v>
+        <v>24767.55</v>
       </c>
       <c r="O2" t="n">
-        <v>25131.98</v>
+        <v>24933.43</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5308,22 +5308,22 @@
         <v>25498.74</v>
       </c>
       <c r="C58" t="n">
-        <v>25548.78</v>
+        <v>25599.07</v>
       </c>
       <c r="D58" t="n">
         <v>25172.89</v>
       </c>
       <c r="E58" t="n">
-        <v>25402.28</v>
+        <v>25537.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-166.28</v>
+        <v>-30.81</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0012</v>
       </c>
       <c r="H58" t="n">
-        <v>375.89</v>
+        <v>426.18</v>
       </c>
       <c r="I58" t="n">
         <v>24652.31</v>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5385,25 +5385,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24797</v>
+        <v>24746.71</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>25047.11</v>
+        <v>25187.46</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>25214.33</v>
+        <v>25324.66</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>25381.56</v>
+        <v>25461.87</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>25590.22</v>
+        <v>25750.84</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>25798.89</v>
+        <v>26039.81</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>25924.67</v>
+        <v>26025.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,25 +666,25 @@
         <v>264.5</v>
       </c>
       <c r="I2" t="n">
-        <v>23741.47</v>
+        <v>23874.63</v>
       </c>
       <c r="J2" t="n">
-        <v>23972.91</v>
+        <v>24022.84</v>
       </c>
       <c r="K2" t="n">
-        <v>24160.64</v>
+        <v>24193.93</v>
       </c>
       <c r="L2" t="n">
-        <v>24348.38</v>
+        <v>24365.02</v>
       </c>
       <c r="M2" t="n">
-        <v>24557.96</v>
+        <v>24524.67</v>
       </c>
       <c r="N2" t="n">
-        <v>24767.55</v>
+        <v>24684.32</v>
       </c>
       <c r="O2" t="n">
-        <v>24933.43</v>
+        <v>24866.85</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,12 +692,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -716,7 +718,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -783,7 +785,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -797,7 +799,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -863,7 +865,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -877,7 +879,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -941,7 +943,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -957,7 +959,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1029,7 +1031,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1043,7 +1045,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1107,7 +1109,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1121,7 +1123,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1189,7 +1191,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1273,7 +1275,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1359,7 +1361,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1441,7 +1443,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1529,7 +1531,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1615,7 +1617,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1699,7 +1701,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1785,7 +1787,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1867,7 +1869,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1955,7 +1957,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2035,7 +2037,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2117,7 +2119,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2199,7 +2201,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2279,7 +2281,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2363,7 +2365,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2447,7 +2449,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2531,7 +2533,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2545,7 +2547,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2613,7 +2615,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2627,7 +2629,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2691,7 +2693,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2707,7 +2709,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2775,7 +2777,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2791,7 +2793,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2859,7 +2861,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2875,7 +2877,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2945,7 +2947,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2959,7 +2961,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3033,7 +3035,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3047,7 +3049,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3111,7 +3113,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3125,7 +3127,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3193,7 +3195,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3207,7 +3209,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3271,7 +3273,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3287,7 +3289,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3351,7 +3353,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3367,7 +3369,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3435,7 +3437,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3451,7 +3453,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3519,7 +3521,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3535,7 +3537,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3605,7 +3607,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3619,7 +3621,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3689,7 +3691,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3703,7 +3705,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3771,7 +3773,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3791,7 +3793,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3861,7 +3863,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3875,7 +3877,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3939,7 +3941,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4027,7 +4029,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4109,7 +4111,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4197,7 +4199,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4279,7 +4281,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4363,7 +4365,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4445,7 +4447,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4531,7 +4533,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4615,7 +4617,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4697,7 +4699,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4777,7 +4779,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4861,7 +4863,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4943,7 +4945,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5029,7 +5031,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5111,7 +5113,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5197,7 +5199,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5211,7 +5213,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5277,7 +5279,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5291,7 +5293,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5357,7 +5359,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5371,7 +5373,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5310,22 +5310,22 @@
         <v>25498.74</v>
       </c>
       <c r="C58" t="n">
-        <v>25599.07</v>
+        <v>25800.62</v>
       </c>
       <c r="D58" t="n">
         <v>25172.89</v>
       </c>
       <c r="E58" t="n">
-        <v>25537.75</v>
+        <v>25716.71</v>
       </c>
       <c r="F58" t="n">
-        <v>-30.81</v>
+        <v>148.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>426.18</v>
+        <v>627.73</v>
       </c>
       <c r="I58" t="n">
         <v>24652.31</v>
@@ -5359,9 +5359,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5378,7 +5378,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5387,25 +5391,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>24746.71</v>
+        <v>24545.16</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>25187.46</v>
+        <v>25203.96</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>25324.66</v>
+        <v>25402.85</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>25461.87</v>
+        <v>25601.73</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>25750.84</v>
+        <v>26030.58</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>26039.81</v>
+        <v>26459.42</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>26025.25</v>
+        <v>26428.35</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>264.5</v>
       </c>
       <c r="I2" t="n">
-        <v>23874.63</v>
+        <v>24119.09</v>
       </c>
       <c r="J2" t="n">
-        <v>24022.84</v>
+        <v>24114.51</v>
       </c>
       <c r="K2" t="n">
-        <v>24193.93</v>
+        <v>24255.05</v>
       </c>
       <c r="L2" t="n">
-        <v>24365.02</v>
+        <v>24395.58</v>
       </c>
       <c r="M2" t="n">
-        <v>24524.67</v>
+        <v>24463.56</v>
       </c>
       <c r="N2" t="n">
-        <v>24684.32</v>
+        <v>24531.53</v>
       </c>
       <c r="O2" t="n">
-        <v>24866.85</v>
+        <v>24744.62</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5382,34 +5375,6 @@
         <is>
           <t>弱警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>24545.16</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>25203.96</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>25402.85</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>25601.73</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>26030.58</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>26459.42</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>26428.35</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,56 +634,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24313.82</v>
+        <v>24232.02</v>
       </c>
       <c r="C2" t="n">
-        <v>24444.41</v>
+        <v>24377.38</v>
       </c>
       <c r="D2" t="n">
-        <v>24179.91</v>
+        <v>23881.98</v>
       </c>
       <c r="E2" t="n">
-        <v>24363.09</v>
+        <v>23902.21</v>
       </c>
       <c r="F2" t="n">
-        <v>3.79</v>
+        <v>-460.88</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.0189</v>
       </c>
       <c r="H2" t="n">
-        <v>264.5</v>
+        <v>495.4</v>
       </c>
       <c r="I2" t="n">
-        <v>24119.09</v>
+        <v>23915.41</v>
       </c>
       <c r="J2" t="n">
-        <v>24114.51</v>
+        <v>24124.05</v>
       </c>
       <c r="K2" t="n">
-        <v>24255.05</v>
+        <v>24230.84</v>
       </c>
       <c r="L2" t="n">
-        <v>24395.58</v>
+        <v>24337.62</v>
       </c>
       <c r="M2" t="n">
-        <v>24463.56</v>
+        <v>24495.34</v>
       </c>
       <c r="N2" t="n">
-        <v>24531.53</v>
+        <v>24653.05</v>
       </c>
       <c r="O2" t="n">
-        <v>24744.62</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>24708.91</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,7 +696,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -706,78 +710,70 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24232.02</v>
+        <v>24012.04</v>
       </c>
       <c r="C3" t="n">
-        <v>24377.38</v>
+        <v>24046.85</v>
       </c>
       <c r="D3" t="n">
-        <v>23881.98</v>
+        <v>23482.67</v>
       </c>
       <c r="E3" t="n">
-        <v>23902.21</v>
+        <v>23596.98</v>
       </c>
       <c r="F3" t="n">
-        <v>-460.88</v>
+        <v>-305.23</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0128</v>
       </c>
       <c r="H3" t="n">
-        <v>495.4</v>
+        <v>564.1799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>23915.41</v>
+        <v>23386.58</v>
       </c>
       <c r="J3" t="n">
-        <v>24124.05</v>
+        <v>23293.08</v>
       </c>
       <c r="K3" t="n">
-        <v>24230.84</v>
+        <v>23654.51</v>
       </c>
       <c r="L3" t="n">
-        <v>24337.62</v>
+        <v>24015.95</v>
       </c>
       <c r="M3" t="n">
-        <v>24495.34</v>
+        <v>24149.91</v>
       </c>
       <c r="N3" t="n">
-        <v>24653.05</v>
+        <v>24283.88</v>
       </c>
       <c r="O3" t="n">
-        <v>24708.91</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>24872.78</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -792,7 +788,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -802,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24012.04</v>
+        <v>23771.86</v>
       </c>
       <c r="C4" t="n">
-        <v>24046.85</v>
+        <v>23883.58</v>
       </c>
       <c r="D4" t="n">
-        <v>23482.67</v>
+        <v>23563.37</v>
       </c>
       <c r="E4" t="n">
-        <v>23596.98</v>
+        <v>23698.15</v>
       </c>
       <c r="F4" t="n">
-        <v>-305.23</v>
+        <v>101.17</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0128</v>
+        <v>0.0043</v>
       </c>
       <c r="H4" t="n">
-        <v>564.1799999999999</v>
+        <v>320.21</v>
       </c>
       <c r="I4" t="n">
-        <v>23386.58</v>
+        <v>22918.49</v>
       </c>
       <c r="J4" t="n">
-        <v>23293.08</v>
+        <v>22948.91</v>
       </c>
       <c r="K4" t="n">
-        <v>23654.51</v>
+        <v>23314.89</v>
       </c>
       <c r="L4" t="n">
-        <v>24015.95</v>
+        <v>23680.87</v>
       </c>
       <c r="M4" t="n">
-        <v>24149.91</v>
+        <v>23879.07</v>
       </c>
       <c r="N4" t="n">
-        <v>24283.88</v>
+        <v>24077.27</v>
       </c>
       <c r="O4" t="n">
-        <v>24872.78</v>
+        <v>24611.03</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,18 +849,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -872,161 +868,159 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23771.86</v>
+        <v>23785.26</v>
       </c>
       <c r="C5" t="n">
-        <v>23883.58</v>
+        <v>23855.35</v>
       </c>
       <c r="D5" t="n">
-        <v>23563.37</v>
+        <v>23284.67</v>
       </c>
       <c r="E5" t="n">
-        <v>23698.15</v>
+        <v>23639.41</v>
       </c>
       <c r="F5" t="n">
-        <v>101.17</v>
+        <v>-58.74</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0025</v>
       </c>
       <c r="H5" t="n">
-        <v>320.21</v>
+        <v>570.6799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>22918.49</v>
+        <v>23243.16</v>
       </c>
       <c r="J5" t="n">
-        <v>22948.91</v>
+        <v>23365.28</v>
       </c>
       <c r="K5" t="n">
-        <v>23314.89</v>
+        <v>23538.04</v>
       </c>
       <c r="L5" t="n">
-        <v>23680.87</v>
+        <v>23710.81</v>
       </c>
       <c r="M5" t="n">
-        <v>23879.07</v>
+        <v>23858.26</v>
       </c>
       <c r="N5" t="n">
-        <v>24077.27</v>
+        <v>24005.7</v>
       </c>
       <c r="O5" t="n">
-        <v>24611.03</v>
+        <v>24203.79</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23785.26</v>
+        <v>23567.49</v>
       </c>
       <c r="C6" t="n">
-        <v>23855.35</v>
+        <v>23756.04</v>
       </c>
       <c r="D6" t="n">
-        <v>23284.67</v>
+        <v>23383.84</v>
       </c>
       <c r="E6" t="n">
-        <v>23639.41</v>
+        <v>23739.47</v>
       </c>
       <c r="F6" t="n">
-        <v>-58.74</v>
+        <v>100.06</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0042</v>
       </c>
       <c r="H6" t="n">
-        <v>570.6799999999999</v>
+        <v>372.2</v>
       </c>
       <c r="I6" t="n">
-        <v>23243.16</v>
+        <v>22713.99</v>
       </c>
       <c r="J6" t="n">
-        <v>23365.28</v>
+        <v>23103.43</v>
       </c>
       <c r="K6" t="n">
-        <v>23538.04</v>
+        <v>23354.07</v>
       </c>
       <c r="L6" t="n">
-        <v>23710.81</v>
+        <v>23604.71</v>
       </c>
       <c r="M6" t="n">
-        <v>23858.26</v>
+        <v>23924.75</v>
       </c>
       <c r="N6" t="n">
-        <v>24005.7</v>
+        <v>24244.79</v>
       </c>
       <c r="O6" t="n">
-        <v>24203.79</v>
+        <v>24426.03</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1038,60 +1032,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23567.49</v>
+        <v>23835.61</v>
       </c>
       <c r="C7" t="n">
-        <v>23756.04</v>
+        <v>24524.11</v>
       </c>
       <c r="D7" t="n">
-        <v>23383.84</v>
+        <v>23666.81</v>
       </c>
       <c r="E7" t="n">
-        <v>23739.47</v>
+        <v>24378.8</v>
       </c>
       <c r="F7" t="n">
-        <v>100.06</v>
+        <v>639.33</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0269</v>
       </c>
       <c r="H7" t="n">
-        <v>372.2</v>
+        <v>857.3</v>
       </c>
       <c r="I7" t="n">
-        <v>22713.99</v>
+        <v>23011.64</v>
       </c>
       <c r="J7" t="n">
-        <v>23103.43</v>
+        <v>23452.04</v>
       </c>
       <c r="K7" t="n">
-        <v>23354.07</v>
+        <v>23553.37</v>
       </c>
       <c r="L7" t="n">
-        <v>23604.71</v>
+        <v>23654.71</v>
       </c>
       <c r="M7" t="n">
-        <v>23924.75</v>
+        <v>23925.57</v>
       </c>
       <c r="N7" t="n">
-        <v>24244.79</v>
+        <v>24196.44</v>
       </c>
       <c r="O7" t="n">
-        <v>24426.03</v>
+        <v>24128.24</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,78 +1100,80 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C8" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D8" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E8" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F8" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H8" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I8" t="n">
-        <v>23011.64</v>
+        <v>22809.51</v>
       </c>
       <c r="J8" t="n">
-        <v>23452.04</v>
+        <v>23663.17</v>
       </c>
       <c r="K8" t="n">
-        <v>23553.37</v>
+        <v>23950.15</v>
       </c>
       <c r="L8" t="n">
-        <v>23654.71</v>
+        <v>24237.13</v>
       </c>
       <c r="M8" t="n">
-        <v>23925.57</v>
+        <v>24807.45</v>
       </c>
       <c r="N8" t="n">
-        <v>24196.44</v>
+        <v>25377.77</v>
       </c>
       <c r="O8" t="n">
-        <v>24128.24</v>
+        <v>25381.41</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,93 +1184,95 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C9" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D9" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E9" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F9" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H9" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I9" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J9" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K9" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L9" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M9" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N9" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O9" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1282,243 +1284,243 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C10" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D10" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E10" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F10" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H10" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I10" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J10" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K10" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L10" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M10" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N10" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O10" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C11" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D11" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E11" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F11" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H11" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I11" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J11" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K11" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L11" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M11" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N11" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O11" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C12" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D12" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E12" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F12" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H12" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I12" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J12" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K12" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L12" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M12" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N12" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O12" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1529,8 +1531,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1538,7 +1542,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1552,306 +1556,304 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C13" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D13" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E13" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F13" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H13" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I13" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J13" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K13" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L13" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M13" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N13" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O13" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C14" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D14" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E14" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F14" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H14" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I14" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J14" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K14" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L14" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M14" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N14" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O14" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C15" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D15" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E15" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F15" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H15" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I15" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J15" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K15" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L15" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M15" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N15" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O15" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C16" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D16" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E16" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F16" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H16" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J16" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K16" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L16" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M16" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N16" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O16" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,85 +1861,81 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="11" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C17" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D17" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E17" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F17" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H17" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I17" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J17" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K17" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L17" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M17" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N17" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O17" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,12 +1943,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1966,7 +1962,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1976,50 +1972,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C18" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D18" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E18" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F18" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H18" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I18" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J18" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K18" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L18" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M18" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N18" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O18" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2027,18 +2023,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2046,60 +2042,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C19" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D19" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E19" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F19" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H19" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I19" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J19" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K19" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L19" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M19" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N19" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O19" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,12 +2107,10 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2126,64 +2124,60 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C20" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D20" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E20" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F20" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I20" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J20" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K20" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L20" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M20" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N20" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O20" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2191,24 +2185,32 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2218,50 +2220,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C21" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D21" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E21" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F21" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H21" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I21" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J21" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K21" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L21" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M21" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N21" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O21" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2269,32 +2271,30 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2304,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C22" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D22" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E22" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F22" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H22" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I22" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J22" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K22" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L22" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M22" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N22" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O22" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,27 +2358,21 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2388,63 +2382,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C23" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D23" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E23" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F23" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H23" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J23" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K23" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L23" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M23" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N23" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O23" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>25817.05</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2466,66 +2466,64 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C24" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D24" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E24" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F24" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H24" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I24" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J24" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K24" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L24" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M24" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N24" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O24" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2540,7 +2538,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2550,132 +2548,134 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C25" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D25" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E25" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F25" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H25" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I25" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J25" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K25" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L25" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M25" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N25" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O25" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="10" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C26" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D26" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E26" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F26" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H26" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I26" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J26" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K26" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L26" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M26" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N26" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O26" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2686,7 +2686,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2702,7 +2702,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="10" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2716,50 +2716,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C27" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D27" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E27" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F27" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H27" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I27" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J27" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K27" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L27" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M27" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N27" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O27" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,14 +2770,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2786,7 +2786,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="10" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2800,50 +2800,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C28" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D28" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E28" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F28" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H28" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I28" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J28" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K28" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L28" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M28" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N28" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O28" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,18 +2851,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2870,7 +2870,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2884,65 +2884,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C29" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D29" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E29" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F29" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H29" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I29" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J29" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K29" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L29" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M29" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N29" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O29" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2954,83 +2958,73 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C30" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D30" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E30" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F30" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H30" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I30" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J30" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K30" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L30" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M30" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N30" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O30" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26452.34</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3042,7 +3036,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="10" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3052,63 +3046,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C31" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D31" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E31" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F31" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H31" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I31" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J31" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K31" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L31" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M31" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N31" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O31" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3120,7 +3118,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="10" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3130,79 +3128,77 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C32" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D32" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E32" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H32" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I32" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J32" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K32" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L32" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M32" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N32" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O32" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="10" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3212,50 +3208,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C33" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D33" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E33" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F33" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H33" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I33" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J33" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K33" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L33" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M33" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N33" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O33" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3266,14 +3262,14 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3282,60 +3278,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C34" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D34" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E34" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F34" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H34" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I34" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J34" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K34" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L34" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M34" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N34" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O34" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3346,7 +3346,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="11" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3362,7 +3362,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="10" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3376,50 +3376,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C35" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D35" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E35" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F35" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H35" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I35" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J35" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K35" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L35" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M35" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N35" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O35" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3430,7 +3430,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3446,7 +3446,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="10" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3460,50 +3460,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C36" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D36" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E36" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F36" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H36" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J36" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K36" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L36" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M36" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N36" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O36" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3511,83 +3511,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C37" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D37" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E37" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F37" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H37" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I37" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J37" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K37" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L37" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M37" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N37" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O37" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3614,7 +3614,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="10" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3628,50 +3628,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C38" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D38" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E38" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F38" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H38" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I38" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J38" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K38" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L38" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M38" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N38" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O38" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3679,83 +3679,87 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="10" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C39" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D39" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E39" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F39" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H39" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J39" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K39" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L39" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M39" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N39" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O39" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3763,87 +3767,79 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W39" s="10" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C40" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D40" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E40" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F40" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H40" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I40" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J40" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K40" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L40" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M40" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N40" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O40" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3851,79 +3847,87 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C41" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D41" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E41" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F41" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I41" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J41" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K41" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L41" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M41" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N41" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O41" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3934,84 +3938,76 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="11" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C42" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D42" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E42" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F42" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H42" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I42" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J42" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K42" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L42" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M42" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N42" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O42" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4019,17 +4015,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4038,63 +4036,69 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C43" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D43" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E43" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H43" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J43" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K43" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L43" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M43" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N43" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O43" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
@@ -4109,10 +4113,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4120,7 +4122,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4134,302 +4136,300 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C44" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D44" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E44" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F44" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H44" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I44" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J44" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K44" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L44" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M44" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N44" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O44" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
       </c>
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C45" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D45" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E45" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F45" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H45" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I45" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J45" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K45" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L45" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M45" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N45" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O45" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C46" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D46" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E46" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F46" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H46" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I46" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J46" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K46" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L46" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M46" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N46" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O46" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C47" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D47" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E47" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F47" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H47" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I47" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J47" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K47" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L47" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M47" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N47" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O47" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4437,83 +4437,83 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C48" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D48" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E48" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F48" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H48" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I48" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J48" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K48" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L48" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M48" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N48" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O48" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4540,64 +4540,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C49" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D49" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E49" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F49" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H49" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I49" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J49" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K49" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L49" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M49" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N49" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O49" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4605,83 +4605,79 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C50" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D50" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E50" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F50" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H50" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I50" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J50" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K50" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L50" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M50" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N50" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O50" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4692,23 +4688,27 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="11" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4718,50 +4718,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C51" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D51" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E51" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F51" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H51" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J51" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K51" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L51" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M51" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N51" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O51" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4772,7 +4772,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4787,12 +4787,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4802,50 +4800,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C52" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D52" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E52" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F52" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H52" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I52" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J52" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K52" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L52" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M52" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N52" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O52" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4856,25 +4854,23 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4884,249 +4880,251 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C53" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D53" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E53" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F53" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H53" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I53" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J53" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K53" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L53" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M53" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N53" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O53" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+        <v>26901.43</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C54" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D54" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E54" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F54" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H54" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I54" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J54" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K54" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L54" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M54" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N54" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O54" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C55" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D55" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E55" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F55" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H55" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I55" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J55" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K55" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L55" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M55" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N55" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O55" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5134,64 +5132,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C56" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D56" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E56" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F56" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H56" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I56" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J56" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K56" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L56" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M56" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N56" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O56" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5206,7 +5202,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="10" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5216,50 +5212,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C57" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D57" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E57" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F57" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H57" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I57" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J57" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K57" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L57" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M57" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N57" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O57" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5286,96 +5282,12 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25498.74</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25800.62</v>
-      </c>
-      <c r="D58" t="n">
-        <v>25172.89</v>
-      </c>
-      <c r="E58" t="n">
-        <v>25716.71</v>
-      </c>
-      <c r="F58" t="n">
-        <v>148.15</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="H58" t="n">
-        <v>627.73</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24652.31</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24786.22</v>
-      </c>
-      <c r="K58" t="n">
-        <v>25214.14</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25642.07</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25922.98</v>
-      </c>
-      <c r="N58" t="n">
-        <v>26203.9</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26778.83</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5289,6 +5292,92 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25491.35</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25617.99</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25434.16</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>183.83</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24545.16</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24584.98</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24990.2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25395.41</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25617.92</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25840.44</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26428.35</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5308,13 +5305,13 @@
         <v>25434.16</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>25575.01</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>270.95</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0107</v>
       </c>
       <c r="H58" t="n">
         <v>183.83</v>
@@ -5340,27 +5337,25 @@
       <c r="O58" t="n">
         <v>26428.35</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5374,7 +5369,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5299,22 +5299,22 @@
         <v>25491.35</v>
       </c>
       <c r="C58" t="n">
-        <v>25617.99</v>
+        <v>25783.16</v>
       </c>
       <c r="D58" t="n">
-        <v>25434.16</v>
+        <v>25423.07</v>
       </c>
       <c r="E58" t="n">
-        <v>25575.01</v>
+        <v>25578.85</v>
       </c>
       <c r="F58" t="n">
-        <v>270.95</v>
+        <v>274.79</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0109</v>
       </c>
       <c r="H58" t="n">
-        <v>183.83</v>
+        <v>360.09</v>
       </c>
       <c r="I58" t="n">
         <v>24545.16</v>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5299,22 +5299,22 @@
         <v>25491.35</v>
       </c>
       <c r="C58" t="n">
-        <v>25783.16</v>
+        <v>25617.99</v>
       </c>
       <c r="D58" t="n">
-        <v>25423.07</v>
+        <v>25434.16</v>
       </c>
       <c r="E58" t="n">
-        <v>25578.85</v>
+        <v>25575.01</v>
       </c>
       <c r="F58" t="n">
-        <v>274.79</v>
+        <v>270.95</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0107</v>
       </c>
       <c r="H58" t="n">
-        <v>360.09</v>
+        <v>183.83</v>
       </c>
       <c r="I58" t="n">
         <v>24545.16</v>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5299,22 +5299,22 @@
         <v>25491.35</v>
       </c>
       <c r="C58" t="n">
-        <v>25617.99</v>
+        <v>25729.05</v>
       </c>
       <c r="D58" t="n">
-        <v>25434.16</v>
+        <v>25365.21</v>
       </c>
       <c r="E58" t="n">
-        <v>25575.01</v>
+        <v>25410.63</v>
       </c>
       <c r="F58" t="n">
-        <v>270.95</v>
+        <v>106.57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0042</v>
       </c>
       <c r="H58" t="n">
-        <v>183.83</v>
+        <v>363.84</v>
       </c>
       <c r="I58" t="n">
         <v>24545.16</v>
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>25729.05</v>
       </c>
       <c r="D58" t="n">
-        <v>25365.21</v>
+        <v>25164.2</v>
       </c>
       <c r="E58" t="n">
-        <v>25410.63</v>
+        <v>25266.53</v>
       </c>
       <c r="F58" t="n">
-        <v>106.57</v>
+        <v>-37.53</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0015</v>
       </c>
       <c r="H58" t="n">
-        <v>363.84</v>
+        <v>564.85</v>
       </c>
       <c r="I58" t="n">
         <v>24545.16</v>
@@ -5346,9 +5346,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5367,11 +5367,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,66 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24232.02</v>
+        <v>24012.04</v>
       </c>
       <c r="C2" t="n">
-        <v>24377.38</v>
+        <v>24046.85</v>
       </c>
       <c r="D2" t="n">
-        <v>23881.98</v>
+        <v>23482.67</v>
       </c>
       <c r="E2" t="n">
-        <v>23902.21</v>
+        <v>23596.98</v>
       </c>
       <c r="F2" t="n">
-        <v>-460.88</v>
+        <v>-305.23</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0128</v>
       </c>
       <c r="H2" t="n">
-        <v>495.4</v>
+        <v>564.1799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23915.41</v>
+        <v>23386.58</v>
       </c>
       <c r="J2" t="n">
-        <v>24124.05</v>
+        <v>23293.08</v>
       </c>
       <c r="K2" t="n">
-        <v>24230.84</v>
+        <v>23654.51</v>
       </c>
       <c r="L2" t="n">
-        <v>24337.62</v>
+        <v>24015.95</v>
       </c>
       <c r="M2" t="n">
-        <v>24495.34</v>
+        <v>24149.91</v>
       </c>
       <c r="N2" t="n">
-        <v>24653.05</v>
+        <v>24283.88</v>
       </c>
       <c r="O2" t="n">
-        <v>24708.91</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>24872.78</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -710,58 +706,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24012.04</v>
+        <v>23771.86</v>
       </c>
       <c r="C3" t="n">
-        <v>24046.85</v>
+        <v>23883.58</v>
       </c>
       <c r="D3" t="n">
-        <v>23482.67</v>
+        <v>23563.37</v>
       </c>
       <c r="E3" t="n">
-        <v>23596.98</v>
+        <v>23698.15</v>
       </c>
       <c r="F3" t="n">
-        <v>-305.23</v>
+        <v>101.17</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0128</v>
+        <v>0.0043</v>
       </c>
       <c r="H3" t="n">
-        <v>564.1799999999999</v>
+        <v>320.21</v>
       </c>
       <c r="I3" t="n">
-        <v>23386.58</v>
+        <v>22918.49</v>
       </c>
       <c r="J3" t="n">
-        <v>23293.08</v>
+        <v>22948.91</v>
       </c>
       <c r="K3" t="n">
-        <v>23654.51</v>
+        <v>23314.89</v>
       </c>
       <c r="L3" t="n">
-        <v>24015.95</v>
+        <v>23680.87</v>
       </c>
       <c r="M3" t="n">
-        <v>24149.91</v>
+        <v>23879.07</v>
       </c>
       <c r="N3" t="n">
-        <v>24283.88</v>
+        <v>24077.27</v>
       </c>
       <c r="O3" t="n">
-        <v>24872.78</v>
+        <v>24611.03</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -790,78 +790,84 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23771.86</v>
+        <v>23785.26</v>
       </c>
       <c r="C4" t="n">
-        <v>23883.58</v>
+        <v>23855.35</v>
       </c>
       <c r="D4" t="n">
-        <v>23563.37</v>
+        <v>23284.67</v>
       </c>
       <c r="E4" t="n">
-        <v>23698.15</v>
+        <v>23639.41</v>
       </c>
       <c r="F4" t="n">
-        <v>101.17</v>
+        <v>-58.74</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0025</v>
       </c>
       <c r="H4" t="n">
-        <v>320.21</v>
+        <v>570.6799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>22918.49</v>
+        <v>23243.16</v>
       </c>
       <c r="J4" t="n">
-        <v>22948.91</v>
+        <v>23365.28</v>
       </c>
       <c r="K4" t="n">
-        <v>23314.89</v>
+        <v>23538.04</v>
       </c>
       <c r="L4" t="n">
-        <v>23680.87</v>
+        <v>23710.81</v>
       </c>
       <c r="M4" t="n">
-        <v>23879.07</v>
+        <v>23858.26</v>
       </c>
       <c r="N4" t="n">
-        <v>24077.27</v>
+        <v>24005.7</v>
       </c>
       <c r="O4" t="n">
-        <v>24611.03</v>
+        <v>24203.79</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -870,79 +876,75 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23785.26</v>
+        <v>23567.49</v>
       </c>
       <c r="C5" t="n">
-        <v>23855.35</v>
+        <v>23756.04</v>
       </c>
       <c r="D5" t="n">
-        <v>23284.67</v>
+        <v>23383.84</v>
       </c>
       <c r="E5" t="n">
-        <v>23639.41</v>
+        <v>23739.47</v>
       </c>
       <c r="F5" t="n">
-        <v>-58.74</v>
+        <v>100.06</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0042</v>
       </c>
       <c r="H5" t="n">
-        <v>570.6799999999999</v>
+        <v>372.2</v>
       </c>
       <c r="I5" t="n">
-        <v>23243.16</v>
+        <v>22713.99</v>
       </c>
       <c r="J5" t="n">
-        <v>23365.28</v>
+        <v>23103.43</v>
       </c>
       <c r="K5" t="n">
-        <v>23538.04</v>
+        <v>23354.07</v>
       </c>
       <c r="L5" t="n">
-        <v>23710.81</v>
+        <v>23604.71</v>
       </c>
       <c r="M5" t="n">
-        <v>23858.26</v>
+        <v>23924.75</v>
       </c>
       <c r="N5" t="n">
-        <v>24005.7</v>
+        <v>24244.79</v>
       </c>
       <c r="O5" t="n">
-        <v>24203.79</v>
+        <v>24426.03</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -956,58 +958,62 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23567.49</v>
+        <v>23835.61</v>
       </c>
       <c r="C6" t="n">
-        <v>23756.04</v>
+        <v>24524.11</v>
       </c>
       <c r="D6" t="n">
-        <v>23383.84</v>
+        <v>23666.81</v>
       </c>
       <c r="E6" t="n">
-        <v>23739.47</v>
+        <v>24378.8</v>
       </c>
       <c r="F6" t="n">
-        <v>100.06</v>
+        <v>639.33</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0269</v>
       </c>
       <c r="H6" t="n">
-        <v>372.2</v>
+        <v>857.3</v>
       </c>
       <c r="I6" t="n">
-        <v>22713.99</v>
+        <v>23011.64</v>
       </c>
       <c r="J6" t="n">
-        <v>23103.43</v>
+        <v>23452.04</v>
       </c>
       <c r="K6" t="n">
-        <v>23354.07</v>
+        <v>23553.37</v>
       </c>
       <c r="L6" t="n">
-        <v>23604.71</v>
+        <v>23654.71</v>
       </c>
       <c r="M6" t="n">
-        <v>23924.75</v>
+        <v>23925.57</v>
       </c>
       <c r="N6" t="n">
-        <v>24244.79</v>
+        <v>24196.44</v>
       </c>
       <c r="O6" t="n">
-        <v>24426.03</v>
+        <v>24128.24</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,76 +1026,78 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C7" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D7" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E7" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F7" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H7" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I7" t="n">
-        <v>23011.64</v>
+        <v>22809.51</v>
       </c>
       <c r="J7" t="n">
-        <v>23452.04</v>
+        <v>23663.17</v>
       </c>
       <c r="K7" t="n">
-        <v>23553.37</v>
+        <v>23950.15</v>
       </c>
       <c r="L7" t="n">
-        <v>23654.71</v>
+        <v>24237.13</v>
       </c>
       <c r="M7" t="n">
-        <v>23925.57</v>
+        <v>24807.45</v>
       </c>
       <c r="N7" t="n">
-        <v>24196.44</v>
+        <v>25377.77</v>
       </c>
       <c r="O7" t="n">
-        <v>24128.24</v>
+        <v>25381.41</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,91 +1110,93 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C8" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D8" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E8" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F8" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H8" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I8" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J8" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K8" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L8" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M8" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N8" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O8" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1198,243 +1208,243 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C9" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D9" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E9" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F9" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H9" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I9" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J9" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K9" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L9" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M9" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N9" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O9" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C10" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D10" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E10" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F10" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H10" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I10" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J10" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K10" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L10" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M10" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N10" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O10" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C11" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D11" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E11" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F11" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H11" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I11" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J11" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K11" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L11" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M11" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N11" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O11" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1445,8 +1455,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1454,7 +1466,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1468,306 +1480,304 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C12" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D12" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E12" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F12" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H12" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I12" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J12" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K12" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L12" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M12" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N12" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O12" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C13" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D13" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E13" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F13" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H13" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I13" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J13" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K13" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L13" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M13" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N13" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O13" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C14" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D14" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E14" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F14" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H14" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I14" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J14" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K14" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L14" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M14" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N14" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O14" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C15" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D15" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E15" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F15" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H15" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J15" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K15" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L15" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M15" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N15" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O15" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1775,8 +1785,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1785,75 +1797,69 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C16" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D16" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E16" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F16" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H16" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I16" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J16" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K16" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L16" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M16" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N16" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O16" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,10 +1867,8 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
@@ -1882,7 +1886,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1892,50 +1896,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C17" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D17" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E17" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F17" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H17" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I17" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J17" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K17" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L17" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M17" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N17" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O17" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1943,18 +1947,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1962,60 +1966,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C18" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D18" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E18" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F18" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H18" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I18" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J18" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K18" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L18" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M18" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N18" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O18" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,10 +2031,8 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
@@ -2042,64 +2048,60 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C19" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D19" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E19" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F19" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I19" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J19" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K19" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L19" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M19" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N19" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O19" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,24 +2109,32 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2134,50 +2144,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C20" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D20" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E20" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F20" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H20" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I20" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J20" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K20" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L20" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M20" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N20" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O20" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,32 +2195,30 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2220,50 +2228,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C21" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D21" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E21" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F21" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H21" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I21" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J21" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K21" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L21" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M21" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N21" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O21" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,25 +2284,19 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2304,63 +2306,69 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C22" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D22" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E22" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F22" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H22" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J22" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K22" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L22" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M22" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N22" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O22" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>25817.05</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2374,7 +2382,7 @@
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2382,66 +2390,64 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C23" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D23" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E23" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F23" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H23" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I23" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J23" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K23" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L23" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M23" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N23" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O23" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2456,7 +2462,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2466,132 +2472,134 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C24" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D24" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E24" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F24" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H24" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I24" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J24" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K24" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L24" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M24" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N24" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O24" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C25" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D25" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E25" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F25" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H25" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I25" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J25" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K25" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L25" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M25" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N25" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O25" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2618,7 +2626,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2632,50 +2640,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C26" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D26" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E26" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F26" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H26" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I26" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J26" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K26" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L26" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M26" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N26" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O26" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2688,12 +2696,12 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2702,7 +2710,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2716,50 +2724,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C27" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D27" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E27" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F27" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H27" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I27" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J27" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K27" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L27" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M27" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N27" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O27" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,18 +2775,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2786,7 +2794,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2800,65 +2808,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C28" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D28" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E28" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F28" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H28" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I28" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J28" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K28" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L28" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M28" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N28" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O28" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2870,83 +2882,73 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C29" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D29" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E29" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F29" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H29" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I29" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J29" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K29" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L29" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M29" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N29" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O29" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26452.34</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2958,7 +2960,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2968,63 +2970,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C30" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D30" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E30" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F30" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H30" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I30" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J30" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K30" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L30" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M30" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N30" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O30" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3036,7 +3042,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3046,79 +3052,77 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C31" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D31" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E31" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H31" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I31" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J31" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K31" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L31" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M31" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N31" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O31" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3128,50 +3132,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C32" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D32" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E32" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F32" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H32" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I32" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J32" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K32" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L32" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M32" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N32" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O32" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,14 +3186,14 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3198,60 +3202,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C33" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D33" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E33" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F33" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H33" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I33" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J33" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K33" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L33" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M33" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N33" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O33" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3278,7 +3286,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3292,50 +3300,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C34" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D34" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E34" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F34" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H34" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I34" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J34" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K34" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L34" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M34" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N34" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O34" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,7 +3370,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3376,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C35" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D35" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E35" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F35" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H35" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J35" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K35" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L35" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M35" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N35" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O35" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3427,83 +3435,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C36" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D36" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E36" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F36" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H36" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I36" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J36" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K36" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L36" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M36" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N36" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O36" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3513,12 +3521,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3530,7 +3538,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3544,50 +3552,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C37" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D37" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E37" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F37" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H37" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I37" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J37" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K37" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L37" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M37" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N37" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O37" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3595,83 +3603,87 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C38" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D38" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E38" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F38" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H38" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J38" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K38" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L38" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M38" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N38" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O38" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3679,87 +3691,79 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C39" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D39" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E39" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F39" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H39" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I39" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J39" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K39" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L39" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M39" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N39" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O39" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3767,79 +3771,87 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C40" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D40" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E40" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F40" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I40" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J40" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K40" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L40" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M40" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N40" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O40" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,77 +3869,69 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C41" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D41" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E41" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F41" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H41" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I41" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J41" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K41" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L41" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M41" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N41" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O41" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3935,17 +3939,19 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3954,63 +3960,69 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C42" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D42" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E42" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H42" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J42" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K42" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L42" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M42" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N42" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O42" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
@@ -4025,10 +4037,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4036,7 +4046,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4050,302 +4060,300 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C43" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D43" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E43" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F43" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H43" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I43" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J43" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K43" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L43" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M43" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N43" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O43" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C44" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D44" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E44" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F44" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H44" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I44" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J44" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K44" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L44" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M44" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N44" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O44" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C45" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D45" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E45" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F45" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H45" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I45" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J45" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K45" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L45" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M45" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N45" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O45" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C46" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D46" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E46" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F46" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H46" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I46" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J46" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K46" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L46" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M46" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N46" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O46" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4353,83 +4361,83 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C47" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D47" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E47" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F47" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H47" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I47" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J47" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K47" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L47" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M47" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N47" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O47" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4456,64 +4464,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C48" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D48" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E48" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F48" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H48" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I48" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J48" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K48" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L48" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M48" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N48" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O48" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4521,83 +4529,79 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C49" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D49" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E49" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F49" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H49" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I49" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J49" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K49" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L49" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M49" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N49" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O49" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,16 +4619,20 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4634,50 +4642,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C50" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D50" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E50" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F50" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H50" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J50" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K50" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L50" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M50" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N50" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O50" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4703,12 +4711,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4718,50 +4724,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C51" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D51" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E51" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F51" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H51" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I51" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J51" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K51" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L51" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M51" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N51" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O51" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,18 +4785,16 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4800,249 +4804,251 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C52" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D52" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E52" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F52" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H52" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I52" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J52" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K52" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L52" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M52" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N52" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O52" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+        <v>26901.43</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C53" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D53" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E53" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F53" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H53" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I53" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J53" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K53" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L53" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M53" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N53" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O53" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C54" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D54" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E54" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F54" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H54" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I54" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J54" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K54" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L54" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M54" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N54" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O54" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr"/>
@@ -5050,64 +5056,62 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C55" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D55" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E55" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F55" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H55" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I55" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J55" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K55" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L55" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M55" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N55" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O55" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5122,7 +5126,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5132,50 +5136,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C56" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D56" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E56" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F56" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H56" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I56" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J56" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K56" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L56" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M56" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N56" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O56" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5202,7 +5206,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5212,50 +5216,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25498.74</v>
+        <v>25491.35</v>
       </c>
       <c r="C57" t="n">
-        <v>25800.62</v>
+        <v>25783.16</v>
       </c>
       <c r="D57" t="n">
-        <v>25172.89</v>
+        <v>25164.2</v>
       </c>
       <c r="E57" t="n">
-        <v>25304.06</v>
+        <v>25408.64</v>
       </c>
       <c r="F57" t="n">
-        <v>-264.5</v>
+        <v>104.58</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0041</v>
       </c>
       <c r="H57" t="n">
-        <v>627.73</v>
+        <v>618.96</v>
       </c>
       <c r="I57" t="n">
-        <v>24652.31</v>
+        <v>24545.16</v>
       </c>
       <c r="J57" t="n">
-        <v>24786.22</v>
+        <v>24584.98</v>
       </c>
       <c r="K57" t="n">
-        <v>25214.14</v>
+        <v>24990.2</v>
       </c>
       <c r="L57" t="n">
-        <v>25642.07</v>
+        <v>25395.41</v>
       </c>
       <c r="M57" t="n">
-        <v>25922.98</v>
+        <v>25617.92</v>
       </c>
       <c r="N57" t="n">
-        <v>26203.9</v>
+        <v>25840.44</v>
       </c>
       <c r="O57" t="n">
-        <v>26778.83</v>
+        <v>26428.35</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5263,18 +5267,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5282,92 +5286,16 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25491.35</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25729.05</v>
-      </c>
-      <c r="D58" t="n">
-        <v>25164.2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>25266.53</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-37.53</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="H58" t="n">
-        <v>564.85</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24545.16</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24584.98</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24990.2</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25395.41</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25617.92</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25840.44</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26428.35</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5297,6 +5300,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25443.98</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25575.66</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25360.32</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>215.34</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24545.24</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24757.16</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25099.16</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25441.16</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25718.12</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25995.08</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26402.12</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,35 +659,37 @@
         <v>564.1799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23386.58</v>
+        <v>23500.85</v>
       </c>
       <c r="J2" t="n">
-        <v>23293.08</v>
+        <v>23435.92</v>
       </c>
       <c r="K2" t="n">
-        <v>23654.51</v>
+        <v>23711.65</v>
       </c>
       <c r="L2" t="n">
-        <v>24015.95</v>
+        <v>23987.38</v>
       </c>
       <c r="M2" t="n">
-        <v>24149.91</v>
+        <v>24092.78</v>
       </c>
       <c r="N2" t="n">
-        <v>24283.88</v>
+        <v>24198.17</v>
       </c>
       <c r="O2" t="n">
-        <v>24872.78</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>24644.24</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -5310,22 +5309,22 @@
         <v>25443.98</v>
       </c>
       <c r="C58" t="n">
-        <v>25575.66</v>
+        <v>25617.31</v>
       </c>
       <c r="D58" t="n">
-        <v>25360.32</v>
+        <v>25338.03</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>25399.21</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-9.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>215.34</v>
+        <v>279.28</v>
       </c>
       <c r="I58" t="n">
         <v>24545.24</v>
@@ -5348,10 +5347,8 @@
       <c r="O58" t="n">
         <v>26402.12</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5359,9 +5356,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,33 +659,35 @@
         <v>564.1799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23500.85</v>
+        <v>23557.43</v>
       </c>
       <c r="J2" t="n">
-        <v>23435.92</v>
+        <v>23506.64</v>
       </c>
       <c r="K2" t="n">
-        <v>23711.65</v>
+        <v>23739.94</v>
       </c>
       <c r="L2" t="n">
-        <v>23987.38</v>
+        <v>23973.23</v>
       </c>
       <c r="M2" t="n">
-        <v>24092.78</v>
+        <v>24064.49</v>
       </c>
       <c r="N2" t="n">
-        <v>24198.17</v>
+        <v>24155.74</v>
       </c>
       <c r="O2" t="n">
-        <v>24644.24</v>
+        <v>24531.08</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5312,19 +5314,19 @@
         <v>25617.31</v>
       </c>
       <c r="D58" t="n">
-        <v>25338.03</v>
+        <v>25190.33</v>
       </c>
       <c r="E58" t="n">
-        <v>25399.21</v>
+        <v>25199.19</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.43</v>
+        <v>-209.45</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>279.28</v>
+        <v>426.98</v>
       </c>
       <c r="I58" t="n">
         <v>24545.24</v>
@@ -5353,12 +5355,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5314,19 +5314,19 @@
         <v>25617.31</v>
       </c>
       <c r="D58" t="n">
-        <v>25190.33</v>
+        <v>24831.6</v>
       </c>
       <c r="E58" t="n">
-        <v>25199.19</v>
+        <v>24939.35</v>
       </c>
       <c r="F58" t="n">
-        <v>-209.45</v>
+        <v>-469.29</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="H58" t="n">
-        <v>426.98</v>
+        <v>785.71</v>
       </c>
       <c r="I58" t="n">
         <v>24545.24</v>
@@ -5379,11 +5379,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,74 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24012.04</v>
+        <v>23771.86</v>
       </c>
       <c r="C2" t="n">
-        <v>24046.85</v>
+        <v>23883.58</v>
       </c>
       <c r="D2" t="n">
-        <v>23482.67</v>
+        <v>23563.37</v>
       </c>
       <c r="E2" t="n">
-        <v>23596.98</v>
+        <v>23698.15</v>
       </c>
       <c r="F2" t="n">
-        <v>-305.23</v>
+        <v>101.17</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0128</v>
+        <v>0.0043</v>
       </c>
       <c r="H2" t="n">
-        <v>564.1799999999999</v>
+        <v>320.21</v>
       </c>
       <c r="I2" t="n">
-        <v>23557.43</v>
+        <v>22918.49</v>
       </c>
       <c r="J2" t="n">
-        <v>23506.64</v>
+        <v>22948.91</v>
       </c>
       <c r="K2" t="n">
-        <v>23739.94</v>
+        <v>23314.89</v>
       </c>
       <c r="L2" t="n">
-        <v>23973.23</v>
+        <v>23680.87</v>
       </c>
       <c r="M2" t="n">
-        <v>24064.49</v>
+        <v>23879.07</v>
       </c>
       <c r="N2" t="n">
-        <v>24155.74</v>
+        <v>24077.27</v>
       </c>
       <c r="O2" t="n">
-        <v>24531.08</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>24611.03</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -715,76 +711,78 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23771.86</v>
+        <v>23785.26</v>
       </c>
       <c r="C3" t="n">
-        <v>23883.58</v>
+        <v>23855.35</v>
       </c>
       <c r="D3" t="n">
-        <v>23563.37</v>
+        <v>23284.67</v>
       </c>
       <c r="E3" t="n">
-        <v>23698.15</v>
+        <v>23639.41</v>
       </c>
       <c r="F3" t="n">
-        <v>101.17</v>
+        <v>-58.74</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0025</v>
       </c>
       <c r="H3" t="n">
-        <v>320.21</v>
+        <v>570.6799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>22918.49</v>
+        <v>23243.16</v>
       </c>
       <c r="J3" t="n">
-        <v>22948.91</v>
+        <v>23365.28</v>
       </c>
       <c r="K3" t="n">
-        <v>23314.89</v>
+        <v>23538.04</v>
       </c>
       <c r="L3" t="n">
-        <v>23680.87</v>
+        <v>23710.81</v>
       </c>
       <c r="M3" t="n">
-        <v>23879.07</v>
+        <v>23858.26</v>
       </c>
       <c r="N3" t="n">
-        <v>24077.27</v>
+        <v>24005.7</v>
       </c>
       <c r="O3" t="n">
-        <v>24611.03</v>
+        <v>24203.79</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -799,74 +797,70 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23785.26</v>
+        <v>23567.49</v>
       </c>
       <c r="C4" t="n">
-        <v>23855.35</v>
+        <v>23756.04</v>
       </c>
       <c r="D4" t="n">
-        <v>23284.67</v>
+        <v>23383.84</v>
       </c>
       <c r="E4" t="n">
-        <v>23639.41</v>
+        <v>23739.47</v>
       </c>
       <c r="F4" t="n">
-        <v>-58.74</v>
+        <v>100.06</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0042</v>
       </c>
       <c r="H4" t="n">
-        <v>570.6799999999999</v>
+        <v>372.2</v>
       </c>
       <c r="I4" t="n">
-        <v>23243.16</v>
+        <v>22713.99</v>
       </c>
       <c r="J4" t="n">
-        <v>23365.28</v>
+        <v>23103.43</v>
       </c>
       <c r="K4" t="n">
-        <v>23538.04</v>
+        <v>23354.07</v>
       </c>
       <c r="L4" t="n">
-        <v>23710.81</v>
+        <v>23604.71</v>
       </c>
       <c r="M4" t="n">
-        <v>23858.26</v>
+        <v>23924.75</v>
       </c>
       <c r="N4" t="n">
-        <v>24005.7</v>
+        <v>24244.79</v>
       </c>
       <c r="O4" t="n">
-        <v>24203.79</v>
+        <v>24426.03</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -885,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23567.49</v>
+        <v>23835.61</v>
       </c>
       <c r="C5" t="n">
-        <v>23756.04</v>
+        <v>24524.11</v>
       </c>
       <c r="D5" t="n">
-        <v>23383.84</v>
+        <v>23666.81</v>
       </c>
       <c r="E5" t="n">
-        <v>23739.47</v>
+        <v>24378.8</v>
       </c>
       <c r="F5" t="n">
-        <v>100.06</v>
+        <v>639.33</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0269</v>
       </c>
       <c r="H5" t="n">
-        <v>372.2</v>
+        <v>857.3</v>
       </c>
       <c r="I5" t="n">
-        <v>22713.99</v>
+        <v>23011.64</v>
       </c>
       <c r="J5" t="n">
-        <v>23103.43</v>
+        <v>23452.04</v>
       </c>
       <c r="K5" t="n">
-        <v>23354.07</v>
+        <v>23553.37</v>
       </c>
       <c r="L5" t="n">
-        <v>23604.71</v>
+        <v>23654.71</v>
       </c>
       <c r="M5" t="n">
-        <v>23924.75</v>
+        <v>23925.57</v>
       </c>
       <c r="N5" t="n">
-        <v>24244.79</v>
+        <v>24196.44</v>
       </c>
       <c r="O5" t="n">
-        <v>24426.03</v>
+        <v>24128.24</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,78 +940,80 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C6" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D6" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E6" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F6" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H6" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I6" t="n">
-        <v>23011.64</v>
+        <v>22809.51</v>
       </c>
       <c r="J6" t="n">
-        <v>23452.04</v>
+        <v>23663.17</v>
       </c>
       <c r="K6" t="n">
-        <v>23553.37</v>
+        <v>23950.15</v>
       </c>
       <c r="L6" t="n">
-        <v>23654.71</v>
+        <v>24237.13</v>
       </c>
       <c r="M6" t="n">
-        <v>23925.57</v>
+        <v>24807.45</v>
       </c>
       <c r="N6" t="n">
-        <v>24196.44</v>
+        <v>25377.77</v>
       </c>
       <c r="O6" t="n">
-        <v>24128.24</v>
+        <v>25381.41</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,93 +1024,95 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C7" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D7" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E7" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F7" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H7" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I7" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J7" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K7" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L7" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M7" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N7" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O7" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1133,79 +1131,77 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C8" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D8" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E8" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F8" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H8" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I8" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J8" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K8" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L8" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M8" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N8" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O8" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1219,76 +1215,78 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C9" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D9" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E9" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F9" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H9" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I9" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J9" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K9" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L9" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M9" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N9" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O9" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1303,78 +1301,80 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C10" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D10" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E10" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F10" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H10" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I10" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J10" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K10" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L10" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M10" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N10" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O10" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1396,77 +1396,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C11" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D11" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E11" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F11" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H11" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I11" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J11" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K11" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L11" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M11" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N11" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O11" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1475,83 +1473,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C12" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D12" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E12" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F12" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H12" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I12" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J12" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K12" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L12" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M12" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N12" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O12" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1561,80 +1555,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C13" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D13" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E13" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F13" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H13" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I13" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J13" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K13" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L13" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M13" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N13" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O13" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1645,57 +1643,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C14" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D14" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E14" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F14" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H14" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J14" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K14" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L14" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M14" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N14" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O14" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1703,24 +1701,24 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1729,59 +1727,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C15" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D15" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E15" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F15" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H15" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I15" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J15" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K15" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L15" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M15" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N15" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O15" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1789,12 +1783,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1820,50 +1812,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C16" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D16" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E16" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F16" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H16" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I16" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J16" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K16" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L16" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M16" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N16" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O16" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1871,18 +1863,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1895,55 +1887,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C17" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D17" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E17" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F17" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H17" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I17" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J17" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K17" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L17" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M17" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N17" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O17" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1951,12 +1947,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1975,59 +1969,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C18" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D18" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E18" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F18" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I18" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J18" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K18" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L18" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M18" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N18" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O18" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2035,22 +2025,30 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2062,50 +2060,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C19" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D19" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E19" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F19" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H19" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I19" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J19" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K19" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L19" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M19" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N19" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O19" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,29 +2111,27 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -2148,50 +2144,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C20" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D20" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E20" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F20" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H20" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I20" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J20" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K20" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L20" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M20" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N20" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O20" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2202,25 +2198,19 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2232,63 +2222,69 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C21" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D21" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E21" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F21" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H21" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J21" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K21" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L21" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M21" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N21" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O21" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>25817.05</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2300,9 +2296,9 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2310,67 +2306,65 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C22" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D22" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E22" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F22" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H22" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I22" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J22" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K22" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L22" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M22" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N22" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O22" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2394,72 +2388,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C23" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D23" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E23" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F23" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H23" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I23" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J23" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K23" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L23" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M23" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N23" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O23" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2471,55 +2463,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C24" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D24" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E24" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F24" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H24" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I24" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J24" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K24" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L24" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M24" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N24" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O24" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,7 +2526,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2560,50 +2556,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C25" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D25" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E25" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F25" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H25" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I25" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J25" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K25" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L25" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M25" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N25" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O25" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,14 +2610,14 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2644,50 +2640,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C26" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D26" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E26" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F26" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H26" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I26" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J26" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K26" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L26" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M26" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N26" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O26" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,18 +2691,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2728,56 +2724,60 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C27" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D27" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E27" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F27" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H27" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I27" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J27" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K27" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L27" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M27" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N27" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O27" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2803,78 +2803,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C28" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D28" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E28" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F28" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H28" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I28" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J28" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K28" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L28" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M28" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N28" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O28" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26452.34</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2896,63 +2886,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C29" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D29" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E29" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F29" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H29" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I29" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J29" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K29" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L29" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M29" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N29" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O29" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2974,71 +2968,69 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C30" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D30" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E30" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H30" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I30" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J30" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K30" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L30" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M30" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N30" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O30" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3056,50 +3048,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C31" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D31" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E31" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F31" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H31" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I31" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J31" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K31" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L31" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M31" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N31" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O31" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,12 +3104,12 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3131,55 +3123,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C32" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D32" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E32" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F32" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H32" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I32" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J32" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K32" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L32" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M32" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N32" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O32" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3190,7 +3186,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3220,50 +3216,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C33" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D33" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E33" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F33" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H33" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I33" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J33" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K33" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L33" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M33" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N33" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O33" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,7 +3270,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3304,50 +3300,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C34" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D34" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E34" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F34" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H34" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J34" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K34" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L34" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M34" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N34" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O34" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,18 +3351,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3381,57 +3377,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C35" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D35" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E35" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F35" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H35" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I35" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J35" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K35" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L35" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M35" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N35" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O35" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3441,12 +3437,12 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3472,50 +3468,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C36" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D36" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E36" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F36" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H36" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I36" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J36" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K36" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L36" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M36" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N36" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O36" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3523,24 +3519,28 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
@@ -3549,57 +3549,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C37" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D37" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E37" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F37" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H37" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J37" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K37" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L37" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M37" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N37" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O37" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,87 +3607,79 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C38" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D38" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E38" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F38" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H38" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I38" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J38" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K38" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L38" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M38" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N38" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O38" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,79 +3687,87 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C39" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D39" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E39" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F39" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I39" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J39" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K39" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L39" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M39" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N39" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O39" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3778,84 +3778,76 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C40" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D40" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E40" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F40" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H40" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I40" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J40" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K40" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L40" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M40" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N40" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O40" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3863,17 +3855,19 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3887,58 +3881,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C41" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D41" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E41" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H41" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J41" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K41" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L41" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M41" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N41" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O41" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
@@ -3948,15 +3948,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3978,72 +3976,70 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C42" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D42" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E42" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F42" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H42" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I42" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J42" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K42" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L42" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M42" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N42" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O42" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4055,78 +4051,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C43" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D43" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E43" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F43" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H43" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I43" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J43" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K43" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L43" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M43" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N43" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O43" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4139,141 +4133,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C44" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D44" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E44" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F44" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H44" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I44" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J44" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K44" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L44" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M44" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N44" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O44" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C45" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D45" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E45" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F45" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H45" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I45" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J45" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K45" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L45" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M45" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N45" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O45" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4281,83 +4277,83 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C46" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D46" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E46" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F46" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H46" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I46" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J46" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K46" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L46" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M46" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N46" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O46" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4370,7 +4366,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4391,57 +4387,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C47" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D47" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E47" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F47" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H47" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I47" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J47" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K47" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L47" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M47" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N47" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O47" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4449,19 +4445,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4473,59 +4469,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C48" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D48" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E48" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F48" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H48" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I48" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J48" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K48" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L48" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M48" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N48" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O48" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4536,21 +4528,25 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4562,50 +4558,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C49" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D49" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E49" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F49" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H49" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J49" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K49" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L49" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M49" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N49" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O49" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4616,7 +4612,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4631,10 +4627,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4646,50 +4640,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C50" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D50" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E50" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F50" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H50" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I50" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J50" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K50" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L50" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M50" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N50" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O50" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4700,20 +4694,18 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4728,69 +4720,73 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C51" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D51" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E51" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F51" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H51" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I51" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J51" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K51" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L51" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M51" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N51" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O51" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>26901.43</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4803,82 +4799,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C52" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D52" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E52" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F52" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H52" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I52" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J52" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K52" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L52" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M52" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N52" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O52" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4887,90 +4885,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C53" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D53" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E53" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F53" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H53" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I53" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J53" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K53" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L53" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M53" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N53" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O53" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr"/>
@@ -4978,65 +4972,63 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C54" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D54" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E54" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F54" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H54" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I54" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J54" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K54" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L54" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M54" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N54" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O54" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5060,50 +5052,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C55" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D55" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E55" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F55" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H55" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I55" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J55" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K55" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L55" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M55" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N55" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O55" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5116,7 +5108,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5140,50 +5132,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25498.74</v>
+        <v>25491.35</v>
       </c>
       <c r="C56" t="n">
-        <v>25800.62</v>
+        <v>25783.16</v>
       </c>
       <c r="D56" t="n">
-        <v>25172.89</v>
+        <v>25164.2</v>
       </c>
       <c r="E56" t="n">
-        <v>25304.06</v>
+        <v>25408.64</v>
       </c>
       <c r="F56" t="n">
-        <v>-264.5</v>
+        <v>104.58</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0041</v>
       </c>
       <c r="H56" t="n">
-        <v>627.73</v>
+        <v>618.96</v>
       </c>
       <c r="I56" t="n">
-        <v>24652.31</v>
+        <v>24545.16</v>
       </c>
       <c r="J56" t="n">
-        <v>24786.22</v>
+        <v>24584.98</v>
       </c>
       <c r="K56" t="n">
-        <v>25214.14</v>
+        <v>24990.2</v>
       </c>
       <c r="L56" t="n">
-        <v>25642.07</v>
+        <v>25395.41</v>
       </c>
       <c r="M56" t="n">
-        <v>25922.98</v>
+        <v>25617.92</v>
       </c>
       <c r="N56" t="n">
-        <v>26203.9</v>
+        <v>25840.44</v>
       </c>
       <c r="O56" t="n">
-        <v>26778.83</v>
+        <v>26428.35</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5191,18 +5183,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5215,55 +5207,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25491.35</v>
+        <v>25443.98</v>
       </c>
       <c r="C57" t="n">
-        <v>25783.16</v>
+        <v>25617.31</v>
       </c>
       <c r="D57" t="n">
-        <v>25164.2</v>
+        <v>24831.6</v>
       </c>
       <c r="E57" t="n">
-        <v>25408.64</v>
+        <v>25231.2</v>
       </c>
       <c r="F57" t="n">
-        <v>104.58</v>
+        <v>-177.44</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.007</v>
       </c>
       <c r="H57" t="n">
-        <v>618.96</v>
+        <v>785.71</v>
       </c>
       <c r="I57" t="n">
-        <v>24545.16</v>
+        <v>24545.24</v>
       </c>
       <c r="J57" t="n">
-        <v>24584.98</v>
+        <v>24757.16</v>
       </c>
       <c r="K57" t="n">
-        <v>24990.2</v>
+        <v>25099.16</v>
       </c>
       <c r="L57" t="n">
-        <v>25395.41</v>
+        <v>25441.16</v>
       </c>
       <c r="M57" t="n">
-        <v>25617.92</v>
+        <v>25718.12</v>
       </c>
       <c r="N57" t="n">
-        <v>25840.44</v>
+        <v>25995.08</v>
       </c>
       <c r="O57" t="n">
-        <v>26428.35</v>
+        <v>26402.12</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5271,18 +5267,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5295,91 +5291,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25443.98</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25617.31</v>
-      </c>
-      <c r="D58" t="n">
-        <v>24831.6</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24939.35</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-469.29</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0185</v>
-      </c>
-      <c r="H58" t="n">
-        <v>785.71</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24545.24</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24757.16</v>
-      </c>
-      <c r="K58" t="n">
-        <v>25099.16</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25441.16</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25718.12</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25995.08</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26402.12</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5293,6 +5296,90 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25251.39</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25324.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25143.26</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>181.44</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24045.89</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24448.86</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24838.34</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25227.83</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25624.05</v>
+      </c>
+      <c r="N58" t="n">
+        <v>26020.28</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26403.02</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>320.21</v>
       </c>
       <c r="I2" t="n">
-        <v>22918.49</v>
+        <v>23159.54</v>
       </c>
       <c r="J2" t="n">
-        <v>22948.91</v>
+        <v>23207.45</v>
       </c>
       <c r="K2" t="n">
-        <v>23314.89</v>
+        <v>23423.2</v>
       </c>
       <c r="L2" t="n">
-        <v>23680.87</v>
+        <v>23638.94</v>
       </c>
       <c r="M2" t="n">
-        <v>23879.07</v>
+        <v>23770.77</v>
       </c>
       <c r="N2" t="n">
-        <v>24077.27</v>
+        <v>23902.59</v>
       </c>
       <c r="O2" t="n">
-        <v>24611.03</v>
+        <v>24202.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -712,11 +709,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5306,22 +5299,22 @@
         <v>25251.39</v>
       </c>
       <c r="C58" t="n">
-        <v>25324.7</v>
+        <v>25522.09</v>
       </c>
       <c r="D58" t="n">
         <v>25143.26</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>25449.19</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>217.99</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0086</v>
       </c>
       <c r="H58" t="n">
-        <v>181.44</v>
+        <v>378.83</v>
       </c>
       <c r="I58" t="n">
         <v>24045.89</v>
@@ -5344,25 +5337,25 @@
       <c r="O58" t="n">
         <v>26403.02</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5376,7 +5369,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>320.21</v>
       </c>
       <c r="I2" t="n">
-        <v>23159.54</v>
+        <v>23238.72</v>
       </c>
       <c r="J2" t="n">
-        <v>23207.45</v>
+        <v>23237.15</v>
       </c>
       <c r="K2" t="n">
-        <v>23423.2</v>
+        <v>23442.99</v>
       </c>
       <c r="L2" t="n">
-        <v>23638.94</v>
+        <v>23648.83</v>
       </c>
       <c r="M2" t="n">
-        <v>23770.77</v>
+        <v>23750.97</v>
       </c>
       <c r="N2" t="n">
-        <v>23902.59</v>
+        <v>23853.11</v>
       </c>
       <c r="O2" t="n">
-        <v>24202.25</v>
+        <v>24162.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,8 +698,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5302,19 +5304,19 @@
         <v>25522.09</v>
       </c>
       <c r="D58" t="n">
-        <v>25143.26</v>
+        <v>25038.51</v>
       </c>
       <c r="E58" t="n">
-        <v>25449.19</v>
+        <v>25104.36</v>
       </c>
       <c r="F58" t="n">
-        <v>217.99</v>
+        <v>-126.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.005</v>
       </c>
       <c r="H58" t="n">
-        <v>378.83</v>
+        <v>483.58</v>
       </c>
       <c r="I58" t="n">
         <v>24045.89</v>
@@ -5346,15 +5348,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5304,19 +5304,19 @@
         <v>25522.09</v>
       </c>
       <c r="D58" t="n">
-        <v>25038.51</v>
+        <v>24792.79</v>
       </c>
       <c r="E58" t="n">
-        <v>25104.36</v>
+        <v>24806.97</v>
       </c>
       <c r="F58" t="n">
-        <v>-126.84</v>
+        <v>-424.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0168</v>
       </c>
       <c r="H58" t="n">
-        <v>483.58</v>
+        <v>729.3</v>
       </c>
       <c r="I58" t="n">
         <v>24045.89</v>
@@ -5345,12 +5345,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5367,11 +5369,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,74 +634,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23771.86</v>
+        <v>23785.26</v>
       </c>
       <c r="C2" t="n">
-        <v>23883.58</v>
+        <v>23855.35</v>
       </c>
       <c r="D2" t="n">
-        <v>23563.37</v>
+        <v>23284.67</v>
       </c>
       <c r="E2" t="n">
-        <v>23698.15</v>
+        <v>23639.41</v>
       </c>
       <c r="F2" t="n">
-        <v>101.17</v>
+        <v>-58.74</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0043</v>
+        <v>-0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>320.21</v>
+        <v>570.6799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23238.72</v>
+        <v>23243.16</v>
       </c>
       <c r="J2" t="n">
-        <v>23237.15</v>
+        <v>23365.28</v>
       </c>
       <c r="K2" t="n">
-        <v>23442.99</v>
+        <v>23538.04</v>
       </c>
       <c r="L2" t="n">
-        <v>23648.83</v>
+        <v>23710.81</v>
       </c>
       <c r="M2" t="n">
-        <v>23750.97</v>
+        <v>23858.26</v>
       </c>
       <c r="N2" t="n">
-        <v>23853.11</v>
+        <v>24005.7</v>
       </c>
       <c r="O2" t="n">
-        <v>24162.66</v>
+        <v>24203.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,72 +711,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23785.26</v>
+        <v>23567.49</v>
       </c>
       <c r="C3" t="n">
-        <v>23855.35</v>
+        <v>23756.04</v>
       </c>
       <c r="D3" t="n">
-        <v>23284.67</v>
+        <v>23383.84</v>
       </c>
       <c r="E3" t="n">
-        <v>23639.41</v>
+        <v>23739.47</v>
       </c>
       <c r="F3" t="n">
-        <v>-58.74</v>
+        <v>100.06</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0042</v>
       </c>
       <c r="H3" t="n">
-        <v>570.6799999999999</v>
+        <v>372.2</v>
       </c>
       <c r="I3" t="n">
-        <v>23243.16</v>
+        <v>22713.99</v>
       </c>
       <c r="J3" t="n">
-        <v>23365.28</v>
+        <v>23103.43</v>
       </c>
       <c r="K3" t="n">
-        <v>23538.04</v>
+        <v>23354.07</v>
       </c>
       <c r="L3" t="n">
-        <v>23710.81</v>
+        <v>23604.71</v>
       </c>
       <c r="M3" t="n">
-        <v>23858.26</v>
+        <v>23924.75</v>
       </c>
       <c r="N3" t="n">
-        <v>24005.7</v>
+        <v>24244.79</v>
       </c>
       <c r="O3" t="n">
-        <v>24203.79</v>
+        <v>24426.03</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -795,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23567.49</v>
+        <v>23835.61</v>
       </c>
       <c r="C4" t="n">
-        <v>23756.04</v>
+        <v>24524.11</v>
       </c>
       <c r="D4" t="n">
-        <v>23383.84</v>
+        <v>23666.81</v>
       </c>
       <c r="E4" t="n">
-        <v>23739.47</v>
+        <v>24378.8</v>
       </c>
       <c r="F4" t="n">
-        <v>100.06</v>
+        <v>639.33</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0269</v>
       </c>
       <c r="H4" t="n">
-        <v>372.2</v>
+        <v>857.3</v>
       </c>
       <c r="I4" t="n">
-        <v>22713.99</v>
+        <v>23011.64</v>
       </c>
       <c r="J4" t="n">
-        <v>23103.43</v>
+        <v>23452.04</v>
       </c>
       <c r="K4" t="n">
-        <v>23354.07</v>
+        <v>23553.37</v>
       </c>
       <c r="L4" t="n">
-        <v>23604.71</v>
+        <v>23654.71</v>
       </c>
       <c r="M4" t="n">
-        <v>23924.75</v>
+        <v>23925.57</v>
       </c>
       <c r="N4" t="n">
-        <v>24244.79</v>
+        <v>24196.44</v>
       </c>
       <c r="O4" t="n">
-        <v>24426.03</v>
+        <v>24128.24</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,78 +856,80 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C5" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D5" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E5" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F5" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H5" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I5" t="n">
-        <v>23011.64</v>
+        <v>22809.51</v>
       </c>
       <c r="J5" t="n">
-        <v>23452.04</v>
+        <v>23663.17</v>
       </c>
       <c r="K5" t="n">
-        <v>23553.37</v>
+        <v>23950.15</v>
       </c>
       <c r="L5" t="n">
-        <v>23654.71</v>
+        <v>24237.13</v>
       </c>
       <c r="M5" t="n">
-        <v>23925.57</v>
+        <v>24807.45</v>
       </c>
       <c r="N5" t="n">
-        <v>24196.44</v>
+        <v>25377.77</v>
       </c>
       <c r="O5" t="n">
-        <v>24128.24</v>
+        <v>25381.41</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,93 +940,95 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C6" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D6" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E6" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F6" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H6" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I6" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J6" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K6" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L6" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M6" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N6" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O6" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1043,79 +1047,77 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C7" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D7" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E7" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F7" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H7" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I7" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J7" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K7" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L7" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M7" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N7" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O7" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1129,76 +1131,78 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C8" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D8" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E8" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F8" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H8" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I8" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J8" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K8" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L8" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M8" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N8" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O8" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,78 +1217,80 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C9" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D9" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E9" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F9" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H9" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I9" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J9" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K9" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L9" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M9" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N9" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O9" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1306,77 +1312,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C10" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D10" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E10" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F10" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H10" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I10" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J10" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K10" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L10" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M10" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N10" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O10" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1385,83 +1389,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C11" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D11" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E11" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F11" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H11" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I11" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J11" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K11" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L11" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M11" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N11" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O11" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1471,80 +1471,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C12" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D12" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E12" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F12" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H12" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I12" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J12" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K12" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L12" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M12" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N12" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O12" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1555,57 +1559,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C13" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D13" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E13" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F13" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H13" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J13" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K13" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L13" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M13" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N13" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O13" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1613,24 +1617,24 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1639,59 +1643,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C14" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D14" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E14" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F14" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H14" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I14" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J14" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K14" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L14" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M14" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N14" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O14" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,12 +1699,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1730,50 +1728,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C15" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D15" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E15" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F15" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H15" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I15" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J15" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K15" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L15" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M15" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N15" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O15" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1781,18 +1779,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1805,55 +1803,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C16" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D16" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E16" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F16" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H16" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I16" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J16" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K16" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L16" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M16" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N16" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O16" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,12 +1863,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1885,59 +1885,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C17" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D17" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E17" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F17" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I17" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J17" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K17" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L17" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M17" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N17" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O17" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,22 +1941,30 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1972,50 +1976,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C18" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D18" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E18" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F18" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H18" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I18" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J18" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K18" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L18" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M18" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N18" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O18" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,29 +2027,27 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
@@ -2058,50 +2060,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C19" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D19" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E19" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F19" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H19" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I19" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J19" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K19" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L19" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M19" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N19" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O19" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,25 +2114,19 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2142,63 +2138,69 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C20" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D20" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E20" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F20" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H20" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J20" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K20" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L20" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M20" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N20" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O20" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>25817.05</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2210,9 +2212,9 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2220,67 +2222,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C21" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D21" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E21" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F21" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H21" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I21" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J21" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K21" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L21" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M21" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N21" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O21" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2304,72 +2304,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C22" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D22" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E22" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F22" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H22" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I22" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J22" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K22" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L22" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M22" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N22" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O22" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2381,55 +2379,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C23" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D23" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E23" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F23" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H23" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I23" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J23" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K23" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L23" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M23" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N23" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O23" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,7 +2442,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2470,50 +2472,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C24" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D24" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E24" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F24" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H24" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I24" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J24" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K24" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L24" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M24" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N24" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O24" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,14 +2526,14 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2554,50 +2556,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C25" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D25" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E25" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F25" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H25" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I25" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J25" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K25" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L25" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M25" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N25" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O25" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,18 +2607,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2638,56 +2640,60 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C26" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D26" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E26" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F26" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H26" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I26" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J26" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K26" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L26" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M26" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N26" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O26" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2696,7 +2702,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2713,78 +2719,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C27" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D27" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E27" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F27" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H27" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I27" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J27" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K27" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L27" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M27" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N27" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O27" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26452.34</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2806,63 +2802,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C28" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D28" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E28" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F28" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H28" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I28" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J28" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K28" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L28" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M28" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N28" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O28" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2884,71 +2884,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C29" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D29" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E29" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H29" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I29" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J29" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K29" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L29" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M29" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N29" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O29" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2966,50 +2964,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C30" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D30" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E30" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F30" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H30" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I30" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J30" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K30" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L30" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M30" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N30" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O30" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,12 +3020,12 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3041,55 +3039,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C31" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D31" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E31" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F31" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H31" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I31" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J31" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K31" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L31" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M31" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N31" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O31" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,7 +3102,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3130,50 +3132,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C32" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D32" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E32" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F32" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H32" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I32" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J32" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K32" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L32" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M32" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N32" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O32" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3184,7 +3186,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3214,50 +3216,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C33" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D33" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E33" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F33" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H33" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J33" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K33" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L33" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M33" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N33" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O33" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3265,18 +3267,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3291,57 +3293,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C34" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D34" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E34" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F34" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H34" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I34" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J34" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K34" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L34" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M34" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N34" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O34" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3351,12 +3353,12 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3382,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C35" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D35" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E35" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F35" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H35" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I35" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J35" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K35" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L35" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M35" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N35" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O35" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3433,24 +3435,28 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
@@ -3459,57 +3465,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C36" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D36" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E36" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F36" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H36" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J36" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K36" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L36" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M36" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N36" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O36" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3517,87 +3523,79 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C37" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D37" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E37" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F37" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H37" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I37" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J37" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K37" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L37" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M37" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N37" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O37" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,79 +3603,87 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C38" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D38" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E38" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F38" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I38" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J38" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K38" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L38" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M38" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N38" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O38" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3688,84 +3694,76 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C39" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D39" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E39" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F39" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H39" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I39" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J39" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K39" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L39" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M39" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N39" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O39" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,17 +3771,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3797,58 +3797,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C40" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D40" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E40" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H40" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J40" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K40" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L40" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M40" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N40" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O40" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
@@ -3858,15 +3864,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3888,72 +3892,70 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C41" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D41" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E41" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F41" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H41" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I41" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J41" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K41" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L41" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M41" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N41" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O41" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3965,78 +3967,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C42" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D42" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E42" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F42" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H42" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I42" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J42" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K42" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L42" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M42" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N42" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O42" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4049,141 +4049,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C43" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D43" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E43" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F43" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H43" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I43" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J43" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K43" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L43" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M43" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N43" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O43" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C44" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D44" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E44" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F44" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H44" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I44" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J44" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K44" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L44" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M44" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N44" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O44" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4191,83 +4193,83 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C45" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D45" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E45" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F45" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H45" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I45" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J45" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K45" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L45" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M45" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N45" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O45" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4280,7 +4282,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4301,57 +4303,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C46" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D46" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E46" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F46" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H46" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I46" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J46" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K46" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L46" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M46" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N46" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O46" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4359,19 +4361,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4383,59 +4385,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C47" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D47" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E47" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F47" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H47" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I47" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J47" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K47" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L47" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M47" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N47" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O47" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4446,21 +4444,25 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4472,50 +4474,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C48" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D48" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E48" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F48" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H48" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J48" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K48" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L48" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M48" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N48" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O48" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4526,7 +4528,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4541,10 +4543,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4556,50 +4556,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C49" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D49" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E49" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F49" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H49" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I49" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J49" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K49" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L49" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M49" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N49" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O49" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4610,20 +4610,18 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4638,69 +4636,73 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C50" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D50" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E50" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F50" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H50" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I50" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J50" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K50" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L50" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M50" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N50" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O50" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>26901.43</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4713,82 +4715,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C51" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D51" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E51" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F51" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H51" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I51" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J51" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K51" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L51" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M51" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N51" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O51" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4797,90 +4801,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C52" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D52" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E52" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F52" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H52" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I52" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J52" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K52" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L52" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M52" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N52" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O52" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
@@ -4888,65 +4888,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C53" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D53" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E53" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F53" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H53" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I53" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J53" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K53" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L53" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M53" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N53" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O53" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4970,50 +4968,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C54" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D54" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E54" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F54" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H54" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I54" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J54" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K54" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L54" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M54" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N54" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O54" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5026,7 +5024,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5050,50 +5048,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25498.74</v>
+        <v>25491.35</v>
       </c>
       <c r="C55" t="n">
-        <v>25800.62</v>
+        <v>25783.16</v>
       </c>
       <c r="D55" t="n">
-        <v>25172.89</v>
+        <v>25164.2</v>
       </c>
       <c r="E55" t="n">
-        <v>25304.06</v>
+        <v>25408.64</v>
       </c>
       <c r="F55" t="n">
-        <v>-264.5</v>
+        <v>104.58</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0041</v>
       </c>
       <c r="H55" t="n">
-        <v>627.73</v>
+        <v>618.96</v>
       </c>
       <c r="I55" t="n">
-        <v>24652.31</v>
+        <v>24545.16</v>
       </c>
       <c r="J55" t="n">
-        <v>24786.22</v>
+        <v>24584.98</v>
       </c>
       <c r="K55" t="n">
-        <v>25214.14</v>
+        <v>24990.2</v>
       </c>
       <c r="L55" t="n">
-        <v>25642.07</v>
+        <v>25395.41</v>
       </c>
       <c r="M55" t="n">
-        <v>25922.98</v>
+        <v>25617.92</v>
       </c>
       <c r="N55" t="n">
-        <v>26203.9</v>
+        <v>25840.44</v>
       </c>
       <c r="O55" t="n">
-        <v>26778.83</v>
+        <v>26428.35</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5101,18 +5099,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5125,55 +5123,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25491.35</v>
+        <v>25443.98</v>
       </c>
       <c r="C56" t="n">
-        <v>25783.16</v>
+        <v>25617.31</v>
       </c>
       <c r="D56" t="n">
-        <v>25164.2</v>
+        <v>24831.6</v>
       </c>
       <c r="E56" t="n">
-        <v>25408.64</v>
+        <v>25231.2</v>
       </c>
       <c r="F56" t="n">
-        <v>104.58</v>
+        <v>-177.44</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.007</v>
       </c>
       <c r="H56" t="n">
-        <v>618.96</v>
+        <v>785.71</v>
       </c>
       <c r="I56" t="n">
-        <v>24545.16</v>
+        <v>24545.24</v>
       </c>
       <c r="J56" t="n">
-        <v>24584.98</v>
+        <v>24757.16</v>
       </c>
       <c r="K56" t="n">
-        <v>24990.2</v>
+        <v>25099.16</v>
       </c>
       <c r="L56" t="n">
-        <v>25395.41</v>
+        <v>25441.16</v>
       </c>
       <c r="M56" t="n">
-        <v>25617.92</v>
+        <v>25718.12</v>
       </c>
       <c r="N56" t="n">
-        <v>25840.44</v>
+        <v>25995.08</v>
       </c>
       <c r="O56" t="n">
-        <v>26428.35</v>
+        <v>26402.12</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5181,18 +5183,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5205,59 +5207,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25443.98</v>
+        <v>25251.39</v>
       </c>
       <c r="C57" t="n">
-        <v>25617.31</v>
+        <v>25522.09</v>
       </c>
       <c r="D57" t="n">
-        <v>24831.6</v>
+        <v>24792.79</v>
       </c>
       <c r="E57" t="n">
-        <v>25231.2</v>
+        <v>25087.27</v>
       </c>
       <c r="F57" t="n">
-        <v>-177.44</v>
+        <v>-143.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0057</v>
       </c>
       <c r="H57" t="n">
-        <v>785.71</v>
+        <v>729.3</v>
       </c>
       <c r="I57" t="n">
-        <v>24545.24</v>
+        <v>24045.89</v>
       </c>
       <c r="J57" t="n">
-        <v>24757.16</v>
+        <v>24448.86</v>
       </c>
       <c r="K57" t="n">
-        <v>25099.16</v>
+        <v>24838.34</v>
       </c>
       <c r="L57" t="n">
-        <v>25441.16</v>
+        <v>25227.83</v>
       </c>
       <c r="M57" t="n">
-        <v>25718.12</v>
+        <v>25624.05</v>
       </c>
       <c r="N57" t="n">
-        <v>25995.08</v>
+        <v>26020.28</v>
       </c>
       <c r="O57" t="n">
-        <v>26402.12</v>
+        <v>26403.02</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5267,12 +5265,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5290,86 +5288,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25251.39</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25522.09</v>
-      </c>
-      <c r="D58" t="n">
-        <v>24792.79</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24806.97</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-424.23</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0168</v>
-      </c>
-      <c r="H58" t="n">
-        <v>729.3</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24045.89</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24448.86</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24838.34</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25227.83</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25624.05</v>
-      </c>
-      <c r="N58" t="n">
-        <v>26020.28</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26403.02</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5289,6 +5289,88 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25206.95</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25315.75</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25166.57</v>
+      </c>
+      <c r="E58" t="n">
+        <v>25277.68</v>
+      </c>
+      <c r="F58" t="n">
+        <v>190.41</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="H58" t="n">
+        <v>149.18</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24063.49</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24322.88</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24722.62</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25122.35</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25451.92</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25781.49</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26251.39</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5299,22 +5299,22 @@
         <v>25206.95</v>
       </c>
       <c r="C58" t="n">
-        <v>25315.75</v>
+        <v>25453.29</v>
       </c>
       <c r="D58" t="n">
         <v>25166.57</v>
       </c>
       <c r="E58" t="n">
-        <v>25277.68</v>
+        <v>25259.9</v>
       </c>
       <c r="F58" t="n">
-        <v>190.41</v>
+        <v>172.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0069</v>
       </c>
       <c r="H58" t="n">
-        <v>149.18</v>
+        <v>286.72</v>
       </c>
       <c r="I58" t="n">
         <v>24063.49</v>
@@ -5351,8 +5351,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,28 +659,30 @@
         <v>570.6799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23243.16</v>
+        <v>23333.68</v>
       </c>
       <c r="J2" t="n">
-        <v>23365.28</v>
+        <v>23478.43</v>
       </c>
       <c r="K2" t="n">
-        <v>23538.04</v>
+        <v>23583.3</v>
       </c>
       <c r="L2" t="n">
-        <v>23710.81</v>
+        <v>23688.18</v>
       </c>
       <c r="M2" t="n">
-        <v>23858.26</v>
+        <v>23813</v>
       </c>
       <c r="N2" t="n">
-        <v>24005.7</v>
+        <v>23937.81</v>
       </c>
       <c r="O2" t="n">
-        <v>24203.79</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>24022.75</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -697,8 +699,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,7 +717,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5305,13 +5309,13 @@
         <v>25166.57</v>
       </c>
       <c r="E58" t="n">
-        <v>25259.9</v>
+        <v>25298.61</v>
       </c>
       <c r="F58" t="n">
-        <v>172.63</v>
+        <v>211.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>286.72</v>
@@ -5348,12 +5352,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>570.6799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23333.68</v>
+        <v>23415.66</v>
       </c>
       <c r="J2" t="n">
-        <v>23478.43</v>
+        <v>23509.17</v>
       </c>
       <c r="K2" t="n">
-        <v>23583.3</v>
+        <v>23603.8</v>
       </c>
       <c r="L2" t="n">
-        <v>23688.18</v>
+        <v>23698.43</v>
       </c>
       <c r="M2" t="n">
-        <v>23813</v>
+        <v>23792.5</v>
       </c>
       <c r="N2" t="n">
-        <v>23937.81</v>
+        <v>23886.57</v>
       </c>
       <c r="O2" t="n">
-        <v>24022.75</v>
+        <v>23981.76</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -691,12 +691,12 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -5306,19 +5306,19 @@
         <v>25453.29</v>
       </c>
       <c r="D58" t="n">
-        <v>25166.57</v>
+        <v>25133.71</v>
       </c>
       <c r="E58" t="n">
-        <v>25298.61</v>
+        <v>25382.62</v>
       </c>
       <c r="F58" t="n">
-        <v>211.34</v>
+        <v>295.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0118</v>
       </c>
       <c r="H58" t="n">
-        <v>286.72</v>
+        <v>319.58</v>
       </c>
       <c r="I58" t="n">
         <v>24063.49</v>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,75 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23785.26</v>
+        <v>23567.49</v>
       </c>
       <c r="C2" t="n">
-        <v>23855.35</v>
+        <v>23756.04</v>
       </c>
       <c r="D2" t="n">
-        <v>23284.67</v>
+        <v>23383.84</v>
       </c>
       <c r="E2" t="n">
-        <v>23639.41</v>
+        <v>23739.47</v>
       </c>
       <c r="F2" t="n">
-        <v>-58.74</v>
+        <v>100.06</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.0042</v>
       </c>
       <c r="H2" t="n">
-        <v>570.6799999999999</v>
+        <v>372.2</v>
       </c>
       <c r="I2" t="n">
-        <v>23415.66</v>
+        <v>22713.99</v>
       </c>
       <c r="J2" t="n">
-        <v>23509.17</v>
+        <v>23103.43</v>
       </c>
       <c r="K2" t="n">
-        <v>23603.8</v>
+        <v>23354.07</v>
       </c>
       <c r="L2" t="n">
-        <v>23698.43</v>
+        <v>23604.71</v>
       </c>
       <c r="M2" t="n">
-        <v>23792.5</v>
+        <v>23924.75</v>
       </c>
       <c r="N2" t="n">
-        <v>23886.57</v>
+        <v>24244.79</v>
       </c>
       <c r="O2" t="n">
-        <v>23981.76</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>24426.03</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -717,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23567.49</v>
+        <v>23835.61</v>
       </c>
       <c r="C3" t="n">
-        <v>23756.04</v>
+        <v>24524.11</v>
       </c>
       <c r="D3" t="n">
-        <v>23383.84</v>
+        <v>23666.81</v>
       </c>
       <c r="E3" t="n">
-        <v>23739.47</v>
+        <v>24378.8</v>
       </c>
       <c r="F3" t="n">
-        <v>100.06</v>
+        <v>639.33</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0269</v>
       </c>
       <c r="H3" t="n">
-        <v>372.2</v>
+        <v>857.3</v>
       </c>
       <c r="I3" t="n">
-        <v>22713.99</v>
+        <v>23011.64</v>
       </c>
       <c r="J3" t="n">
-        <v>23103.43</v>
+        <v>23452.04</v>
       </c>
       <c r="K3" t="n">
-        <v>23354.07</v>
+        <v>23553.37</v>
       </c>
       <c r="L3" t="n">
-        <v>23604.71</v>
+        <v>23654.71</v>
       </c>
       <c r="M3" t="n">
-        <v>23924.75</v>
+        <v>23925.57</v>
       </c>
       <c r="N3" t="n">
-        <v>24244.79</v>
+        <v>24196.44</v>
       </c>
       <c r="O3" t="n">
-        <v>24426.03</v>
+        <v>24128.24</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,78 +770,80 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C4" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D4" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E4" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F4" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H4" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I4" t="n">
-        <v>23011.64</v>
+        <v>22809.51</v>
       </c>
       <c r="J4" t="n">
-        <v>23452.04</v>
+        <v>23663.17</v>
       </c>
       <c r="K4" t="n">
-        <v>23553.37</v>
+        <v>23950.15</v>
       </c>
       <c r="L4" t="n">
-        <v>23654.71</v>
+        <v>24237.13</v>
       </c>
       <c r="M4" t="n">
-        <v>23925.57</v>
+        <v>24807.45</v>
       </c>
       <c r="N4" t="n">
-        <v>24196.44</v>
+        <v>25377.77</v>
       </c>
       <c r="O4" t="n">
-        <v>24128.24</v>
+        <v>25381.41</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,93 +854,95 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C5" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D5" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E5" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F5" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H5" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I5" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J5" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K5" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L5" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M5" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N5" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O5" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -965,79 +961,77 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C6" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D6" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E6" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F6" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H6" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I6" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J6" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K6" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L6" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M6" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N6" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O6" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1051,76 +1045,78 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C7" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D7" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E7" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F7" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H7" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I7" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J7" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K7" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L7" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M7" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N7" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O7" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1135,78 +1131,80 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C8" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D8" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E8" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F8" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H8" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I8" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J8" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K8" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L8" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M8" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N8" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O8" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1228,77 +1226,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C9" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D9" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E9" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F9" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H9" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I9" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J9" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K9" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L9" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M9" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N9" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O9" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1307,83 +1303,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C10" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D10" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E10" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F10" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H10" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I10" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J10" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K10" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L10" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M10" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N10" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O10" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1393,80 +1385,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C11" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D11" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E11" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F11" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H11" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I11" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J11" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K11" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L11" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M11" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N11" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O11" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1477,57 +1473,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C12" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D12" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E12" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F12" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H12" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J12" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K12" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L12" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M12" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N12" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O12" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,24 +1531,24 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1561,59 +1557,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C13" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D13" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E13" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F13" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H13" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I13" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J13" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K13" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L13" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M13" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N13" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O13" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1621,12 +1613,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1652,50 +1642,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C14" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D14" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E14" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F14" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H14" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I14" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J14" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K14" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L14" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M14" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N14" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O14" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1703,18 +1693,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1727,55 +1717,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C15" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D15" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E15" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F15" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H15" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I15" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J15" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K15" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L15" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M15" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N15" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O15" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,12 +1777,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1807,59 +1799,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C16" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D16" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E16" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F16" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I16" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J16" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K16" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L16" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M16" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N16" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O16" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,22 +1855,30 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1894,50 +1890,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C17" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D17" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E17" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F17" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H17" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I17" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J17" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K17" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L17" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M17" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N17" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O17" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,29 +1941,27 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -1980,50 +1974,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C18" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D18" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E18" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F18" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H18" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I18" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J18" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K18" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L18" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M18" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N18" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O18" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,25 +2028,19 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2064,63 +2052,69 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C19" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D19" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E19" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F19" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H19" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J19" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K19" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L19" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M19" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N19" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O19" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>25817.05</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2132,9 +2126,9 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2142,67 +2136,65 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C20" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D20" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E20" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F20" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H20" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I20" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J20" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K20" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L20" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M20" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N20" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O20" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2226,72 +2218,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C21" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D21" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E21" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F21" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H21" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I21" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J21" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K21" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L21" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M21" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N21" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O21" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2303,55 +2293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C22" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D22" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E22" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F22" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H22" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I22" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J22" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K22" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L22" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M22" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N22" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O22" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,7 +2356,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2392,50 +2386,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C23" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D23" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E23" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F23" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H23" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I23" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J23" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K23" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L23" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M23" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N23" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O23" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,14 +2440,14 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2476,50 +2470,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C24" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D24" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E24" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F24" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H24" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I24" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J24" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K24" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L24" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M24" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N24" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O24" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2527,18 +2521,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2560,56 +2554,60 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C25" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D25" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E25" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F25" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H25" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I25" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J25" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K25" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L25" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M25" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N25" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O25" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2618,7 +2616,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2635,78 +2633,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C26" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D26" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E26" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F26" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H26" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I26" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J26" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K26" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L26" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M26" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N26" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O26" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26452.34</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2728,63 +2716,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C27" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D27" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E27" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F27" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H27" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I27" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J27" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K27" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L27" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M27" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N27" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O27" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2806,71 +2798,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C28" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D28" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E28" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H28" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I28" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J28" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K28" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L28" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M28" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N28" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O28" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2888,50 +2878,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C29" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D29" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E29" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F29" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H29" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I29" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J29" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K29" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L29" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M29" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N29" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O29" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2944,12 +2934,12 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2963,55 +2953,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C30" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D30" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E30" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F30" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H30" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I30" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J30" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K30" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L30" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M30" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N30" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O30" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,7 +3016,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3052,50 +3046,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C31" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D31" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E31" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F31" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H31" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I31" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J31" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K31" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L31" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M31" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N31" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O31" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,7 +3100,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3136,50 +3130,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C32" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D32" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E32" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F32" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H32" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J32" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K32" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L32" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M32" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N32" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O32" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,18 +3181,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3213,57 +3207,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C33" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D33" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E33" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F33" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H33" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I33" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J33" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K33" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L33" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M33" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N33" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O33" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,12 +3267,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3304,50 +3298,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C34" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D34" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E34" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F34" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H34" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I34" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J34" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K34" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L34" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M34" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N34" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O34" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,24 +3349,28 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
@@ -3381,57 +3379,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C35" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D35" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E35" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F35" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H35" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J35" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K35" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L35" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M35" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N35" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O35" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,87 +3437,79 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C36" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D36" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E36" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F36" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H36" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I36" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J36" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K36" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L36" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M36" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N36" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O36" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3527,79 +3517,87 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C37" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D37" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E37" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F37" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I37" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J37" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K37" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L37" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M37" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N37" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O37" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3610,84 +3608,76 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C38" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D38" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E38" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F38" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H38" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I38" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J38" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K38" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L38" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M38" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N38" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O38" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,17 +3685,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3719,58 +3711,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C39" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D39" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E39" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H39" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J39" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K39" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L39" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M39" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N39" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O39" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
@@ -3780,15 +3778,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3810,72 +3806,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C40" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D40" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E40" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F40" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H40" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I40" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J40" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K40" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L40" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M40" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N40" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O40" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3887,78 +3881,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C41" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D41" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E41" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F41" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H41" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I41" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J41" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K41" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L41" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M41" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N41" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O41" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3971,141 +3963,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C42" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D42" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E42" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F42" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H42" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I42" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J42" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K42" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L42" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M42" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N42" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O42" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C43" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D43" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E43" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F43" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H43" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I43" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J43" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K43" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L43" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M43" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N43" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O43" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4113,83 +4107,83 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C44" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D44" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E44" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F44" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H44" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I44" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J44" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K44" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L44" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M44" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N44" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O44" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4202,7 +4196,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4223,57 +4217,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C45" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D45" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E45" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F45" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H45" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I45" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J45" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K45" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L45" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M45" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N45" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O45" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4281,19 +4275,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4305,59 +4299,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C46" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D46" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E46" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F46" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H46" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I46" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J46" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K46" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L46" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M46" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N46" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O46" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4368,21 +4358,25 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4394,50 +4388,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C47" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D47" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E47" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F47" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H47" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J47" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K47" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L47" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M47" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N47" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O47" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4448,7 +4442,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4463,10 +4457,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4478,50 +4470,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C48" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D48" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E48" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F48" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H48" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I48" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J48" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K48" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L48" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M48" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N48" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O48" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4532,20 +4524,18 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4560,69 +4550,73 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C49" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D49" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E49" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F49" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H49" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I49" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J49" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K49" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L49" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M49" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N49" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O49" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>26901.43</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4635,82 +4629,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C50" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D50" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E50" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F50" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H50" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I50" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J50" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K50" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L50" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M50" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N50" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O50" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4719,90 +4715,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C51" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D51" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E51" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F51" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H51" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I51" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J51" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K51" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L51" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M51" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N51" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O51" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr"/>
@@ -4810,65 +4802,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C52" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D52" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E52" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F52" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H52" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I52" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J52" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K52" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L52" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M52" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N52" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O52" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4892,50 +4882,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C53" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D53" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E53" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F53" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H53" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I53" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J53" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K53" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L53" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M53" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N53" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O53" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4948,7 +4938,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4972,50 +4962,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25498.74</v>
+        <v>25491.35</v>
       </c>
       <c r="C54" t="n">
-        <v>25800.62</v>
+        <v>25783.16</v>
       </c>
       <c r="D54" t="n">
-        <v>25172.89</v>
+        <v>25164.2</v>
       </c>
       <c r="E54" t="n">
-        <v>25304.06</v>
+        <v>25408.64</v>
       </c>
       <c r="F54" t="n">
-        <v>-264.5</v>
+        <v>104.58</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0041</v>
       </c>
       <c r="H54" t="n">
-        <v>627.73</v>
+        <v>618.96</v>
       </c>
       <c r="I54" t="n">
-        <v>24652.31</v>
+        <v>24545.16</v>
       </c>
       <c r="J54" t="n">
-        <v>24786.22</v>
+        <v>24584.98</v>
       </c>
       <c r="K54" t="n">
-        <v>25214.14</v>
+        <v>24990.2</v>
       </c>
       <c r="L54" t="n">
-        <v>25642.07</v>
+        <v>25395.41</v>
       </c>
       <c r="M54" t="n">
-        <v>25922.98</v>
+        <v>25617.92</v>
       </c>
       <c r="N54" t="n">
-        <v>26203.9</v>
+        <v>25840.44</v>
       </c>
       <c r="O54" t="n">
-        <v>26778.83</v>
+        <v>26428.35</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5023,18 +5013,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5047,55 +5037,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25491.35</v>
+        <v>25443.98</v>
       </c>
       <c r="C55" t="n">
-        <v>25783.16</v>
+        <v>25617.31</v>
       </c>
       <c r="D55" t="n">
-        <v>25164.2</v>
+        <v>24831.6</v>
       </c>
       <c r="E55" t="n">
-        <v>25408.64</v>
+        <v>25231.2</v>
       </c>
       <c r="F55" t="n">
-        <v>104.58</v>
+        <v>-177.44</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.007</v>
       </c>
       <c r="H55" t="n">
-        <v>618.96</v>
+        <v>785.71</v>
       </c>
       <c r="I55" t="n">
-        <v>24545.16</v>
+        <v>24545.24</v>
       </c>
       <c r="J55" t="n">
-        <v>24584.98</v>
+        <v>24757.16</v>
       </c>
       <c r="K55" t="n">
-        <v>24990.2</v>
+        <v>25099.16</v>
       </c>
       <c r="L55" t="n">
-        <v>25395.41</v>
+        <v>25441.16</v>
       </c>
       <c r="M55" t="n">
-        <v>25617.92</v>
+        <v>25718.12</v>
       </c>
       <c r="N55" t="n">
-        <v>25840.44</v>
+        <v>25995.08</v>
       </c>
       <c r="O55" t="n">
-        <v>26428.35</v>
+        <v>26402.12</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5103,18 +5097,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5127,59 +5121,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25443.98</v>
+        <v>25251.39</v>
       </c>
       <c r="C56" t="n">
-        <v>25617.31</v>
+        <v>25522.09</v>
       </c>
       <c r="D56" t="n">
-        <v>24831.6</v>
+        <v>24792.79</v>
       </c>
       <c r="E56" t="n">
-        <v>25231.2</v>
+        <v>25087.27</v>
       </c>
       <c r="F56" t="n">
-        <v>-177.44</v>
+        <v>-143.93</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0057</v>
       </c>
       <c r="H56" t="n">
-        <v>785.71</v>
+        <v>729.3</v>
       </c>
       <c r="I56" t="n">
-        <v>24545.24</v>
+        <v>24045.89</v>
       </c>
       <c r="J56" t="n">
-        <v>24757.16</v>
+        <v>24448.86</v>
       </c>
       <c r="K56" t="n">
-        <v>25099.16</v>
+        <v>24838.34</v>
       </c>
       <c r="L56" t="n">
-        <v>25441.16</v>
+        <v>25227.83</v>
       </c>
       <c r="M56" t="n">
-        <v>25718.12</v>
+        <v>25624.05</v>
       </c>
       <c r="N56" t="n">
-        <v>25995.08</v>
+        <v>26020.28</v>
       </c>
       <c r="O56" t="n">
-        <v>26402.12</v>
+        <v>26403.02</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5189,12 +5179,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5216,50 +5206,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25251.39</v>
+        <v>25206.95</v>
       </c>
       <c r="C57" t="n">
-        <v>25522.09</v>
+        <v>25693.89</v>
       </c>
       <c r="D57" t="n">
-        <v>24792.79</v>
+        <v>25133.71</v>
       </c>
       <c r="E57" t="n">
-        <v>25087.27</v>
+        <v>25622.61</v>
       </c>
       <c r="F57" t="n">
-        <v>-143.93</v>
+        <v>535.34</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0213</v>
       </c>
       <c r="H57" t="n">
-        <v>729.3</v>
+        <v>560.1799999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>24045.89</v>
+        <v>24063.49</v>
       </c>
       <c r="J57" t="n">
-        <v>24448.86</v>
+        <v>24322.88</v>
       </c>
       <c r="K57" t="n">
-        <v>24838.34</v>
+        <v>24722.62</v>
       </c>
       <c r="L57" t="n">
-        <v>25227.83</v>
+        <v>25122.35</v>
       </c>
       <c r="M57" t="n">
-        <v>25624.05</v>
+        <v>25451.92</v>
       </c>
       <c r="N57" t="n">
-        <v>26020.28</v>
+        <v>25781.49</v>
       </c>
       <c r="O57" t="n">
-        <v>26403.02</v>
+        <v>26251.39</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5267,21 +5257,23 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5291,89 +5283,9 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25206.95</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25453.29</v>
-      </c>
-      <c r="D58" t="n">
-        <v>25133.71</v>
-      </c>
-      <c r="E58" t="n">
-        <v>25382.62</v>
-      </c>
-      <c r="F58" t="n">
-        <v>295.35</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="H58" t="n">
-        <v>319.58</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24063.49</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24322.88</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24722.62</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25122.35</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25451.92</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25781.49</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26251.39</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>372.2</v>
       </c>
       <c r="I2" t="n">
-        <v>22713.99</v>
+        <v>22784.1</v>
       </c>
       <c r="J2" t="n">
-        <v>23103.43</v>
+        <v>23191.07</v>
       </c>
       <c r="K2" t="n">
-        <v>23354.07</v>
+        <v>23389.12</v>
       </c>
       <c r="L2" t="n">
-        <v>23604.71</v>
+        <v>23587.18</v>
       </c>
       <c r="M2" t="n">
-        <v>23924.75</v>
+        <v>23889.7</v>
       </c>
       <c r="N2" t="n">
-        <v>24244.79</v>
+        <v>24192.21</v>
       </c>
       <c r="O2" t="n">
-        <v>24426.03</v>
+        <v>24285.81</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +688,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5286,6 +5293,92 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25540.77</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25540.88</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25198.97</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24573.53</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25166.83</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25342.52</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25518.21</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25902.7</v>
+      </c>
+      <c r="N58" t="n">
+        <v>26287.19</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26254.07</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5312,13 +5309,13 @@
         <v>25198.97</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>25319.77</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-302.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0118</v>
       </c>
       <c r="H58" t="n">
         <v>341.91</v>
@@ -5344,22 +5341,20 @@
       <c r="O58" t="n">
         <v>26254.07</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5306,19 +5306,19 @@
         <v>25540.88</v>
       </c>
       <c r="D58" t="n">
-        <v>25198.97</v>
+        <v>25050.11</v>
       </c>
       <c r="E58" t="n">
-        <v>25319.77</v>
+        <v>25304.42</v>
       </c>
       <c r="F58" t="n">
-        <v>-302.84</v>
+        <v>-318.19</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0124</v>
       </c>
       <c r="H58" t="n">
-        <v>341.91</v>
+        <v>490.77</v>
       </c>
       <c r="I58" t="n">
         <v>24573.53</v>
@@ -5344,8 +5344,10 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5371,11 +5373,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>372.2</v>
       </c>
       <c r="I2" t="n">
-        <v>22784.1</v>
+        <v>23330.38</v>
       </c>
       <c r="J2" t="n">
-        <v>23191.07</v>
+        <v>23395.92</v>
       </c>
       <c r="K2" t="n">
-        <v>23389.12</v>
+        <v>23525.7</v>
       </c>
       <c r="L2" t="n">
-        <v>23587.18</v>
+        <v>23655.47</v>
       </c>
       <c r="M2" t="n">
-        <v>23889.7</v>
+        <v>23753.12</v>
       </c>
       <c r="N2" t="n">
-        <v>24192.21</v>
+        <v>23850.78</v>
       </c>
       <c r="O2" t="n">
-        <v>24285.81</v>
+        <v>24012.67</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -713,7 +715,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5303,22 +5305,22 @@
         <v>25540.77</v>
       </c>
       <c r="C58" t="n">
-        <v>25540.88</v>
+        <v>25706.19</v>
       </c>
       <c r="D58" t="n">
         <v>25050.11</v>
       </c>
       <c r="E58" t="n">
-        <v>25304.42</v>
+        <v>25645.04</v>
       </c>
       <c r="F58" t="n">
-        <v>-318.19</v>
+        <v>22.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0124</v>
+        <v>0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>490.77</v>
+        <v>656.08</v>
       </c>
       <c r="I58" t="n">
         <v>24573.53</v>
@@ -5351,12 +5353,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5373,7 +5375,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,28 +659,30 @@
         <v>372.2</v>
       </c>
       <c r="I2" t="n">
-        <v>23330.38</v>
+        <v>23413.28</v>
       </c>
       <c r="J2" t="n">
-        <v>23395.92</v>
+        <v>23427.01</v>
       </c>
       <c r="K2" t="n">
-        <v>23525.7</v>
+        <v>23546.42</v>
       </c>
       <c r="L2" t="n">
-        <v>23655.47</v>
+        <v>23665.83</v>
       </c>
       <c r="M2" t="n">
-        <v>23753.12</v>
+        <v>23732.4</v>
       </c>
       <c r="N2" t="n">
-        <v>23850.78</v>
+        <v>23798.97</v>
       </c>
       <c r="O2" t="n">
-        <v>24012.67</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>23971.22</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -5311,13 +5313,13 @@
         <v>25050.11</v>
       </c>
       <c r="E58" t="n">
-        <v>25645.04</v>
+        <v>25371.75</v>
       </c>
       <c r="F58" t="n">
-        <v>22.43</v>
+        <v>-250.86</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.0098</v>
       </c>
       <c r="H58" t="n">
         <v>656.08</v>
@@ -5353,12 +5355,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5377,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,140 +634,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23567.49</v>
+        <v>23835.61</v>
       </c>
       <c r="C2" t="n">
-        <v>23756.04</v>
+        <v>24524.11</v>
       </c>
       <c r="D2" t="n">
-        <v>23383.84</v>
+        <v>23666.81</v>
       </c>
       <c r="E2" t="n">
-        <v>23739.47</v>
+        <v>24378.8</v>
       </c>
       <c r="F2" t="n">
-        <v>100.06</v>
+        <v>639.33</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0269</v>
       </c>
       <c r="H2" t="n">
-        <v>372.2</v>
+        <v>857.3</v>
       </c>
       <c r="I2" t="n">
-        <v>23413.28</v>
+        <v>23011.64</v>
       </c>
       <c r="J2" t="n">
-        <v>23427.01</v>
+        <v>23452.04</v>
       </c>
       <c r="K2" t="n">
-        <v>23546.42</v>
+        <v>23553.37</v>
       </c>
       <c r="L2" t="n">
-        <v>23665.83</v>
+        <v>23654.71</v>
       </c>
       <c r="M2" t="n">
-        <v>23732.4</v>
+        <v>23925.57</v>
       </c>
       <c r="N2" t="n">
-        <v>23798.97</v>
+        <v>24196.44</v>
       </c>
       <c r="O2" t="n">
-        <v>23971.22</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>24128.24</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C3" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D3" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E3" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F3" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H3" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I3" t="n">
-        <v>23011.64</v>
+        <v>22809.51</v>
       </c>
       <c r="J3" t="n">
-        <v>23452.04</v>
+        <v>23663.17</v>
       </c>
       <c r="K3" t="n">
-        <v>23553.37</v>
+        <v>23950.15</v>
       </c>
       <c r="L3" t="n">
-        <v>23654.71</v>
+        <v>24237.13</v>
       </c>
       <c r="M3" t="n">
-        <v>23925.57</v>
+        <v>24807.45</v>
       </c>
       <c r="N3" t="n">
-        <v>24196.44</v>
+        <v>25377.77</v>
       </c>
       <c r="O3" t="n">
-        <v>24128.24</v>
+        <v>25381.41</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,91 +774,93 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C4" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D4" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E4" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F4" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H4" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I4" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J4" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K4" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L4" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M4" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N4" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O4" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -883,79 +879,77 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C5" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D5" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E5" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F5" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H5" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I5" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J5" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K5" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L5" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M5" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N5" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O5" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -969,77 +963,79 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C6" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D6" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E6" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F6" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H6" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I6" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J6" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K6" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L6" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M6" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N6" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O6" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1053,66 +1049,66 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C7" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D7" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E7" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F7" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H7" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I7" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J7" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K7" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L7" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M7" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N7" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O7" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1123,8 +1119,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1146,77 +1144,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C8" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D8" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E8" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F8" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H8" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I8" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J8" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K8" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L8" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M8" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N8" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O8" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1225,84 +1221,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C9" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D9" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E9" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F9" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H9" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I9" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J9" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K9" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L9" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M9" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N9" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O9" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1311,80 +1303,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C10" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D10" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E10" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F10" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H10" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I10" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J10" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K10" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L10" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M10" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N10" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O10" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1395,57 +1391,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C11" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D11" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E11" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F11" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H11" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J11" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K11" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L11" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M11" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N11" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O11" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1453,8 +1449,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1463,14 +1461,12 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1479,59 +1475,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C12" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D12" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E12" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F12" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H12" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I12" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J12" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K12" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L12" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M12" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N12" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O12" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1539,10 +1531,8 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1570,50 +1560,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C13" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D13" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E13" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F13" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H13" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I13" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J13" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K13" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L13" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M13" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N13" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O13" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1621,18 +1611,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1645,55 +1635,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C14" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D14" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E14" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F14" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H14" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I14" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J14" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K14" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L14" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M14" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N14" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O14" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1701,10 +1695,8 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
@@ -1725,59 +1717,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C15" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D15" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E15" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F15" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I15" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J15" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K15" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L15" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M15" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N15" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O15" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,22 +1773,30 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1812,50 +1808,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C16" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D16" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E16" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F16" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H16" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J16" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K16" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L16" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M16" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N16" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O16" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1863,29 +1859,27 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -1898,50 +1892,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C17" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D17" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E17" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F17" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H17" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I17" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J17" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K17" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L17" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M17" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N17" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O17" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1954,23 +1948,17 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1982,63 +1970,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C18" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D18" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E18" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F18" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H18" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J18" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K18" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L18" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M18" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N18" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O18" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>25817.05</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2050,9 +2044,9 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2060,64 +2054,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C19" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D19" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E19" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F19" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H19" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I19" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J19" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K19" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L19" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M19" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N19" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O19" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
@@ -2144,72 +2136,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C20" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D20" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E20" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F20" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H20" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I20" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J20" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K20" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L20" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M20" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N20" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O20" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2221,55 +2211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C21" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D21" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E21" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F21" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H21" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I21" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J21" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K21" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L21" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M21" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N21" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O21" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2310,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C22" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D22" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E22" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F22" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H22" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I22" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J22" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K22" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L22" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M22" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N22" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O22" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2366,12 +2360,12 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2394,50 +2388,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C23" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D23" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E23" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F23" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H23" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I23" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J23" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K23" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L23" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M23" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N23" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O23" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,18 +2439,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2478,65 +2472,69 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C24" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D24" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E24" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F24" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H24" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I24" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J24" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K24" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L24" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M24" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N24" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O24" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2553,78 +2551,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C25" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D25" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E25" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F25" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H25" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I25" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J25" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K25" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L25" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M25" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N25" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O25" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26452.34</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2646,63 +2634,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C26" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D26" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E26" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F26" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H26" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I26" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J26" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K26" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L26" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M26" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N26" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O26" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2724,71 +2716,69 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C27" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D27" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E27" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H27" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I27" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J27" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K27" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L27" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M27" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N27" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O27" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2806,50 +2796,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C28" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D28" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E28" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F28" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H28" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I28" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J28" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K28" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L28" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M28" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N28" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O28" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,14 +2850,14 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2881,55 +2871,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C29" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D29" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E29" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F29" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H29" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I29" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J29" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K29" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L29" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M29" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N29" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O29" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2970,50 +2964,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C30" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D30" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E30" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F30" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H30" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I30" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J30" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K30" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L30" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M30" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N30" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O30" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3054,50 +3048,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C31" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D31" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E31" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F31" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H31" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J31" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K31" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L31" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M31" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N31" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O31" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3105,19 +3099,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3131,57 +3125,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C32" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D32" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E32" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F32" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H32" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I32" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J32" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K32" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L32" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M32" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N32" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O32" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3191,12 +3185,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3222,50 +3216,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C33" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D33" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E33" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F33" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H33" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I33" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J33" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K33" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L33" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M33" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N33" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O33" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,24 +3267,28 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
@@ -3299,57 +3297,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C34" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D34" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E34" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F34" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H34" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J34" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K34" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L34" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M34" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N34" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O34" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,87 +3355,79 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C35" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D35" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E35" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F35" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H35" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I35" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J35" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K35" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L35" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M35" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N35" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O35" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3445,79 +3435,87 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C36" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D36" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E36" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F36" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I36" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J36" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K36" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L36" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M36" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N36" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O36" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3535,77 +3533,69 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C37" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D37" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E37" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F37" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H37" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I37" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J37" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K37" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L37" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M37" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N37" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O37" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,17 +3603,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3637,58 +3629,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C38" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D38" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E38" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F38" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H38" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J38" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K38" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L38" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M38" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N38" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O38" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
@@ -3703,10 +3701,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3728,72 +3724,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C39" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D39" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E39" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F39" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H39" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I39" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J39" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K39" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L39" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M39" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N39" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O39" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3805,79 +3799,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C40" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D40" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E40" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F40" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H40" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I40" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J40" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K40" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L40" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M40" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N40" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O40" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3889,141 +3881,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C41" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D41" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E41" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F41" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H41" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I41" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J41" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K41" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L41" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M41" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N41" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O41" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C42" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D42" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E42" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F42" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H42" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I42" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J42" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K42" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L42" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M42" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N42" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O42" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,83 +4025,83 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C43" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D43" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E43" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F43" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H43" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I43" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J43" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K43" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L43" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M43" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N43" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O43" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4141,57 +4135,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C44" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D44" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E44" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F44" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H44" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I44" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J44" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K44" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L44" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M44" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N44" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O44" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,19 +4193,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4223,59 +4217,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C45" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D45" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E45" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F45" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H45" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I45" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J45" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K45" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L45" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M45" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N45" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O45" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4293,14 +4283,18 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
@@ -4312,50 +4306,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C46" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D46" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E46" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F46" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H46" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J46" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K46" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L46" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M46" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N46" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O46" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4381,10 +4375,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4396,50 +4388,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C47" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D47" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E47" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F47" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H47" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I47" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J47" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K47" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L47" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M47" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N47" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O47" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4457,13 +4449,11 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4478,70 +4468,74 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C48" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D48" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E48" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F48" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H48" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I48" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J48" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K48" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L48" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M48" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N48" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O48" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+        <v>26901.43</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4553,82 +4547,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C49" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D49" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E49" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F49" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H49" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I49" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J49" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K49" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L49" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M49" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N49" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O49" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4637,90 +4633,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C50" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D50" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E50" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F50" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H50" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I50" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J50" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K50" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L50" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M50" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N50" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O50" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -4728,62 +4720,60 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C51" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D51" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E51" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F51" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H51" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I51" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J51" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K51" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L51" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M51" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N51" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O51" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
@@ -4810,50 +4800,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C52" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D52" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E52" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F52" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H52" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I52" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J52" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K52" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L52" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M52" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N52" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O52" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4890,50 +4880,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25498.74</v>
+        <v>25491.35</v>
       </c>
       <c r="C53" t="n">
-        <v>25800.62</v>
+        <v>25783.16</v>
       </c>
       <c r="D53" t="n">
-        <v>25172.89</v>
+        <v>25164.2</v>
       </c>
       <c r="E53" t="n">
-        <v>25304.06</v>
+        <v>25408.64</v>
       </c>
       <c r="F53" t="n">
-        <v>-264.5</v>
+        <v>104.58</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0041</v>
       </c>
       <c r="H53" t="n">
-        <v>627.73</v>
+        <v>618.96</v>
       </c>
       <c r="I53" t="n">
-        <v>24652.31</v>
+        <v>24545.16</v>
       </c>
       <c r="J53" t="n">
-        <v>24786.22</v>
+        <v>24584.98</v>
       </c>
       <c r="K53" t="n">
-        <v>25214.14</v>
+        <v>24990.2</v>
       </c>
       <c r="L53" t="n">
-        <v>25642.07</v>
+        <v>25395.41</v>
       </c>
       <c r="M53" t="n">
-        <v>25922.98</v>
+        <v>25617.92</v>
       </c>
       <c r="N53" t="n">
-        <v>26203.9</v>
+        <v>25840.44</v>
       </c>
       <c r="O53" t="n">
-        <v>26778.83</v>
+        <v>26428.35</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4941,18 +4931,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4965,55 +4955,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25491.35</v>
+        <v>25443.98</v>
       </c>
       <c r="C54" t="n">
-        <v>25783.16</v>
+        <v>25617.31</v>
       </c>
       <c r="D54" t="n">
-        <v>25164.2</v>
+        <v>24831.6</v>
       </c>
       <c r="E54" t="n">
-        <v>25408.64</v>
+        <v>25231.2</v>
       </c>
       <c r="F54" t="n">
-        <v>104.58</v>
+        <v>-177.44</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.007</v>
       </c>
       <c r="H54" t="n">
-        <v>618.96</v>
+        <v>785.71</v>
       </c>
       <c r="I54" t="n">
-        <v>24545.16</v>
+        <v>24545.24</v>
       </c>
       <c r="J54" t="n">
-        <v>24584.98</v>
+        <v>24757.16</v>
       </c>
       <c r="K54" t="n">
-        <v>24990.2</v>
+        <v>25099.16</v>
       </c>
       <c r="L54" t="n">
-        <v>25395.41</v>
+        <v>25441.16</v>
       </c>
       <c r="M54" t="n">
-        <v>25617.92</v>
+        <v>25718.12</v>
       </c>
       <c r="N54" t="n">
-        <v>25840.44</v>
+        <v>25995.08</v>
       </c>
       <c r="O54" t="n">
-        <v>26428.35</v>
+        <v>26402.12</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5021,18 +5015,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5045,59 +5039,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25443.98</v>
+        <v>25251.39</v>
       </c>
       <c r="C55" t="n">
-        <v>25617.31</v>
+        <v>25522.09</v>
       </c>
       <c r="D55" t="n">
-        <v>24831.6</v>
+        <v>24792.79</v>
       </c>
       <c r="E55" t="n">
-        <v>25231.2</v>
+        <v>25087.27</v>
       </c>
       <c r="F55" t="n">
-        <v>-177.44</v>
+        <v>-143.93</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0057</v>
       </c>
       <c r="H55" t="n">
-        <v>785.71</v>
+        <v>729.3</v>
       </c>
       <c r="I55" t="n">
-        <v>24545.24</v>
+        <v>24045.89</v>
       </c>
       <c r="J55" t="n">
-        <v>24757.16</v>
+        <v>24448.86</v>
       </c>
       <c r="K55" t="n">
-        <v>25099.16</v>
+        <v>24838.34</v>
       </c>
       <c r="L55" t="n">
-        <v>25441.16</v>
+        <v>25227.83</v>
       </c>
       <c r="M55" t="n">
-        <v>25718.12</v>
+        <v>25624.05</v>
       </c>
       <c r="N55" t="n">
-        <v>25995.08</v>
+        <v>26020.28</v>
       </c>
       <c r="O55" t="n">
-        <v>26402.12</v>
+        <v>26403.02</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5107,12 +5097,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5134,50 +5124,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25251.39</v>
+        <v>25206.95</v>
       </c>
       <c r="C56" t="n">
-        <v>25522.09</v>
+        <v>25693.89</v>
       </c>
       <c r="D56" t="n">
-        <v>24792.79</v>
+        <v>25133.71</v>
       </c>
       <c r="E56" t="n">
-        <v>25087.27</v>
+        <v>25622.61</v>
       </c>
       <c r="F56" t="n">
-        <v>-143.93</v>
+        <v>535.34</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0213</v>
       </c>
       <c r="H56" t="n">
-        <v>729.3</v>
+        <v>560.1799999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>24045.89</v>
+        <v>24063.49</v>
       </c>
       <c r="J56" t="n">
-        <v>24448.86</v>
+        <v>24322.88</v>
       </c>
       <c r="K56" t="n">
-        <v>24838.34</v>
+        <v>24722.62</v>
       </c>
       <c r="L56" t="n">
-        <v>25227.83</v>
+        <v>25122.35</v>
       </c>
       <c r="M56" t="n">
-        <v>25624.05</v>
+        <v>25451.92</v>
       </c>
       <c r="N56" t="n">
-        <v>26020.28</v>
+        <v>25781.49</v>
       </c>
       <c r="O56" t="n">
-        <v>26403.02</v>
+        <v>26251.39</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5185,21 +5175,23 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5209,79 +5201,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25206.95</v>
+        <v>25540.77</v>
       </c>
       <c r="C57" t="n">
-        <v>25693.89</v>
+        <v>25706.19</v>
       </c>
       <c r="D57" t="n">
-        <v>25133.71</v>
+        <v>25013.54</v>
       </c>
       <c r="E57" t="n">
-        <v>25622.61</v>
+        <v>25181.65</v>
       </c>
       <c r="F57" t="n">
-        <v>535.34</v>
+        <v>-440.96</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0172</v>
       </c>
       <c r="H57" t="n">
-        <v>560.1799999999999</v>
+        <v>692.65</v>
       </c>
       <c r="I57" t="n">
-        <v>24063.49</v>
+        <v>24573.53</v>
       </c>
       <c r="J57" t="n">
-        <v>24322.88</v>
+        <v>25166.83</v>
       </c>
       <c r="K57" t="n">
-        <v>24722.62</v>
+        <v>25342.52</v>
       </c>
       <c r="L57" t="n">
-        <v>25122.35</v>
+        <v>25518.21</v>
       </c>
       <c r="M57" t="n">
-        <v>25451.92</v>
+        <v>25902.7</v>
       </c>
       <c r="N57" t="n">
-        <v>25781.49</v>
+        <v>26287.19</v>
       </c>
       <c r="O57" t="n">
-        <v>26251.39</v>
+        <v>26254.07</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5292,92 +5288,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25540.77</v>
-      </c>
-      <c r="C58" t="n">
-        <v>25706.19</v>
-      </c>
-      <c r="D58" t="n">
-        <v>25050.11</v>
-      </c>
-      <c r="E58" t="n">
-        <v>25371.75</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-250.86</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0098</v>
-      </c>
-      <c r="H58" t="n">
-        <v>656.08</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24573.53</v>
-      </c>
-      <c r="J58" t="n">
-        <v>25166.83</v>
-      </c>
-      <c r="K58" t="n">
-        <v>25342.52</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25518.21</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25902.7</v>
-      </c>
-      <c r="N58" t="n">
-        <v>26287.19</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26254.07</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5293,6 +5293,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25235.84</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25509.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>25217.15</v>
+      </c>
+      <c r="E58" t="n">
+        <v>25410.84</v>
+      </c>
+      <c r="F58" t="n">
+        <v>229.19</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="H58" t="n">
+        <v>292.65</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24320.89</v>
+      </c>
+      <c r="J58" t="n">
+        <v>24399.89</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24835.33</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25270.76</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25527.98</v>
+      </c>
+      <c r="N58" t="n">
+        <v>25785.19</v>
+      </c>
+      <c r="O58" t="n">
+        <v>26398.84</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5303,22 +5303,22 @@
         <v>25235.84</v>
       </c>
       <c r="C58" t="n">
-        <v>25509.8</v>
+        <v>25647.49</v>
       </c>
       <c r="D58" t="n">
         <v>25217.15</v>
       </c>
       <c r="E58" t="n">
-        <v>25410.84</v>
+        <v>25590.77</v>
       </c>
       <c r="F58" t="n">
-        <v>229.19</v>
+        <v>409.12</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0162</v>
       </c>
       <c r="H58" t="n">
-        <v>292.65</v>
+        <v>430.34</v>
       </c>
       <c r="I58" t="n">
         <v>24320.89</v>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -5303,22 +5303,22 @@
         <v>25235.84</v>
       </c>
       <c r="C58" t="n">
-        <v>25647.49</v>
+        <v>25716.83</v>
       </c>
       <c r="D58" t="n">
         <v>25217.15</v>
       </c>
       <c r="E58" t="n">
-        <v>25590.77</v>
+        <v>25704.02</v>
       </c>
       <c r="F58" t="n">
-        <v>409.12</v>
+        <v>522.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0162</v>
+        <v>0.0207</v>
       </c>
       <c r="H58" t="n">
-        <v>430.34</v>
+        <v>499.68</v>
       </c>
       <c r="I58" t="n">
         <v>24320.89</v>
@@ -5357,12 +5357,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5373,7 +5375,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>857.3</v>
       </c>
       <c r="I2" t="n">
-        <v>23011.64</v>
+        <v>23402.46</v>
       </c>
       <c r="J2" t="n">
-        <v>23452.04</v>
+        <v>23598.59</v>
       </c>
       <c r="K2" t="n">
-        <v>23553.37</v>
+        <v>23651.08</v>
       </c>
       <c r="L2" t="n">
-        <v>23654.71</v>
+        <v>23703.56</v>
       </c>
       <c r="M2" t="n">
-        <v>23925.57</v>
+        <v>23827.87</v>
       </c>
       <c r="N2" t="n">
-        <v>24196.44</v>
+        <v>23952.17</v>
       </c>
       <c r="O2" t="n">
-        <v>24128.24</v>
+        <v>23932.83</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5303,22 +5303,22 @@
         <v>25235.84</v>
       </c>
       <c r="C58" t="n">
-        <v>25716.83</v>
+        <v>26106.19</v>
       </c>
       <c r="D58" t="n">
         <v>25217.15</v>
       </c>
       <c r="E58" t="n">
-        <v>25704.02</v>
+        <v>26039.68</v>
       </c>
       <c r="F58" t="n">
-        <v>522.37</v>
+        <v>858.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0341</v>
       </c>
       <c r="H58" t="n">
-        <v>499.68</v>
+        <v>889.04</v>
       </c>
       <c r="I58" t="n">
         <v>24320.89</v>
@@ -5368,16 +5368,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/DAX_weekly.xlsx
+++ b/three_gate/analysis/DAX_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23835.61</v>
+        <v>24357.59</v>
       </c>
       <c r="C2" t="n">
-        <v>24524.11</v>
+        <v>24771.34</v>
       </c>
       <c r="D2" t="n">
-        <v>23666.81</v>
+        <v>24241.46</v>
       </c>
       <c r="E2" t="n">
-        <v>24378.8</v>
+        <v>24241.46</v>
       </c>
       <c r="F2" t="n">
-        <v>639.33</v>
+        <v>-137.34</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0269</v>
+        <v>-0.0056</v>
       </c>
       <c r="H2" t="n">
-        <v>857.3</v>
+        <v>529.88</v>
       </c>
       <c r="I2" t="n">
-        <v>23402.46</v>
+        <v>22809.51</v>
       </c>
       <c r="J2" t="n">
-        <v>23598.59</v>
+        <v>23663.17</v>
       </c>
       <c r="K2" t="n">
-        <v>23651.08</v>
+        <v>23950.15</v>
       </c>
       <c r="L2" t="n">
-        <v>23703.56</v>
+        <v>24237.13</v>
       </c>
       <c r="M2" t="n">
-        <v>23827.87</v>
+        <v>24807.45</v>
       </c>
       <c r="N2" t="n">
-        <v>23952.17</v>
+        <v>25377.77</v>
       </c>
       <c r="O2" t="n">
-        <v>23932.83</v>
+        <v>25381.41</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,91 +690,93 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24357.59</v>
+        <v>24372.9</v>
       </c>
       <c r="C3" t="n">
-        <v>24771.34</v>
+        <v>24448.77</v>
       </c>
       <c r="D3" t="n">
-        <v>24241.46</v>
+        <v>23684.37</v>
       </c>
       <c r="E3" t="n">
-        <v>24241.46</v>
+        <v>23830.99</v>
       </c>
       <c r="F3" t="n">
-        <v>-137.34</v>
+        <v>-410.47</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0056</v>
+        <v>-0.0169</v>
       </c>
       <c r="H3" t="n">
-        <v>529.88</v>
+        <v>764.4</v>
       </c>
       <c r="I3" t="n">
-        <v>22809.51</v>
+        <v>23711.58</v>
       </c>
       <c r="J3" t="n">
-        <v>23663.17</v>
+        <v>23579.11</v>
       </c>
       <c r="K3" t="n">
-        <v>23950.15</v>
+        <v>23976.52</v>
       </c>
       <c r="L3" t="n">
-        <v>24237.13</v>
+        <v>24373.93</v>
       </c>
       <c r="M3" t="n">
-        <v>24807.45</v>
+        <v>24506.4</v>
       </c>
       <c r="N3" t="n">
-        <v>25377.77</v>
+        <v>24638.87</v>
       </c>
       <c r="O3" t="n">
-        <v>25381.41</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
+        <v>25301.22</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,79 +795,77 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24372.9</v>
+        <v>24035.19</v>
       </c>
       <c r="C4" t="n">
-        <v>24448.77</v>
+        <v>24384.24</v>
       </c>
       <c r="D4" t="n">
-        <v>23684.37</v>
+        <v>24026.59</v>
       </c>
       <c r="E4" t="n">
-        <v>23830.99</v>
+        <v>24239.89</v>
       </c>
       <c r="F4" t="n">
-        <v>-410.47</v>
+        <v>408.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0169</v>
+        <v>0.0172</v>
       </c>
       <c r="H4" t="n">
-        <v>764.4</v>
+        <v>357.65</v>
       </c>
       <c r="I4" t="n">
-        <v>23711.58</v>
+        <v>22919.97</v>
       </c>
       <c r="J4" t="n">
-        <v>23579.11</v>
+        <v>22948.8</v>
       </c>
       <c r="K4" t="n">
-        <v>23976.52</v>
+        <v>23448.79</v>
       </c>
       <c r="L4" t="n">
-        <v>24373.93</v>
+        <v>23948.78</v>
       </c>
       <c r="M4" t="n">
-        <v>24506.4</v>
+        <v>24213.19</v>
       </c>
       <c r="N4" t="n">
-        <v>24638.87</v>
+        <v>24477.6</v>
       </c>
       <c r="O4" t="n">
-        <v>25301.22</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>25213.17</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -879,77 +879,79 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24035.19</v>
+        <v>24332.85</v>
       </c>
       <c r="C5" t="n">
-        <v>24384.24</v>
+        <v>24348.59</v>
       </c>
       <c r="D5" t="n">
-        <v>24026.59</v>
+        <v>23922.95</v>
       </c>
       <c r="E5" t="n">
-        <v>24239.89</v>
+        <v>23958.3</v>
       </c>
       <c r="F5" t="n">
-        <v>408.9</v>
+        <v>-281.59</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0172</v>
+        <v>-0.0116</v>
       </c>
       <c r="H5" t="n">
-        <v>357.65</v>
+        <v>425.64</v>
       </c>
       <c r="I5" t="n">
-        <v>22919.97</v>
+        <v>23668.94</v>
       </c>
       <c r="J5" t="n">
-        <v>22948.8</v>
+        <v>23899.48</v>
       </c>
       <c r="K5" t="n">
-        <v>23448.79</v>
+        <v>24061.07</v>
       </c>
       <c r="L5" t="n">
-        <v>23948.78</v>
+        <v>24222.65</v>
       </c>
       <c r="M5" t="n">
-        <v>24213.19</v>
+        <v>24418.72</v>
       </c>
       <c r="N5" t="n">
-        <v>24477.6</v>
+        <v>24614.78</v>
       </c>
       <c r="O5" t="n">
-        <v>25213.17</v>
+        <v>24741.89</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -963,66 +965,66 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24332.85</v>
+        <v>23990.34</v>
       </c>
       <c r="C6" t="n">
-        <v>24348.59</v>
+        <v>24248.67</v>
       </c>
       <c r="D6" t="n">
-        <v>23922.95</v>
+        <v>23452.89</v>
       </c>
       <c r="E6" t="n">
-        <v>23958.3</v>
+        <v>23569.96</v>
       </c>
       <c r="F6" t="n">
-        <v>-281.59</v>
+        <v>-388.34</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0162</v>
       </c>
       <c r="H6" t="n">
-        <v>425.64</v>
+        <v>795.78</v>
       </c>
       <c r="I6" t="n">
-        <v>23668.94</v>
+        <v>23497.31</v>
       </c>
       <c r="J6" t="n">
-        <v>23899.48</v>
+        <v>23443.93</v>
       </c>
       <c r="K6" t="n">
-        <v>24061.07</v>
+        <v>23745.48</v>
       </c>
       <c r="L6" t="n">
-        <v>24222.65</v>
+        <v>24047.04</v>
       </c>
       <c r="M6" t="n">
-        <v>24418.72</v>
+        <v>24171.12</v>
       </c>
       <c r="N6" t="n">
-        <v>24614.78</v>
+        <v>24295.21</v>
       </c>
       <c r="O6" t="n">
-        <v>24741.89</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>24774.23</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -1033,8 +1035,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1056,77 +1060,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23990.34</v>
+        <v>23925.36</v>
       </c>
       <c r="C7" t="n">
-        <v>24248.67</v>
+        <v>24441.28</v>
       </c>
       <c r="D7" t="n">
-        <v>23452.89</v>
+        <v>23609.06</v>
       </c>
       <c r="E7" t="n">
-        <v>23569.96</v>
+        <v>23876.55</v>
       </c>
       <c r="F7" t="n">
-        <v>-388.34</v>
+        <v>306.59</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.013</v>
       </c>
       <c r="H7" t="n">
-        <v>795.78</v>
+        <v>832.22</v>
       </c>
       <c r="I7" t="n">
-        <v>23497.31</v>
+        <v>22657.11</v>
       </c>
       <c r="J7" t="n">
-        <v>23443.93</v>
+        <v>22633.77</v>
       </c>
       <c r="K7" t="n">
-        <v>23745.48</v>
+        <v>23172.07</v>
       </c>
       <c r="L7" t="n">
-        <v>24047.04</v>
+        <v>23710.37</v>
       </c>
       <c r="M7" t="n">
-        <v>24171.12</v>
+        <v>23967.85</v>
       </c>
       <c r="N7" t="n">
-        <v>24295.21</v>
+        <v>24225.33</v>
       </c>
       <c r="O7" t="n">
-        <v>24774.23</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>25044.45</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1135,84 +1137,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23925.36</v>
+        <v>23890.48</v>
       </c>
       <c r="C8" t="n">
-        <v>24441.28</v>
+        <v>23928.48</v>
       </c>
       <c r="D8" t="n">
-        <v>23609.06</v>
+        <v>22943.06</v>
       </c>
       <c r="E8" t="n">
-        <v>23876.55</v>
+        <v>23091.87</v>
       </c>
       <c r="F8" t="n">
-        <v>306.59</v>
+        <v>-784.6799999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0329</v>
       </c>
       <c r="H8" t="n">
-        <v>832.22</v>
+        <v>985.42</v>
       </c>
       <c r="I8" t="n">
-        <v>22657.11</v>
+        <v>22776.84</v>
       </c>
       <c r="J8" t="n">
-        <v>22633.77</v>
+        <v>22970.02</v>
       </c>
       <c r="K8" t="n">
-        <v>23172.07</v>
+        <v>23460.44</v>
       </c>
       <c r="L8" t="n">
-        <v>23710.37</v>
+        <v>23950.86</v>
       </c>
       <c r="M8" t="n">
-        <v>23967.85</v>
+        <v>24292.66</v>
       </c>
       <c r="N8" t="n">
-        <v>24225.33</v>
+        <v>24634.46</v>
       </c>
       <c r="O8" t="n">
-        <v>25044.45</v>
+        <v>25273.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1221,80 +1219,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23890.48</v>
+        <v>23280.32</v>
       </c>
       <c r="C9" t="n">
-        <v>23928.48</v>
+        <v>23883.98</v>
       </c>
       <c r="D9" t="n">
-        <v>22943.06</v>
+        <v>23139.27</v>
       </c>
       <c r="E9" t="n">
-        <v>23091.87</v>
+        <v>23836.79</v>
       </c>
       <c r="F9" t="n">
-        <v>-784.6799999999999</v>
+        <v>744.92</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0329</v>
+        <v>0.0323</v>
       </c>
       <c r="H9" t="n">
-        <v>985.42</v>
+        <v>744.71</v>
       </c>
       <c r="I9" t="n">
-        <v>22776.84</v>
+        <v>21957.64</v>
       </c>
       <c r="J9" t="n">
-        <v>22970.02</v>
+        <v>21934.5</v>
       </c>
       <c r="K9" t="n">
-        <v>23460.44</v>
+        <v>22599.16</v>
       </c>
       <c r="L9" t="n">
-        <v>23950.86</v>
+        <v>23263.82</v>
       </c>
       <c r="M9" t="n">
-        <v>24292.66</v>
+        <v>23584.58</v>
       </c>
       <c r="N9" t="n">
-        <v>24634.46</v>
+        <v>23905.34</v>
       </c>
       <c r="O9" t="n">
-        <v>25273.5</v>
+        <v>24913.9</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1305,57 +1307,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23280.32</v>
+        <v>23731.29</v>
       </c>
       <c r="C10" t="n">
-        <v>23883.98</v>
+        <v>24130.92</v>
       </c>
       <c r="D10" t="n">
-        <v>23139.27</v>
+        <v>23433.48</v>
       </c>
       <c r="E10" t="n">
-        <v>23836.79</v>
+        <v>24028.14</v>
       </c>
       <c r="F10" t="n">
-        <v>744.92</v>
+        <v>191.35</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.008</v>
       </c>
       <c r="H10" t="n">
-        <v>744.71</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>21957.64</v>
+        <v>22394.56</v>
       </c>
       <c r="J10" t="n">
-        <v>21934.5</v>
+        <v>23254.66</v>
       </c>
       <c r="K10" t="n">
-        <v>22599.16</v>
+        <v>23464.43</v>
       </c>
       <c r="L10" t="n">
-        <v>23263.82</v>
+        <v>23674.21</v>
       </c>
       <c r="M10" t="n">
-        <v>23584.58</v>
+        <v>24209.14</v>
       </c>
       <c r="N10" t="n">
-        <v>23905.34</v>
+        <v>24744.08</v>
       </c>
       <c r="O10" t="n">
-        <v>24913.9</v>
+        <v>24628.69</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,8 +1365,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1373,14 +1377,12 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1389,59 +1391,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23731.29</v>
+        <v>24015.97</v>
       </c>
       <c r="C11" t="n">
-        <v>24130.92</v>
+        <v>24474.62</v>
       </c>
       <c r="D11" t="n">
-        <v>23433.48</v>
+        <v>23985.28</v>
       </c>
       <c r="E11" t="n">
-        <v>24028.14</v>
+        <v>24186.49</v>
       </c>
       <c r="F11" t="n">
-        <v>191.35</v>
+        <v>158.35</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0066</v>
       </c>
       <c r="H11" t="n">
-        <v>697.4400000000001</v>
+        <v>489.34</v>
       </c>
       <c r="I11" t="n">
-        <v>22394.56</v>
+        <v>22736.04</v>
       </c>
       <c r="J11" t="n">
-        <v>23254.66</v>
+        <v>23453.67</v>
       </c>
       <c r="K11" t="n">
-        <v>23464.43</v>
+        <v>23679.42</v>
       </c>
       <c r="L11" t="n">
-        <v>23674.21</v>
+        <v>23905.17</v>
       </c>
       <c r="M11" t="n">
-        <v>24209.14</v>
+        <v>24376.86</v>
       </c>
       <c r="N11" t="n">
-        <v>24744.08</v>
+        <v>24848.55</v>
       </c>
       <c r="O11" t="n">
-        <v>24628.69</v>
+        <v>24828.36</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,10 +1447,8 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1480,50 +1476,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24015.97</v>
+        <v>24297.64</v>
       </c>
       <c r="C12" t="n">
-        <v>24474.62</v>
+        <v>24318.3</v>
       </c>
       <c r="D12" t="n">
-        <v>23985.28</v>
+        <v>23923.97</v>
       </c>
       <c r="E12" t="n">
-        <v>24186.49</v>
+        <v>24288.4</v>
       </c>
       <c r="F12" t="n">
-        <v>158.35</v>
+        <v>101.91</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0066</v>
+        <v>0.0042</v>
       </c>
       <c r="H12" t="n">
-        <v>489.34</v>
+        <v>394.33</v>
       </c>
       <c r="I12" t="n">
-        <v>22736.04</v>
+        <v>23495.94</v>
       </c>
       <c r="J12" t="n">
-        <v>23453.67</v>
+        <v>23675.42</v>
       </c>
       <c r="K12" t="n">
-        <v>23679.42</v>
+        <v>23941.82</v>
       </c>
       <c r="L12" t="n">
-        <v>23905.17</v>
+        <v>24208.22</v>
       </c>
       <c r="M12" t="n">
-        <v>24376.86</v>
+        <v>24431.16</v>
       </c>
       <c r="N12" t="n">
-        <v>24848.55</v>
+        <v>24654.1</v>
       </c>
       <c r="O12" t="n">
-        <v>24828.36</v>
+        <v>24963.96</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1531,18 +1527,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1555,55 +1551,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24297.64</v>
+        <v>24291.85</v>
       </c>
       <c r="C13" t="n">
-        <v>24318.3</v>
+        <v>24362.01</v>
       </c>
       <c r="D13" t="n">
-        <v>23923.97</v>
+        <v>24203.37</v>
       </c>
       <c r="E13" t="n">
-        <v>24288.4</v>
+        <v>24340.06</v>
       </c>
       <c r="F13" t="n">
-        <v>101.91</v>
+        <v>51.66</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0021</v>
       </c>
       <c r="H13" t="n">
-        <v>394.33</v>
+        <v>158.64</v>
       </c>
       <c r="I13" t="n">
-        <v>23495.94</v>
+        <v>23529.64</v>
       </c>
       <c r="J13" t="n">
-        <v>23675.42</v>
+        <v>23977.7</v>
       </c>
       <c r="K13" t="n">
-        <v>23941.82</v>
+        <v>24091.24</v>
       </c>
       <c r="L13" t="n">
-        <v>24208.22</v>
+        <v>24204.77</v>
       </c>
       <c r="M13" t="n">
-        <v>24431.16</v>
+        <v>24485.57</v>
       </c>
       <c r="N13" t="n">
-        <v>24654.1</v>
+        <v>24766.36</v>
       </c>
       <c r="O13" t="n">
-        <v>24963.96</v>
+        <v>24712.63</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,10 +1611,8 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
@@ -1635,59 +1633,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24291.85</v>
+        <v>24370.94</v>
       </c>
       <c r="C14" t="n">
-        <v>24362.01</v>
+        <v>24676.79</v>
       </c>
       <c r="D14" t="n">
-        <v>24203.37</v>
+        <v>24253.73</v>
       </c>
       <c r="E14" t="n">
-        <v>24340.06</v>
+        <v>24539.34</v>
       </c>
       <c r="F14" t="n">
-        <v>51.66</v>
+        <v>199.28</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>158.64</v>
+        <v>423.06</v>
       </c>
       <c r="I14" t="n">
-        <v>23529.64</v>
+        <v>24044.73</v>
       </c>
       <c r="J14" t="n">
-        <v>23977.7</v>
+        <v>24210.11</v>
       </c>
       <c r="K14" t="n">
-        <v>24091.24</v>
+        <v>24260.74</v>
       </c>
       <c r="L14" t="n">
-        <v>24204.77</v>
+        <v>24311.38</v>
       </c>
       <c r="M14" t="n">
-        <v>24485.57</v>
+        <v>24419.38</v>
       </c>
       <c r="N14" t="n">
-        <v>24766.36</v>
+        <v>24527.39</v>
       </c>
       <c r="O14" t="n">
-        <v>24712.63</v>
+        <v>24520.65</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1695,22 +1689,30 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1722,50 +1724,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24370.94</v>
+        <v>24681.35</v>
       </c>
       <c r="C15" t="n">
-        <v>24676.79</v>
+        <v>25281.18</v>
       </c>
       <c r="D15" t="n">
-        <v>24253.73</v>
+        <v>24639.68</v>
       </c>
       <c r="E15" t="n">
-        <v>24539.34</v>
+        <v>25261.64</v>
       </c>
       <c r="F15" t="n">
-        <v>199.28</v>
+        <v>722.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H15" t="n">
-        <v>423.06</v>
+        <v>641.5</v>
       </c>
       <c r="I15" t="n">
-        <v>24044.73</v>
+        <v>23830.67</v>
       </c>
       <c r="J15" t="n">
-        <v>24210.11</v>
+        <v>24153.32</v>
       </c>
       <c r="K15" t="n">
-        <v>24260.74</v>
+        <v>24327.81</v>
       </c>
       <c r="L15" t="n">
-        <v>24311.38</v>
+        <v>24502.3</v>
       </c>
       <c r="M15" t="n">
-        <v>24419.38</v>
+        <v>24750.87</v>
       </c>
       <c r="N15" t="n">
-        <v>24527.39</v>
+        <v>24999.44</v>
       </c>
       <c r="O15" t="n">
-        <v>24520.65</v>
+        <v>25099.85</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,29 +1775,27 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -1808,50 +1808,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24681.35</v>
+        <v>25248.37</v>
       </c>
       <c r="C16" t="n">
-        <v>25281.18</v>
+        <v>25507.79</v>
       </c>
       <c r="D16" t="n">
-        <v>24639.68</v>
+        <v>25198.53</v>
       </c>
       <c r="E16" t="n">
-        <v>25261.64</v>
+        <v>25297.13</v>
       </c>
       <c r="F16" t="n">
-        <v>722.3</v>
+        <v>35.49</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0014</v>
       </c>
       <c r="H16" t="n">
-        <v>641.5</v>
+        <v>309.26</v>
       </c>
       <c r="I16" t="n">
-        <v>23830.67</v>
+        <v>23998.18</v>
       </c>
       <c r="J16" t="n">
-        <v>24153.32</v>
+        <v>24770.75</v>
       </c>
       <c r="K16" t="n">
-        <v>24327.81</v>
+        <v>24940.89</v>
       </c>
       <c r="L16" t="n">
-        <v>24502.3</v>
+        <v>25111.04</v>
       </c>
       <c r="M16" t="n">
-        <v>24750.87</v>
+        <v>25582.39</v>
       </c>
       <c r="N16" t="n">
-        <v>24999.44</v>
+        <v>26053.75</v>
       </c>
       <c r="O16" t="n">
-        <v>25099.85</v>
+        <v>25922.68</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1864,23 +1864,17 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1892,63 +1886,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25248.37</v>
+        <v>24940.47</v>
       </c>
       <c r="C17" t="n">
-        <v>25507.79</v>
+        <v>25070.61</v>
       </c>
       <c r="D17" t="n">
-        <v>25198.53</v>
+        <v>24349.54</v>
       </c>
       <c r="E17" t="n">
-        <v>25297.13</v>
+        <v>24900.71</v>
       </c>
       <c r="F17" t="n">
-        <v>35.49</v>
+        <v>-396.42</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0157</v>
       </c>
       <c r="H17" t="n">
-        <v>309.26</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>23998.18</v>
+        <v>24889.27</v>
       </c>
       <c r="J17" t="n">
-        <v>24770.75</v>
+        <v>24959.86</v>
       </c>
       <c r="K17" t="n">
-        <v>24940.89</v>
+        <v>25142.5</v>
       </c>
       <c r="L17" t="n">
-        <v>25111.04</v>
+        <v>25325.15</v>
       </c>
       <c r="M17" t="n">
-        <v>25582.39</v>
+        <v>25451.76</v>
       </c>
       <c r="N17" t="n">
-        <v>26053.75</v>
+        <v>25578.38</v>
       </c>
       <c r="O17" t="n">
-        <v>25922.68</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>25817.05</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1960,9 +1960,9 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1970,64 +1970,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24940.47</v>
+        <v>24890.3</v>
       </c>
       <c r="C18" t="n">
-        <v>25070.61</v>
+        <v>25020.22</v>
       </c>
       <c r="D18" t="n">
-        <v>24349.54</v>
+        <v>24266.33</v>
       </c>
       <c r="E18" t="n">
-        <v>24900.71</v>
+        <v>24538.81</v>
       </c>
       <c r="F18" t="n">
-        <v>-396.42</v>
+        <v>-361.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0145</v>
       </c>
       <c r="H18" t="n">
-        <v>721.0700000000001</v>
+        <v>753.89</v>
       </c>
       <c r="I18" t="n">
-        <v>24889.27</v>
+        <v>23628.47</v>
       </c>
       <c r="J18" t="n">
-        <v>24959.86</v>
+        <v>24274.96</v>
       </c>
       <c r="K18" t="n">
-        <v>25142.5</v>
+        <v>24540.18</v>
       </c>
       <c r="L18" t="n">
-        <v>25325.15</v>
+        <v>24805.39</v>
       </c>
       <c r="M18" t="n">
-        <v>25451.76</v>
+        <v>25261.25</v>
       </c>
       <c r="N18" t="n">
-        <v>25578.38</v>
+        <v>25717.1</v>
       </c>
       <c r="O18" t="n">
-        <v>25817.05</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>25791.68</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
@@ -2054,72 +2052,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24890.3</v>
+        <v>24392.09</v>
       </c>
       <c r="C19" t="n">
-        <v>25020.22</v>
+        <v>25098.71</v>
       </c>
       <c r="D19" t="n">
-        <v>24266.33</v>
+        <v>24272.62</v>
       </c>
       <c r="E19" t="n">
-        <v>24538.81</v>
+        <v>24721.46</v>
       </c>
       <c r="F19" t="n">
-        <v>-361.9</v>
+        <v>182.65</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0145</v>
+        <v>0.0074</v>
       </c>
       <c r="H19" t="n">
-        <v>753.89</v>
+        <v>826.09</v>
       </c>
       <c r="I19" t="n">
-        <v>23628.47</v>
+        <v>23512.44</v>
       </c>
       <c r="J19" t="n">
-        <v>24274.96</v>
+        <v>23732.69</v>
       </c>
       <c r="K19" t="n">
-        <v>24540.18</v>
+        <v>24161.87</v>
       </c>
       <c r="L19" t="n">
-        <v>24805.39</v>
+        <v>24591.04</v>
       </c>
       <c r="M19" t="n">
-        <v>25261.25</v>
+        <v>24915.76</v>
       </c>
       <c r="N19" t="n">
-        <v>25717.1</v>
+        <v>25240.47</v>
       </c>
       <c r="O19" t="n">
-        <v>25791.68</v>
+        <v>25774.11</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2131,55 +2127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24392.09</v>
+        <v>24860.67</v>
       </c>
       <c r="C20" t="n">
-        <v>25098.71</v>
+        <v>25239.01</v>
       </c>
       <c r="D20" t="n">
-        <v>24272.62</v>
+        <v>24714.89</v>
       </c>
       <c r="E20" t="n">
-        <v>24721.46</v>
+        <v>24914.88</v>
       </c>
       <c r="F20" t="n">
-        <v>182.65</v>
+        <v>193.42</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0078</v>
       </c>
       <c r="H20" t="n">
-        <v>826.09</v>
+        <v>524.12</v>
       </c>
       <c r="I20" t="n">
-        <v>23512.44</v>
+        <v>23446.53</v>
       </c>
       <c r="J20" t="n">
-        <v>23732.69</v>
+        <v>23913.27</v>
       </c>
       <c r="K20" t="n">
-        <v>24161.87</v>
+        <v>24308.42</v>
       </c>
       <c r="L20" t="n">
-        <v>24591.04</v>
+        <v>24703.56</v>
       </c>
       <c r="M20" t="n">
-        <v>24915.76</v>
+        <v>25134.51</v>
       </c>
       <c r="N20" t="n">
-        <v>25240.47</v>
+        <v>25565.45</v>
       </c>
       <c r="O20" t="n">
-        <v>25774.11</v>
+        <v>25924.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2220,50 +2220,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24860.67</v>
+        <v>24988.61</v>
       </c>
       <c r="C21" t="n">
-        <v>25239.01</v>
+        <v>25331.06</v>
       </c>
       <c r="D21" t="n">
-        <v>24714.89</v>
+        <v>24734.04</v>
       </c>
       <c r="E21" t="n">
-        <v>24914.88</v>
+        <v>25260.69</v>
       </c>
       <c r="F21" t="n">
-        <v>193.42</v>
+        <v>345.81</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0078</v>
+        <v>0.0139</v>
       </c>
       <c r="H21" t="n">
-        <v>524.12</v>
+        <v>597.02</v>
       </c>
       <c r="I21" t="n">
-        <v>23446.53</v>
+        <v>24190.77</v>
       </c>
       <c r="J21" t="n">
-        <v>23913.27</v>
+        <v>24359.73</v>
       </c>
       <c r="K21" t="n">
-        <v>24308.42</v>
+        <v>24652.82</v>
       </c>
       <c r="L21" t="n">
-        <v>24703.56</v>
+        <v>24945.92</v>
       </c>
       <c r="M21" t="n">
-        <v>25134.51</v>
+        <v>25176.94</v>
       </c>
       <c r="N21" t="n">
-        <v>25565.45</v>
+        <v>25407.97</v>
       </c>
       <c r="O21" t="n">
-        <v>25924.8</v>
+        <v>25763.13</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2304,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24988.61</v>
+        <v>25114.39</v>
       </c>
       <c r="C22" t="n">
-        <v>25331.06</v>
+        <v>25405.97</v>
       </c>
       <c r="D22" t="n">
-        <v>24734.04</v>
+        <v>24878.1</v>
       </c>
       <c r="E22" t="n">
-        <v>25260.69</v>
+        <v>25284.26</v>
       </c>
       <c r="F22" t="n">
-        <v>345.81</v>
+        <v>23.57</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0009</v>
       </c>
       <c r="H22" t="n">
-        <v>597.02</v>
+        <v>527.87</v>
       </c>
       <c r="I22" t="n">
-        <v>24190.77</v>
+        <v>24137.02</v>
       </c>
       <c r="J22" t="n">
-        <v>24359.73</v>
+        <v>24777.74</v>
       </c>
       <c r="K22" t="n">
-        <v>24652.82</v>
+        <v>24962.18</v>
       </c>
       <c r="L22" t="n">
-        <v>24945.92</v>
+        <v>25146.62</v>
       </c>
       <c r="M22" t="n">
-        <v>25176.94</v>
+        <v>25559.2</v>
       </c>
       <c r="N22" t="n">
-        <v>25407.97</v>
+        <v>25971.78</v>
       </c>
       <c r="O22" t="n">
-        <v>25763.13</v>
+        <v>25928.08</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,18 +2355,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2388,65 +2388,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25114.39</v>
+        <v>24695.44</v>
       </c>
       <c r="C23" t="n">
-        <v>25405.97</v>
+        <v>24897.61</v>
       </c>
       <c r="D23" t="n">
-        <v>24878.1</v>
+        <v>23342.88</v>
       </c>
       <c r="E23" t="n">
-        <v>25284.26</v>
+        <v>23591.03</v>
       </c>
       <c r="F23" t="n">
-        <v>23.57</v>
+        <v>-1693.23</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0009</v>
+        <v>-0.067</v>
       </c>
       <c r="H23" t="n">
-        <v>527.87</v>
+        <v>1554.73</v>
       </c>
       <c r="I23" t="n">
-        <v>24137.02</v>
+        <v>24350.23</v>
       </c>
       <c r="J23" t="n">
-        <v>24777.74</v>
+        <v>24827.5</v>
       </c>
       <c r="K23" t="n">
-        <v>24962.18</v>
+        <v>25020.32</v>
       </c>
       <c r="L23" t="n">
-        <v>25146.62</v>
+        <v>25213.15</v>
       </c>
       <c r="M23" t="n">
-        <v>25559.2</v>
+        <v>25548.2</v>
       </c>
       <c r="N23" t="n">
-        <v>25971.78</v>
+        <v>25883.24</v>
       </c>
       <c r="O23" t="n">
-        <v>25928.08</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>25933.84</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2463,78 +2467,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24695.44</v>
+        <v>22998.94</v>
       </c>
       <c r="C24" t="n">
-        <v>24897.61</v>
+        <v>24061.15</v>
       </c>
       <c r="D24" t="n">
-        <v>23342.88</v>
+        <v>22927.55</v>
       </c>
       <c r="E24" t="n">
-        <v>23591.03</v>
+        <v>23447.29</v>
       </c>
       <c r="F24" t="n">
-        <v>-1693.23</v>
+        <v>-143.74</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0061</v>
       </c>
       <c r="H24" t="n">
-        <v>1554.73</v>
+        <v>1133.6</v>
       </c>
       <c r="I24" t="n">
-        <v>24350.23</v>
+        <v>21788.15</v>
       </c>
       <c r="J24" t="n">
-        <v>24827.5</v>
+        <v>21771.69</v>
       </c>
       <c r="K24" t="n">
-        <v>25020.32</v>
+        <v>22813.67</v>
       </c>
       <c r="L24" t="n">
-        <v>25213.15</v>
+        <v>23855.64</v>
       </c>
       <c r="M24" t="n">
-        <v>25548.2</v>
+        <v>24368.39</v>
       </c>
       <c r="N24" t="n">
-        <v>25883.24</v>
+        <v>24881.15</v>
       </c>
       <c r="O24" t="n">
-        <v>25933.84</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26452.34</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2556,63 +2550,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22998.94</v>
+        <v>23480.5</v>
       </c>
       <c r="C25" t="n">
-        <v>24061.15</v>
+        <v>23957.1</v>
       </c>
       <c r="D25" t="n">
-        <v>22927.55</v>
+        <v>22369.47</v>
       </c>
       <c r="E25" t="n">
-        <v>23447.29</v>
+        <v>22380.19</v>
       </c>
       <c r="F25" t="n">
-        <v>-143.74</v>
+        <v>-1067.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0455</v>
       </c>
       <c r="H25" t="n">
-        <v>1133.6</v>
+        <v>1587.63</v>
       </c>
       <c r="I25" t="n">
-        <v>21788.15</v>
+        <v>21793.95</v>
       </c>
       <c r="J25" t="n">
-        <v>21771.69</v>
+        <v>22290.16</v>
       </c>
       <c r="K25" t="n">
-        <v>22813.67</v>
+        <v>22880.49</v>
       </c>
       <c r="L25" t="n">
-        <v>23855.64</v>
+        <v>23470.82</v>
       </c>
       <c r="M25" t="n">
-        <v>24368.39</v>
+        <v>24014.09</v>
       </c>
       <c r="N25" t="n">
-        <v>24881.15</v>
+        <v>24557.36</v>
       </c>
       <c r="O25" t="n">
-        <v>26452.34</v>
+        <v>25194.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2634,71 +2632,69 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23480.5</v>
+        <v>21947.82</v>
       </c>
       <c r="C26" t="n">
-        <v>23957.1</v>
+        <v>23178.7</v>
       </c>
       <c r="D26" t="n">
-        <v>22369.47</v>
+        <v>21863.81</v>
       </c>
       <c r="E26" t="n">
-        <v>22380.19</v>
+        <v>22300.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-1067.1</v>
+        <v>-79.44</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0035</v>
       </c>
       <c r="H26" t="n">
-        <v>1587.63</v>
+        <v>1314.89</v>
       </c>
       <c r="I26" t="n">
-        <v>21793.95</v>
+        <v>20781.84</v>
       </c>
       <c r="J26" t="n">
-        <v>22290.16</v>
+        <v>20401.01</v>
       </c>
       <c r="K26" t="n">
-        <v>22880.49</v>
+        <v>21586.38</v>
       </c>
       <c r="L26" t="n">
-        <v>23470.82</v>
+        <v>22771.74</v>
       </c>
       <c r="M26" t="n">
-        <v>24014.09</v>
+        <v>23174</v>
       </c>
       <c r="N26" t="n">
-        <v>24557.36</v>
+        <v>23576.27</v>
       </c>
       <c r="O26" t="n">
-        <v>25194.75</v>
+        <v>25544.73</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2716,50 +2712,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21947.82</v>
+        <v>22213.86</v>
       </c>
       <c r="C27" t="n">
-        <v>23178.7</v>
+        <v>23377.65</v>
       </c>
       <c r="D27" t="n">
-        <v>21863.81</v>
+        <v>22209.45</v>
       </c>
       <c r="E27" t="n">
-        <v>22300.75</v>
+        <v>23168.08</v>
       </c>
       <c r="F27" t="n">
-        <v>-79.44</v>
+        <v>867.33</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0035</v>
+        <v>0.0389</v>
       </c>
       <c r="H27" t="n">
-        <v>1314.89</v>
+        <v>1168.2</v>
       </c>
       <c r="I27" t="n">
-        <v>20781.84</v>
+        <v>20548.92</v>
       </c>
       <c r="J27" t="n">
-        <v>20401.01</v>
+        <v>20875.61</v>
       </c>
       <c r="K27" t="n">
-        <v>21586.38</v>
+        <v>21643.31</v>
       </c>
       <c r="L27" t="n">
-        <v>22771.74</v>
+        <v>22411</v>
       </c>
       <c r="M27" t="n">
-        <v>23174</v>
+        <v>22958.19</v>
       </c>
       <c r="N27" t="n">
-        <v>23576.27</v>
+        <v>23505.39</v>
       </c>
       <c r="O27" t="n">
-        <v>25544.73</v>
+        <v>24493.59</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,14 +2766,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2791,55 +2787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22213.86</v>
+        <v>23181.65</v>
       </c>
       <c r="C28" t="n">
-        <v>23377.65</v>
+        <v>24163.91</v>
       </c>
       <c r="D28" t="n">
-        <v>22209.45</v>
+        <v>22842.14</v>
       </c>
       <c r="E28" t="n">
-        <v>23168.08</v>
+        <v>23803.95</v>
       </c>
       <c r="F28" t="n">
-        <v>867.33</v>
+        <v>635.87</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0274</v>
       </c>
       <c r="H28" t="n">
-        <v>1168.2</v>
+        <v>1321.77</v>
       </c>
       <c r="I28" t="n">
-        <v>20548.92</v>
+        <v>21041.25</v>
       </c>
       <c r="J28" t="n">
-        <v>20875.61</v>
+        <v>22187.14</v>
       </c>
       <c r="K28" t="n">
-        <v>21643.31</v>
+        <v>22583.98</v>
       </c>
       <c r="L28" t="n">
-        <v>22411</v>
+        <v>22980.81</v>
       </c>
       <c r="M28" t="n">
-        <v>22958.19</v>
+        <v>23752.18</v>
       </c>
       <c r="N28" t="n">
-        <v>23505.39</v>
+        <v>24523.55</v>
       </c>
       <c r="O28" t="n">
-        <v>24493.59</v>
+        <v>24545.85</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2880,50 +2880,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23181.65</v>
+        <v>23562.19</v>
       </c>
       <c r="C29" t="n">
-        <v>24163.91</v>
+        <v>24792.46</v>
       </c>
       <c r="D29" t="n">
-        <v>22842.14</v>
+        <v>23482.01</v>
       </c>
       <c r="E29" t="n">
-        <v>23803.95</v>
+        <v>24702.24</v>
       </c>
       <c r="F29" t="n">
-        <v>635.87</v>
+        <v>898.29</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0377</v>
       </c>
       <c r="H29" t="n">
-        <v>1321.77</v>
+        <v>1310.45</v>
       </c>
       <c r="I29" t="n">
-        <v>21041.25</v>
+        <v>21520.37</v>
       </c>
       <c r="J29" t="n">
-        <v>22187.14</v>
+        <v>22632.64</v>
       </c>
       <c r="K29" t="n">
-        <v>22583.98</v>
+        <v>23143.06</v>
       </c>
       <c r="L29" t="n">
-        <v>22980.81</v>
+        <v>23653.49</v>
       </c>
       <c r="M29" t="n">
-        <v>23752.18</v>
+        <v>24464.83</v>
       </c>
       <c r="N29" t="n">
-        <v>24523.55</v>
+        <v>25276.18</v>
       </c>
       <c r="O29" t="n">
-        <v>24545.85</v>
+        <v>25485.68</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2964,50 +2964,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23562.19</v>
+        <v>24385.04</v>
       </c>
       <c r="C30" t="n">
-        <v>24792.46</v>
+        <v>24606.84</v>
       </c>
       <c r="D30" t="n">
-        <v>23482.01</v>
+        <v>23991.78</v>
       </c>
       <c r="E30" t="n">
-        <v>24702.24</v>
+        <v>24128.98</v>
       </c>
       <c r="F30" t="n">
-        <v>898.29</v>
+        <v>-573.26</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.0232</v>
       </c>
       <c r="H30" t="n">
-        <v>1310.45</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>21520.37</v>
+        <v>22171.56</v>
       </c>
       <c r="J30" t="n">
-        <v>22632.64</v>
+        <v>23674.29</v>
       </c>
       <c r="K30" t="n">
-        <v>23143.06</v>
+        <v>24047.01</v>
       </c>
       <c r="L30" t="n">
-        <v>23653.49</v>
+        <v>24419.74</v>
       </c>
       <c r="M30" t="n">
-        <v>24464.83</v>
+        <v>25357.47</v>
       </c>
       <c r="N30" t="n">
-        <v>25276.18</v>
+        <v>26295.19</v>
       </c>
       <c r="O30" t="n">
-        <v>25485.68</v>
+        <v>26102.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3015,19 +3015,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3041,57 +3041,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24385.04</v>
+        <v>24196.43</v>
       </c>
       <c r="C31" t="n">
-        <v>24606.84</v>
+        <v>24382.32</v>
       </c>
       <c r="D31" t="n">
-        <v>23991.78</v>
+        <v>23715.71</v>
       </c>
       <c r="E31" t="n">
-        <v>24128.98</v>
+        <v>24292.38</v>
       </c>
       <c r="F31" t="n">
-        <v>-573.26</v>
+        <v>163.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0232</v>
+        <v>0.0068</v>
       </c>
       <c r="H31" t="n">
-        <v>615.0599999999999</v>
+        <v>666.61</v>
       </c>
       <c r="I31" t="n">
-        <v>22171.56</v>
+        <v>23376.72</v>
       </c>
       <c r="J31" t="n">
-        <v>23674.29</v>
+        <v>23428.76</v>
       </c>
       <c r="K31" t="n">
-        <v>24047.01</v>
+        <v>23821.45</v>
       </c>
       <c r="L31" t="n">
-        <v>24419.74</v>
+        <v>24214.15</v>
       </c>
       <c r="M31" t="n">
-        <v>25357.47</v>
+        <v>24436.51</v>
       </c>
       <c r="N31" t="n">
-        <v>26295.19</v>
+        <v>24658.88</v>
       </c>
       <c r="O31" t="n">
-        <v>26102.91</v>
+        <v>25221.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3132,50 +3132,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24196.43</v>
+        <v>24274.5</v>
       </c>
       <c r="C32" t="n">
-        <v>24382.32</v>
+        <v>25152.51</v>
       </c>
       <c r="D32" t="n">
-        <v>23715.71</v>
+        <v>23974.74</v>
       </c>
       <c r="E32" t="n">
-        <v>24292.38</v>
+        <v>24338.63</v>
       </c>
       <c r="F32" t="n">
-        <v>163.4</v>
+        <v>46.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0019</v>
       </c>
       <c r="H32" t="n">
-        <v>666.61</v>
+        <v>1177.77</v>
       </c>
       <c r="I32" t="n">
-        <v>23376.72</v>
+        <v>23049.1</v>
       </c>
       <c r="J32" t="n">
-        <v>23428.76</v>
+        <v>23747.45</v>
       </c>
       <c r="K32" t="n">
-        <v>23821.45</v>
+        <v>23959.08</v>
       </c>
       <c r="L32" t="n">
-        <v>24214.15</v>
+        <v>24170.7</v>
       </c>
       <c r="M32" t="n">
-        <v>24436.51</v>
+        <v>24625.69</v>
       </c>
       <c r="N32" t="n">
-        <v>24658.88</v>
+        <v>25080.67</v>
       </c>
       <c r="O32" t="n">
-        <v>25221.9</v>
+        <v>25048.93</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,24 +3183,28 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
@@ -3209,57 +3213,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24274.5</v>
+        <v>24333.31</v>
       </c>
       <c r="C33" t="n">
-        <v>25152.51</v>
+        <v>24492.95</v>
       </c>
       <c r="D33" t="n">
-        <v>23974.74</v>
+        <v>23917.63</v>
       </c>
       <c r="E33" t="n">
-        <v>24338.63</v>
+        <v>23950.57</v>
       </c>
       <c r="F33" t="n">
-        <v>46.25</v>
+        <v>-388.06</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0159</v>
       </c>
       <c r="H33" t="n">
-        <v>1177.77</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>23049.1</v>
+        <v>22796.97</v>
       </c>
       <c r="J33" t="n">
-        <v>23747.45</v>
+        <v>23048.36</v>
       </c>
       <c r="K33" t="n">
-        <v>23959.08</v>
+        <v>23749.75</v>
       </c>
       <c r="L33" t="n">
-        <v>24170.7</v>
+        <v>24451.13</v>
       </c>
       <c r="M33" t="n">
-        <v>24625.69</v>
+        <v>24927.52</v>
       </c>
       <c r="N33" t="n">
-        <v>25080.67</v>
+        <v>25403.9</v>
       </c>
       <c r="O33" t="n">
-        <v>25048.93</v>
+        <v>26330.28</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3267,87 +3271,79 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24333.31</v>
+        <v>23833.11</v>
       </c>
       <c r="C34" t="n">
-        <v>24492.95</v>
+        <v>24943.75</v>
       </c>
       <c r="D34" t="n">
-        <v>23917.63</v>
+        <v>23797.33</v>
       </c>
       <c r="E34" t="n">
-        <v>23950.57</v>
+        <v>24888.56</v>
       </c>
       <c r="F34" t="n">
-        <v>-388.06</v>
+        <v>937.99</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0159</v>
+        <v>0.0392</v>
       </c>
       <c r="H34" t="n">
-        <v>575.3200000000001</v>
+        <v>1146.42</v>
       </c>
       <c r="I34" t="n">
-        <v>22796.97</v>
+        <v>23342.31</v>
       </c>
       <c r="J34" t="n">
-        <v>23048.36</v>
+        <v>23247.89</v>
       </c>
       <c r="K34" t="n">
-        <v>23749.75</v>
+        <v>23662.91</v>
       </c>
       <c r="L34" t="n">
-        <v>24451.13</v>
+        <v>24077.93</v>
       </c>
       <c r="M34" t="n">
-        <v>24927.52</v>
+        <v>24238.23</v>
       </c>
       <c r="N34" t="n">
-        <v>25403.9</v>
+        <v>24398.53</v>
       </c>
       <c r="O34" t="n">
-        <v>26330.28</v>
+        <v>25068.27</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,79 +3351,87 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23833.11</v>
+        <v>25181.27</v>
       </c>
       <c r="C35" t="n">
-        <v>24943.75</v>
+        <v>25438.41</v>
       </c>
       <c r="D35" t="n">
-        <v>23797.33</v>
+        <v>24973.25</v>
       </c>
       <c r="E35" t="n">
-        <v>24888.56</v>
+        <v>25104.7</v>
       </c>
       <c r="F35" t="n">
-        <v>937.99</v>
+        <v>216.14</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0392</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>1146.42</v>
+        <v>465.16</v>
       </c>
       <c r="I35" t="n">
-        <v>23342.31</v>
+        <v>22650.91</v>
       </c>
       <c r="J35" t="n">
-        <v>23247.89</v>
+        <v>24001.15</v>
       </c>
       <c r="K35" t="n">
-        <v>23662.91</v>
+        <v>24315.35</v>
       </c>
       <c r="L35" t="n">
-        <v>24077.93</v>
+        <v>24629.55</v>
       </c>
       <c r="M35" t="n">
-        <v>24238.23</v>
+        <v>25461.77</v>
       </c>
       <c r="N35" t="n">
-        <v>24398.53</v>
+        <v>26293.99</v>
       </c>
       <c r="O35" t="n">
-        <v>25068.27</v>
+        <v>26090.17</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3445,77 +3449,69 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25181.27</v>
+        <v>25083.24</v>
       </c>
       <c r="C36" t="n">
-        <v>25438.41</v>
+        <v>25362.83</v>
       </c>
       <c r="D36" t="n">
-        <v>24973.25</v>
+        <v>24756.47</v>
       </c>
       <c r="E36" t="n">
-        <v>25104.7</v>
+        <v>24759.05</v>
       </c>
       <c r="F36" t="n">
-        <v>216.14</v>
+        <v>-345.65</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="H36" t="n">
-        <v>465.16</v>
+        <v>606.36</v>
       </c>
       <c r="I36" t="n">
-        <v>22650.91</v>
+        <v>24508.09</v>
       </c>
       <c r="J36" t="n">
-        <v>24001.15</v>
+        <v>24588.97</v>
       </c>
       <c r="K36" t="n">
-        <v>24315.35</v>
+        <v>24872.12</v>
       </c>
       <c r="L36" t="n">
-        <v>24629.55</v>
+        <v>25155.26</v>
       </c>
       <c r="M36" t="n">
-        <v>25461.77</v>
+        <v>25337.28</v>
       </c>
       <c r="N36" t="n">
-        <v>26293.99</v>
+        <v>25519.29</v>
       </c>
       <c r="O36" t="n">
-        <v>26090.17</v>
+        <v>25903.57</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3523,17 +3519,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3547,58 +3545,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25083.24</v>
+        <v>24447.32</v>
       </c>
       <c r="C37" t="n">
-        <v>25362.83</v>
+        <v>24820.95</v>
       </c>
       <c r="D37" t="n">
-        <v>24756.47</v>
+        <v>24043.52</v>
       </c>
       <c r="E37" t="n">
-        <v>24759.05</v>
+        <v>24635.3</v>
       </c>
       <c r="F37" t="n">
-        <v>-345.65</v>
+        <v>-123.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.005</v>
       </c>
       <c r="H37" t="n">
-        <v>606.36</v>
+        <v>777.4299999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>24508.09</v>
+        <v>24150.11</v>
       </c>
       <c r="J37" t="n">
-        <v>24588.97</v>
+        <v>24002.39</v>
       </c>
       <c r="K37" t="n">
-        <v>24872.12</v>
+        <v>24455.87</v>
       </c>
       <c r="L37" t="n">
-        <v>25155.26</v>
+        <v>24909.35</v>
       </c>
       <c r="M37" t="n">
-        <v>25337.28</v>
+        <v>25062.23</v>
       </c>
       <c r="N37" t="n">
-        <v>25519.29</v>
+        <v>25215.11</v>
       </c>
       <c r="O37" t="n">
-        <v>25903.57</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
+        <v>25969.19</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q37" s="6" t="n">
         <v/>
@@ -3613,10 +3617,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3638,72 +3640,70 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24447.32</v>
+        <v>25068.37</v>
       </c>
       <c r="C38" t="n">
-        <v>24820.95</v>
+        <v>25173.02</v>
       </c>
       <c r="D38" t="n">
-        <v>24043.52</v>
+        <v>24763.53</v>
       </c>
       <c r="E38" t="n">
-        <v>24635.3</v>
+        <v>24985.82</v>
       </c>
       <c r="F38" t="n">
-        <v>-123.75</v>
+        <v>350.52</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0142</v>
       </c>
       <c r="H38" t="n">
-        <v>777.4299999999999</v>
+        <v>409.49</v>
       </c>
       <c r="I38" t="n">
-        <v>24150.11</v>
+        <v>23266.09</v>
       </c>
       <c r="J38" t="n">
-        <v>24002.39</v>
+        <v>23959.4</v>
       </c>
       <c r="K38" t="n">
-        <v>24455.87</v>
+        <v>24246.59</v>
       </c>
       <c r="L38" t="n">
-        <v>24909.35</v>
+        <v>24533.77</v>
       </c>
       <c r="M38" t="n">
-        <v>25062.23</v>
+        <v>25024.02</v>
       </c>
       <c r="N38" t="n">
-        <v>25215.11</v>
+        <v>25514.26</v>
       </c>
       <c r="O38" t="n">
-        <v>25969.19</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>25598.38</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3715,79 +3715,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25068.37</v>
+        <v>25035.93</v>
       </c>
       <c r="C39" t="n">
-        <v>25173.02</v>
+        <v>25176.21</v>
       </c>
       <c r="D39" t="n">
-        <v>24763.53</v>
+        <v>24547.7</v>
       </c>
       <c r="E39" t="n">
-        <v>24985.82</v>
+        <v>24671.22</v>
       </c>
       <c r="F39" t="n">
-        <v>350.52</v>
+        <v>-314.6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0142</v>
+        <v>-0.0126</v>
       </c>
       <c r="H39" t="n">
-        <v>409.49</v>
+        <v>628.51</v>
       </c>
       <c r="I39" t="n">
-        <v>23266.09</v>
+        <v>24354.04</v>
       </c>
       <c r="J39" t="n">
-        <v>23959.4</v>
+        <v>24585.1</v>
       </c>
       <c r="K39" t="n">
-        <v>24246.59</v>
+        <v>24781.08</v>
       </c>
       <c r="L39" t="n">
-        <v>24533.77</v>
+        <v>24977.05</v>
       </c>
       <c r="M39" t="n">
-        <v>25024.02</v>
+        <v>25190.57</v>
       </c>
       <c r="N39" t="n">
-        <v>25514.26</v>
+        <v>25404.08</v>
       </c>
       <c r="O39" t="n">
-        <v>25598.38</v>
+        <v>25582.51</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3799,141 +3797,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25035.93</v>
+        <v>24724.34</v>
       </c>
       <c r="C40" t="n">
-        <v>25176.21</v>
+        <v>25826.78</v>
       </c>
       <c r="D40" t="n">
-        <v>24547.7</v>
+        <v>24556.78</v>
       </c>
       <c r="E40" t="n">
-        <v>24671.22</v>
+        <v>25779.31</v>
       </c>
       <c r="F40" t="n">
-        <v>-314.6</v>
+        <v>1108.09</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0126</v>
+        <v>0.0449</v>
       </c>
       <c r="H40" t="n">
-        <v>628.51</v>
+        <v>1270</v>
       </c>
       <c r="I40" t="n">
-        <v>24354.04</v>
+        <v>23919.19</v>
       </c>
       <c r="J40" t="n">
-        <v>24585.1</v>
+        <v>23947.34</v>
       </c>
       <c r="K40" t="n">
-        <v>24781.08</v>
+        <v>24356.96</v>
       </c>
       <c r="L40" t="n">
-        <v>24977.05</v>
+        <v>24766.59</v>
       </c>
       <c r="M40" t="n">
-        <v>25190.57</v>
+        <v>24985.48</v>
       </c>
       <c r="N40" t="n">
-        <v>25404.08</v>
+        <v>25204.37</v>
       </c>
       <c r="O40" t="n">
-        <v>25582.51</v>
+        <v>25804.72</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24724.34</v>
+        <v>25811.9</v>
       </c>
       <c r="C41" t="n">
-        <v>25826.78</v>
+        <v>25900.1</v>
       </c>
       <c r="D41" t="n">
-        <v>24556.78</v>
+        <v>24830.17</v>
       </c>
       <c r="E41" t="n">
-        <v>25779.31</v>
+        <v>25067.09</v>
       </c>
       <c r="F41" t="n">
-        <v>1108.09</v>
+        <v>-712.22</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0449</v>
+        <v>-0.0276</v>
       </c>
       <c r="H41" t="n">
-        <v>1270</v>
+        <v>1069.93</v>
       </c>
       <c r="I41" t="n">
-        <v>23919.19</v>
+        <v>23286.78</v>
       </c>
       <c r="J41" t="n">
-        <v>23947.34</v>
+        <v>24803.08</v>
       </c>
       <c r="K41" t="n">
-        <v>24356.96</v>
+        <v>25144.31</v>
       </c>
       <c r="L41" t="n">
-        <v>24766.59</v>
+        <v>25485.54</v>
       </c>
       <c r="M41" t="n">
-        <v>24985.48</v>
+        <v>26414.31</v>
       </c>
       <c r="N41" t="n">
-        <v>25204.37</v>
+        <v>27343.08</v>
       </c>
       <c r="O41" t="n">
-        <v>25804.72</v>
+        <v>27096.78</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3941,83 +3941,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25811.9</v>
+        <v>24963.8</v>
       </c>
       <c r="C42" t="n">
-        <v>25900.1</v>
+        <v>25204.68</v>
       </c>
       <c r="D42" t="n">
-        <v>24830.17</v>
+        <v>24651.34</v>
       </c>
       <c r="E42" t="n">
-        <v>25067.09</v>
+        <v>24830.98</v>
       </c>
       <c r="F42" t="n">
-        <v>-712.22</v>
+        <v>-236.11</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0276</v>
+        <v>-0.0094</v>
       </c>
       <c r="H42" t="n">
-        <v>1069.93</v>
+        <v>553.34</v>
       </c>
       <c r="I42" t="n">
-        <v>23286.78</v>
+        <v>23760.24</v>
       </c>
       <c r="J42" t="n">
-        <v>24803.08</v>
+        <v>23848.14</v>
       </c>
       <c r="K42" t="n">
-        <v>25144.31</v>
+        <v>24532.12</v>
       </c>
       <c r="L42" t="n">
-        <v>25485.54</v>
+        <v>25216.11</v>
       </c>
       <c r="M42" t="n">
-        <v>26414.31</v>
+        <v>25602.05</v>
       </c>
       <c r="N42" t="n">
-        <v>27343.08</v>
+        <v>25988</v>
       </c>
       <c r="O42" t="n">
-        <v>27096.78</v>
+        <v>26970.03</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4051,57 +4051,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24963.8</v>
+        <v>24769.15</v>
       </c>
       <c r="C43" t="n">
-        <v>25204.68</v>
+        <v>25271.34</v>
       </c>
       <c r="D43" t="n">
-        <v>24651.34</v>
+        <v>24696.59</v>
       </c>
       <c r="E43" t="n">
-        <v>24830.98</v>
+        <v>25099</v>
       </c>
       <c r="F43" t="n">
-        <v>-236.11</v>
+        <v>268.02</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0108</v>
       </c>
       <c r="H43" t="n">
-        <v>553.34</v>
+        <v>574.75</v>
       </c>
       <c r="I43" t="n">
-        <v>23760.24</v>
+        <v>24098</v>
       </c>
       <c r="J43" t="n">
-        <v>23848.14</v>
+        <v>24229.13</v>
       </c>
       <c r="K43" t="n">
-        <v>24532.12</v>
+        <v>24554.31</v>
       </c>
       <c r="L43" t="n">
-        <v>25216.11</v>
+        <v>24879.5</v>
       </c>
       <c r="M43" t="n">
-        <v>25602.05</v>
+        <v>25107.65</v>
       </c>
       <c r="N43" t="n">
-        <v>25988</v>
+        <v>25335.81</v>
       </c>
       <c r="O43" t="n">
-        <v>26970.03</v>
+        <v>25758.02</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4109,19 +4109,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4133,59 +4133,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24769.15</v>
+        <v>25459.32</v>
       </c>
       <c r="C44" t="n">
-        <v>25271.34</v>
+        <v>25891.51</v>
       </c>
       <c r="D44" t="n">
-        <v>24696.59</v>
+        <v>25303.11</v>
       </c>
       <c r="E44" t="n">
-        <v>25099</v>
+        <v>25629.24</v>
       </c>
       <c r="F44" t="n">
-        <v>268.02</v>
+        <v>530.24</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0211</v>
       </c>
       <c r="H44" t="n">
-        <v>574.75</v>
+        <v>588.4</v>
       </c>
       <c r="I44" t="n">
-        <v>24098</v>
+        <v>24121.84</v>
       </c>
       <c r="J44" t="n">
-        <v>24229.13</v>
+        <v>24581.77</v>
       </c>
       <c r="K44" t="n">
-        <v>24554.31</v>
+        <v>24811.62</v>
       </c>
       <c r="L44" t="n">
-        <v>24879.5</v>
+        <v>25041.48</v>
       </c>
       <c r="M44" t="n">
-        <v>25107.65</v>
+        <v>25386.38</v>
       </c>
       <c r="N44" t="n">
-        <v>25335.81</v>
+        <v>25731.27</v>
       </c>
       <c r="O44" t="n">
-        <v>25758.02</v>
+        <v>25846.09</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4203,14 +4199,18 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
@@ -4222,50 +4222,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25459.32</v>
+        <v>25855.12</v>
       </c>
       <c r="C45" t="n">
-        <v>25891.51</v>
+        <v>26445.18</v>
       </c>
       <c r="D45" t="n">
-        <v>25303.11</v>
+        <v>25855.12</v>
       </c>
       <c r="E45" t="n">
-        <v>25629.24</v>
+        <v>26319.45</v>
       </c>
       <c r="F45" t="n">
-        <v>530.24</v>
+        <v>690.21</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0211</v>
+        <v>0.0269</v>
       </c>
       <c r="H45" t="n">
-        <v>588.4</v>
+        <v>590.0599999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>24121.84</v>
+        <v>24714.71</v>
       </c>
       <c r="J45" t="n">
-        <v>24581.77</v>
+        <v>25056.81</v>
       </c>
       <c r="K45" t="n">
-        <v>24811.62</v>
+        <v>25335.04</v>
       </c>
       <c r="L45" t="n">
-        <v>25041.48</v>
+        <v>25613.27</v>
       </c>
       <c r="M45" t="n">
-        <v>25386.38</v>
+        <v>25923.44</v>
       </c>
       <c r="N45" t="n">
-        <v>25731.27</v>
+        <v>26233.61</v>
       </c>
       <c r="O45" t="n">
-        <v>25846.09</v>
+        <v>26479.91</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4291,10 +4291,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
@@ -4306,50 +4304,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25855.12</v>
+        <v>26360.44</v>
       </c>
       <c r="C46" t="n">
-        <v>26445.18</v>
+        <v>26573.5</v>
       </c>
       <c r="D46" t="n">
-        <v>25855.12</v>
+        <v>26245.57</v>
       </c>
       <c r="E46" t="n">
-        <v>26319.45</v>
+        <v>26440.31</v>
       </c>
       <c r="F46" t="n">
-        <v>690.21</v>
+        <v>120.86</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0046</v>
       </c>
       <c r="H46" t="n">
-        <v>590.0599999999999</v>
+        <v>327.93</v>
       </c>
       <c r="I46" t="n">
-        <v>24714.71</v>
+        <v>25265.06</v>
       </c>
       <c r="J46" t="n">
-        <v>25056.81</v>
+        <v>25814.04</v>
       </c>
       <c r="K46" t="n">
-        <v>25335.04</v>
+        <v>26024.42</v>
       </c>
       <c r="L46" t="n">
-        <v>25613.27</v>
+        <v>26234.8</v>
       </c>
       <c r="M46" t="n">
-        <v>25923.44</v>
+        <v>26614.48</v>
       </c>
       <c r="N46" t="n">
-        <v>26233.61</v>
+        <v>26994.16</v>
       </c>
       <c r="O46" t="n">
-        <v>26479.91</v>
+        <v>27035.24</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4367,13 +4365,11 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4388,70 +4384,74 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26360.44</v>
+        <v>26490.3</v>
       </c>
       <c r="C47" t="n">
-        <v>26573.5</v>
+        <v>26493.5</v>
       </c>
       <c r="D47" t="n">
-        <v>26245.57</v>
+        <v>25914.11</v>
       </c>
       <c r="E47" t="n">
-        <v>26440.31</v>
+        <v>26136.56</v>
       </c>
       <c r="F47" t="n">
-        <v>120.86</v>
+        <v>-303.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0115</v>
       </c>
       <c r="H47" t="n">
-        <v>327.93</v>
+        <v>579.39</v>
       </c>
       <c r="I47" t="n">
-        <v>25265.06</v>
+        <v>25917.64</v>
       </c>
       <c r="J47" t="n">
-        <v>25814.04</v>
+        <v>26127.77</v>
       </c>
       <c r="K47" t="n">
-        <v>26024.42</v>
+        <v>26276.35</v>
       </c>
       <c r="L47" t="n">
-        <v>26234.8</v>
+        <v>26424.92</v>
       </c>
       <c r="M47" t="n">
-        <v>26614.48</v>
+        <v>26604.28</v>
       </c>
       <c r="N47" t="n">
-        <v>26994.16</v>
+        <v>26783.63</v>
       </c>
       <c r="O47" t="n">
-        <v>27035.24</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+        <v>26901.43</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4463,82 +4463,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26490.3</v>
+        <v>26091.29</v>
       </c>
       <c r="C48" t="n">
-        <v>26493.5</v>
+        <v>26618.74</v>
       </c>
       <c r="D48" t="n">
-        <v>25914.11</v>
+        <v>26038.07</v>
       </c>
       <c r="E48" t="n">
-        <v>26136.56</v>
+        <v>26569.99</v>
       </c>
       <c r="F48" t="n">
-        <v>-303.75</v>
+        <v>433.43</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0115</v>
+        <v>0.0166</v>
       </c>
       <c r="H48" t="n">
-        <v>579.39</v>
+        <v>580.67</v>
       </c>
       <c r="I48" t="n">
-        <v>25917.64</v>
+        <v>25334.72</v>
       </c>
       <c r="J48" t="n">
-        <v>26127.77</v>
+        <v>25523.55</v>
       </c>
       <c r="K48" t="n">
-        <v>26276.35</v>
+        <v>25846.87</v>
       </c>
       <c r="L48" t="n">
-        <v>26424.92</v>
+        <v>26170.18</v>
       </c>
       <c r="M48" t="n">
-        <v>26604.28</v>
+        <v>26426.26</v>
       </c>
       <c r="N48" t="n">
-        <v>26783.63</v>
+        <v>26682.33</v>
       </c>
       <c r="O48" t="n">
-        <v>26901.43</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
+        <v>27072.89</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4547,90 +4549,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26091.29</v>
+        <v>26464.14</v>
       </c>
       <c r="C49" t="n">
-        <v>26618.74</v>
+        <v>26471.79</v>
       </c>
       <c r="D49" t="n">
-        <v>26038.07</v>
+        <v>25727.93</v>
       </c>
       <c r="E49" t="n">
-        <v>26569.99</v>
+        <v>26046.4</v>
       </c>
       <c r="F49" t="n">
-        <v>433.43</v>
+        <v>-523.59</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.0197</v>
       </c>
       <c r="H49" t="n">
-        <v>580.67</v>
+        <v>743.86</v>
       </c>
       <c r="I49" t="n">
-        <v>25334.72</v>
+        <v>25457.4</v>
       </c>
       <c r="J49" t="n">
-        <v>25523.55</v>
+        <v>26110.11</v>
       </c>
       <c r="K49" t="n">
-        <v>25846.87</v>
+        <v>26279.66</v>
       </c>
       <c r="L49" t="n">
-        <v>26170.18</v>
+        <v>26449.2</v>
       </c>
       <c r="M49" t="n">
-        <v>26426.26</v>
+        <v>26860.33</v>
       </c>
       <c r="N49" t="n">
-        <v>26682.33</v>
+        <v>27271.45</v>
       </c>
       <c r="O49" t="n">
-        <v>27072.89</v>
+        <v>27199.41</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -4638,62 +4636,60 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26464.14</v>
+        <v>26039.54</v>
       </c>
       <c r="C50" t="n">
-        <v>26471.79</v>
+        <v>26069.99</v>
       </c>
       <c r="D50" t="n">
-        <v>25727.93</v>
+        <v>25361.15</v>
       </c>
       <c r="E50" t="n">
-        <v>26046.4</v>
+        <v>25568.56</v>
       </c>
       <c r="F50" t="n">
-        <v>-523.59</v>
+        <v>-477.84</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0183</v>
       </c>
       <c r="H50" t="n">
-        <v>743.86</v>
+        <v>708.84</v>
       </c>
       <c r="I50" t="n">
-        <v>25457.4</v>
+        <v>24984.07</v>
       </c>
       <c r="J50" t="n">
-        <v>26110.11</v>
+        <v>25275.81</v>
       </c>
       <c r="K50" t="n">
-        <v>26279.66</v>
+        <v>25674.47</v>
       </c>
       <c r="L50" t="n">
-        <v>26449.2</v>
+        <v>26073.13</v>
       </c>
       <c r="M50" t="n">
-        <v>26860.33</v>
+        <v>26418.33</v>
       </c>
       <c r="N50" t="n">
-        <v>27271.45</v>
+        <v>26763.53</v>
       </c>
       <c r="O50" t="n">
-        <v>27199.41</v>
+        <v>27215.65</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4720,50 +4716,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26039.54</v>
+        <v>25498.74</v>
       </c>
       <c r="C51" t="n">
-        <v>26069.99</v>
+        <v>25800.62</v>
       </c>
       <c r="D51" t="n">
-        <v>25361.15</v>
+        <v>25172.89</v>
       </c>
       <c r="E51" t="n">
-        <v>25568.56</v>
+        <v>25304.06</v>
       </c>
       <c r="F51" t="n">
-        <v>-477.84</v>
+        <v>-264.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0103</v>
       </c>
       <c r="H51" t="n">
-        <v>708.84</v>
+        <v>627.73</v>
       </c>
       <c r="I51" t="n">
-        <v>24984.07</v>
+        <v>24652.31</v>
       </c>
       <c r="J51" t="n">
-        <v>25275.81</v>
+        <v>24786.22</v>
       </c>
       <c r="K51" t="n">
-        <v>25674.47</v>
+        <v>25214.14</v>
       </c>
       <c r="L51" t="n">
-        <v>26073.13</v>
+        <v>25642.07</v>
       </c>
       <c r="M51" t="n">
-        <v>26418.33</v>
+        <v>25922.98</v>
       </c>
       <c r="N51" t="n">
-        <v>26763.53</v>
+        <v>26203.9</v>
       </c>
       <c r="O51" t="n">
-        <v>27215.65</v>
+        <v>26778.83</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4800,50 +4796,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25498.74</v>
+        <v>25491.35</v>
       </c>
       <c r="C52" t="n">
-        <v>25800.62</v>
+        <v>25783.16</v>
       </c>
       <c r="D52" t="n">
-        <v>25172.89</v>
+        <v>25164.2</v>
       </c>
       <c r="E52" t="n">
-        <v>25304.06</v>
+        <v>25408.64</v>
       </c>
       <c r="F52" t="n">
-        <v>-264.5</v>
+        <v>104.58</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0041</v>
       </c>
       <c r="H52" t="n">
-        <v>627.73</v>
+        <v>618.96</v>
       </c>
       <c r="I52" t="n">
-        <v>24652.31</v>
+        <v>24545.16</v>
       </c>
       <c r="J52" t="n">
-        <v>24786.22</v>
+        <v>24584.98</v>
       </c>
       <c r="K52" t="n">
-        <v>25214.14</v>
+        <v>24990.2</v>
       </c>
       <c r="L52" t="n">
-        <v>25642.07</v>
+        <v>25395.41</v>
       </c>
       <c r="M52" t="n">
-        <v>25922.98</v>
+        <v>25617.92</v>
       </c>
       <c r="N52" t="n">
-        <v>26203.9</v>
+        <v>25840.44</v>
       </c>
       <c r="O52" t="n">
-        <v>26778.83</v>
+        <v>26428.35</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4851,18 +4847,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4875,55 +4871,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25491.35</v>
+        <v>25443.98</v>
       </c>
       <c r="C53" t="n">
-        <v>25783.16</v>
+        <v>25617.31</v>
       </c>
       <c r="D53" t="n">
-        <v>25164.2</v>
+        <v>24831.6</v>
       </c>
       <c r="E53" t="n">
-        <v>25408.64</v>
+        <v>25231.2</v>
       </c>
       <c r="F53" t="n">
-        <v>104.58</v>
+        <v>-177.44</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.007</v>
       </c>
       <c r="H53" t="n">
-        <v>618.96</v>
+        <v>785.71</v>
       </c>
       <c r="I53" t="n">
-        <v>24545.16</v>
+        <v>24545.24</v>
       </c>
       <c r="J53" t="n">
-        <v>24584.98</v>
+        <v>24757.16</v>
       </c>
       <c r="K53" t="n">
-        <v>24990.2</v>
+        <v>25099.16</v>
       </c>
       <c r="L53" t="n">
-        <v>25395.41</v>
+        <v>25441.16</v>
       </c>
       <c r="M53" t="n">
-        <v>25617.92</v>
+        <v>25718.12</v>
       </c>
       <c r="N53" t="n">
-        <v>25840.44</v>
+        <v>25995.08</v>
       </c>
       <c r="O53" t="n">
-        <v>26428.35</v>
+        <v>26402.12</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4931,18 +4931,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4955,59 +4955,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25443.98</v>
+        <v>25251.39</v>
       </c>
       <c r="C54" t="n">
-        <v>25617.31</v>
+        <v>25522.09</v>
       </c>
       <c r="D54" t="n">
-        <v>24831.6</v>
+        <v>24792.79</v>
       </c>
       <c r="E54" t="n">
-        <v>25231.2</v>
+        <v>25087.27</v>
       </c>
       <c r="F54" t="n">
-        <v>-177.44</v>
+        <v>-143.93</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0057</v>
       </c>
       <c r="H54" t="n">
-        <v>785.71</v>
+        <v>729.3</v>
       </c>
       <c r="I54" t="n">
-        <v>24545.24</v>
+        <v>24045.89</v>
       </c>
       <c r="J54" t="n">
-        <v>24757.16</v>
+        <v>24448.86</v>
       </c>
       <c r="K54" t="n">
-        <v>25099.16</v>
+        <v>24838.34</v>
       </c>
       <c r="L54" t="n">
-        <v>25441.16</v>
+        <v>25227.83</v>
       </c>
       <c r="M54" t="n">
-        <v>25718.12</v>
+        <v>25624.05</v>
       </c>
       <c r="N54" t="n">
-        <v>25995.08</v>
+        <v>26020.28</v>
       </c>
       <c r="O54" t="n">
-        <v>26402.12</v>
+        <v>26403.02</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5017,12 +5013,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5044,50 +5040,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25251.39</v>
+        <v>25206.95</v>
       </c>
       <c r="C55" t="n">
-        <v>25522.09</v>
+        <v>25693.89</v>
       </c>
       <c r="D55" t="n">
-        <v>24792.79</v>
+        <v>25133.71</v>
       </c>
       <c r="E55" t="n">
-        <v>25087.27</v>
+        <v>25622.61</v>
       </c>
       <c r="F55" t="n">
-        <v>-143.93</v>
+        <v>535.34</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0213</v>
       </c>
       <c r="H55" t="n">
-        <v>729.3</v>
+        <v>560.1799999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>24045.89</v>
+        <v>24063.49</v>
       </c>
       <c r="J55" t="n">
-        <v>24448.86</v>
+        <v>24322.88</v>
       </c>
       <c r="K55" t="n">
-        <v>24838.34</v>
+        <v>24722.62</v>
       </c>
       <c r="L55" t="n">
-        <v>25227.83</v>
+        <v>25122.35</v>
       </c>
       <c r="M55" t="n">
-        <v>25624.05</v>
+        <v>25451.92</v>
       </c>
       <c r="N55" t="n">
-        <v>26020.28</v>
+        <v>25781.49</v>
       </c>
       <c r="O55" t="n">
-        <v>26403.02</v>
+        <v>26251.39</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5095,21 +5091,23 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5119,79 +5117,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25206.95</v>
+        <v>25540.77</v>
       </c>
       <c r="C56" t="n">
-        <v>25693.89</v>
+        <v>25706.19</v>
       </c>
       <c r="D56" t="n">
-        <v>25133.71</v>
+        <v>25013.54</v>
       </c>
       <c r="E56" t="n">
-        <v>25622.61</v>
+        <v>25181.65</v>
       </c>
       <c r="F56" t="n">
-        <v>535.34</v>
+        <v>-440.96</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0213</v>
+        <v>-0.0172</v>
       </c>
       <c r="H56" t="n">
-        <v>560.1799999999999</v>
+        <v>692.65</v>
       </c>
       <c r="I56" t="n">
-        <v>24063.49</v>
+        <v>24573.53</v>
       </c>
       <c r="J56" t="n">
-        <v>24322.88</v>
+        <v>25166.83</v>
       </c>
       <c r="K56" t="n">
-        <v>24722.62</v>
+        <v>25342.52</v>
       </c>
       <c r="L56" t="n">
-        <v>25122.35</v>
+        <v>25518.21</v>
       </c>
       <c r="M56" t="n">
-        <v>25451.92</v>
+        <v>25902.7</v>
       </c>
       <c r="N56" t="n">
-        <v>25781.49</v>
+        <v>26287.19</v>
       </c>
       <c r="O56" t="n">
-        <v>26251.39</v>
+        <v>26254.07</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5203,177 +5205,91 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25540.77</v>
+        <v>25235.84</v>
       </c>
       <c r="C57" t="n">
-        <v>25706.19</v>
+        <v>26106.19</v>
       </c>
       <c r="D57" t="n">
-        <v>25013.54</v>
+        <v>25217.15</v>
       </c>
       <c r="E57" t="n">
-        <v>25181.65</v>
+        <v>25818.21</v>
       </c>
       <c r="F57" t="n">
-        <v>-440.96</v>
+        <v>636.5599999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0172</v>
+        <v>0.0253</v>
       </c>
       <c r="H57" t="n">
-        <v>692.65</v>
+        <v>889.04</v>
       </c>
       <c r="I57" t="n">
-        <v>24573.53</v>
+        <v>24320.89</v>
       </c>
       <c r="J57" t="n">
-        <v>25166.83</v>
+        <v>24399.89</v>
       </c>
       <c r="K57" t="n">
-        <v>25342.52</v>
+        <v>24835.33</v>
       </c>
       <c r="L57" t="n">
-        <v>25518.21</v>
+        <v>25270.76</v>
       </c>
       <c r="M57" t="n">
-        <v>25902.7</v>
+        <v>25527.98</v>
       </c>
       <c r="N57" t="n">
-        <v>26287.19</v>
+        <v>25785.19</v>
       </c>
       <c r="O57" t="n">
-        <v>26254.07</v>
+        <v>26398.84</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>25235.84</v>
-      </c>
-      <c r="C58" t="n">
-        <v>26106.19</v>
-      </c>
-      <c r="D58" t="n">
-        <v>25217.15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>26039.68</v>
-      </c>
-      <c r="F58" t="n">
-        <v>858.03</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0341</v>
-      </c>
-      <c r="H58" t="n">
-        <v>889.04</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24320.89</v>
-      </c>
-      <c r="J58" t="n">
-        <v>24399.89</v>
-      </c>
-      <c r="K58" t="n">
-        <v>24835.33</v>
-      </c>
-      <c r="L58" t="n">
-        <v>25270.76</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25527.98</v>
-      </c>
-      <c r="N58" t="n">
-        <v>25785.19</v>
-      </c>
-      <c r="O58" t="n">
-        <v>26398.84</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
